--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-350.0300000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.56788e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-61.461</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06911281489594526</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3936698717948769</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.930997304582252</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.87210501640884</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.21947061934407</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.66871024912238</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.013x + -20428.708</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.323747969975969e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2586.84725592886</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000845e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8171067159191447</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-311.8800000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.63289e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-62.927</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1910543130990644</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5267723102585367</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.134585400425155</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.87274017983911</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.45051959703535</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.14594536917514</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.753x + -20994.100</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.243424914054024e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2472.02471984687</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001272e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8173916224843785</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-302.9500000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.65145e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-63.383</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4255483870967612</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.026666666666608</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.132622739018061</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.71042713567837</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.98872998598784</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.25946863714121</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.947x + -21042.937</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.487304966651269e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2429.667557780532</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000008256e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8174941142872491</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-301.46</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.66116e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-63.699</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1458210422812247</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6887733887733997</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.293607954545458</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.80384437239456</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.31562869220404</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.35350925532681</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.114x + -21143.332</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.412624397153866e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2398.365200523783</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000002506e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8175918416580957</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-302.26</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.6729e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.984</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07519083969465755</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4031177829098941</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.945803357314173</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.699353169469554</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.94219095687694</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.16583802044572</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.787x + -20152.544</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.487790344343117e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2369.019706315526</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000115e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8177430005991729</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-285.9899999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.68413e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-64.301</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07955665024630304</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7959420289855733</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.133697234352249</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.056112224448851</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.2524522619306</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.46460540010293</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.319x + -21099.596</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.122977023555733e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2342.644976134678</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8179159658623437</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-281.4999999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.69319e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-64.556</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6324459234609291</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8241676942046238</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.297320061255772</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.769258266309223</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.9910377313169</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.51424850142372</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.413x + -21088.496</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.234150516350621e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2318.814309752132</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000076e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.818099682844138</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-284.3100000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.70232e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-64.753</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4562271062270772</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5707382550335168</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.03739837398374</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.816702977487322</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18.68501317782741</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.3479571801164</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.104x + -20220.069</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.632902926560166e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2297.196617573889</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000877e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8183064137903061</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-274.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.71116e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-65.015</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2970454545454007</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6771047227926291</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.102588438308916</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.627663331371482</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19.05980553726456</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.39902851910159</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 10.197x + -20248.027</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.828493312931939e-12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2277.325681088746</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8185311841796514</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-274.5699999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.71722e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-65.193</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7976702508959942</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4587147887323725</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.124664879356535</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.497173544375334</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19.27708984811738</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.39091253370604</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.182x + -20050.911</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.122233241569001e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2258.278862675067</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000004632e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8187604292413309</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-270.4099999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.72603e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-65.396</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4420704845814839</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4747081712061997</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8945469798657776</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.559654350417166</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19.59334227620773</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.45181317356524</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.295x + -20123.388</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.206565981022582e-14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2240.091406700813</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8189917624324934</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-262.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.73371e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-65.59399999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3541899441340641</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5342642320086169</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.362996594778637</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.512400906002286</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.65905631038383</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.47601219736865</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 10.340x + -20061.183</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.002991068050196e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2222.104134904337</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.00000000000118e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8192459476339421</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-262.8500000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.74088e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-65.809</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3841818181818274</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4550087873462115</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7988326848248868</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.52915966386556</v>
+      </c>
+      <c r="J14" t="n">
+        <v>17.04792516646086</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.29369569325458</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 10.008x + -19212.895</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.037389633769716e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2204.560726432944</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.00000000000048e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8195006339956028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-250.9400000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.74915e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-66.01600000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.632649572649592</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4783910196445003</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9291838417147177</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.663282674772063</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19.9087522418928</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.55171167265325</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.485x + -20039.837</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.89597990234963e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2186.438826776923</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8197793088208508</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-246.79</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.75645e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-66.197</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2434042553191375</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4688046647230798</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9983430799221245</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.814862138533979</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20.17378351015897</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.57235353542768</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.525x + -19962.328</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.88081800803275e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2168.44960213808</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000814e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8200499075385141</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-243.71</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.76371e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-66.396</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1544207317073149</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6698315467074842</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.095953141640018</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.687617765814273</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20.48898892195001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.58906510992153</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.557x + -19870.824</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.394618212055567e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2150.697390267059</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000105e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8203218995395141</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-236.8999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.77145e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-66.596</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.425842696629147</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3551119766309576</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.502519893899108</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.525184275184312</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20.52617800020768</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.61605159952668</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.611x + -19817.718</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.780509939592464e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2132.505116102536</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000376e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8205959326397551</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-231.95</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.77966e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-66.782</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6886649874056293</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4292249047014076</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.168306010928987</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.635066666666613</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.49012737551057</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.63667721716214</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.652x + -19731.541</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.256970417595998e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2114.301664692274</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000429e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8208555340040277</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-229.98</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.78655e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-66.97799999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2462757527733778</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2266488413547116</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.536611374407521</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.670784982935182</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20.63670133607735</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.65233205633582</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.683x + -19632.737</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.1907409611764e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2096.065770975982</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8211350358494037</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-228.5699999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.79416e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-67.196</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3324478178368112</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5527397260273904</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.474022346368743</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.773021925643575</v>
+      </c>
+      <c r="J21" t="n">
+        <v>17.92286347236746</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.44383619669455</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 10.280x + -18671.840</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.196065742501888e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2077.467099719895</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.00000000000388e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8214261988556832</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-221.3499999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.80047e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-67.372</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4352402745995777</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.911654135338464</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.090259740259713</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.595928753180744</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20.90349361015664</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.72507677859303</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.831x + -19571.366</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.672082578549202e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2057.764452642697</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.00000000000319e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8217278797467344</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-642.1500000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.24598e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-52.22</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>7.326634273776826</v>
+      </c>
+      <c r="K2" t="n">
+        <v>80.46022753213575</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 5.950x + -16596.437</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.086883614155678e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3150.041474697055</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000002127e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.816019314392889</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-473.1900000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.50617e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-57.014</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07316692667706126</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4952591656131515</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.029713493530446</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.653190348525476</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.2923991778671</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.29931049878363</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 7.395x + -18039.687</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.953758495807705e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2813.683736807206</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000092e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8169922817106536</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-404.27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.56008e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-58.915</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3881556683587455</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6341922695738159</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.070540677109657</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.913585813044759</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.58080452143282</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.12721420698479</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 8.297x + -19576.865</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.587305870153576e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2723.73192417196</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000007256e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8172046310811947</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-359.5299999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.57981e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-59.933</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6132111861138156</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9827722772277231</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.457560405300037</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.426779793251413</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.55784237975648</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.82196546708683</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.238x + -21528.525</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.017523991552934e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2674.843221352956</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8173278837103433</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-366.6800000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.59346e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-60.657</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01195039458849224</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8844909609896571</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.167331932773075</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.84843063488352</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.17851291028614</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 8.360x + -18971.860</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.564685976818668e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2633.010412677293</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000135e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.817480515916053</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-336.4000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.60676e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.223</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2155255544840882</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9361702127659295</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.385803520726878</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.918413348946138</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.88479081851846</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.90111205292037</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.359x + -21101.023</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.699355603460853e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2592.781821596367</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8176567548882594</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-335.4899999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.61957e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-61.699</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.250248756218918</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5526490066225234</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.03590425531912</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.737578757875707</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.19478999449868</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.7154442810232</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.080x + -20113.860</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.600960766084204e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2554.027386601243</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.00000000001678e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8178570218045128</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-321.52</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.63361e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5366504854368606</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3584967320261362</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.143029490616631</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.621946082561104</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.95061505542963</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.85014603447942</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.281x + -20281.378</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.421581870159603e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2516.5753119736</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8180700508087868</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-307.1000000000004</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.64564e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.602</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.16601178781914</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.650267857142817</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.226390346274944</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.944460988683725</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28.42415180959887</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.21828066961335</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.876x + -21379.636</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.339855109240715e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2480.550825597673</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8182931365863191</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-305.1800000000003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.6591e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-62.996</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1770025839793141</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5423480083857113</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.225000000000019</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6764285714286</v>
+      </c>
+      <c r="J11" t="n">
+        <v>21.1056576418306</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.04447768895014</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.586x + -20420.200</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.036382452996853e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2446.944159903048</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8185136253431561</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-414.4500000000003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.55935e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-58.352</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4268680445151118</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7776947705443157</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.249007862223878</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.227582397348579</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24.04814665321205</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.16577915132731</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.344x + -19828.458</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.542881904764241e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2701.831590606215</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000112e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8177933982786206</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-342.4899999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.61466e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-61.194</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.166273584905667</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1718749999999939</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.156821378340342</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.798462929475662</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.6007973304738</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.62452825045602</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.950x + -20067.307</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.142657200067725e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2583.229542437809</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000002826e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8181484381521468</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-326.6300000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.62738e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-61.952</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1121212121212109</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.571169354838756</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9669083717863549</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.636326023996679</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.87226948236077</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.83055126744466</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.251x + -20370.423</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.025575325807361e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2538.714699164927</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001918e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8182197875865584</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-320.5900000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.63498e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.36</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3478858350951508</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.020977353992901</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.096551724137973</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.54973305954825</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.29080252833919</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.9650348185034</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.459x + -20597.931</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.135952387318772e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2507.926963519586</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000226e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.818279889635725</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-322.96</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.64007e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-62.701</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.02926208651398968</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2988977955911664</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.951447245564891</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.336912362159</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.95622810917169</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.77616862547849</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.170x + -19693.177</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.115334331640313e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2480.208714911109</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8183684494997781</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-311.4599999999996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.64831e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.109</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1882943143812804</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1510204081632536</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.000280636108542</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.433182076006768</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.53433330166287</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.87018936677882</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.311x + -19793.929</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.497925975947455e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2452.968327995208</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8184932486559968</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-302.3600000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.65328e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-63.396</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6347368421052422</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5179982440737453</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9578145695364265</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.690482128013273</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.76744932080738</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.21531341296713</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.871x + -20864.349</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.759762479546224e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2427.61287404634</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8186466810846492</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-298.0699999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.66028e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.671</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1390697674418673</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6590796019900218</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.313046495489257</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.581365159128966</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.85640074615799</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.32075407376576</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.056x + -21066.680</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.784359300133081e-13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2403.38300821044</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8188129449133479</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-301.3700000000003</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.66653e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-63.943</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03146766169153264</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4468129571577376</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7095477386934208</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.445284124194475</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.36313144980152</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.10431499623327</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.684x + -20034.878</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.268957503321733e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2380.142599188782</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000081e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8190007458013827</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-288.0599999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.67369e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-64.239</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2909407665505153</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7679039301310366</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.388283582089544</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.755659574468069</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.16256421981209</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.39459888704101</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.189x + -20962.993</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.243229995285135e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2357.842904353146</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000188e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8191968952765044</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-281.74</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.68074e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-64.488</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.241043723554316</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8281951219512091</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.409725685785603</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.750479511769812</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23.31820649449569</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.48819197142076</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.363x + -21147.042</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.786353359074191e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2336.549176340451</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.819398544133023</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-286.6199999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.68452e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-64.72499999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.05493197278910691</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5605932203389947</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.162962962962901</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.495202952029508</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.02803514226293</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.27667473740605</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.978x + -20121.952</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.320292495968892e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2315.660692212417</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000522e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8196288879205859</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-284.7200000000003</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.69242e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-64.98999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.191961414791003</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1630617977528206</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8758139534883993</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.359870782483834</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.54082510549502</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.06863647500586</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.625x + -19184.507</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.650732854260847e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2295.033058050712</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8198401343475772</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-282.23</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.69735e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-65.199</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2969696969696615</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3851315789473341</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6818956336528617</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.319264069264076</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16.71935717042281</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.12331800311765</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 9.715x + -19215.074</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.267501041664768e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2275.765793905397</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000099e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8200691839237128</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-265.97</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.70132e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-65.411</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.472549019607821</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7118993135011537</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.347467876039276</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.864963855421668</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24.94880172072926</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.66097067907468</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.700x + -21160.371</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.791518274147209e-12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2257.770160290217</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8202696063643365</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-270.3299999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.70694e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-65.61799999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3783821478382325</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8398657718120702</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9453231939162883</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.576962457337811</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20.22864971093547</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.46436919022685</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.318x + -20173.417</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.177594460518473e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2238.235005567555</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8205216769259432</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-269.1999999999998</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.71452e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-65.85899999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1500000000000019</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4660280970625718</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.282992125984167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.15361890694239</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17.45927884714912</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.24640570436796</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 9.925x + -19172.143</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.620803406553089e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2218.787863907711</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000045e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8207782671205919</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-259.6100000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.71953e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-66.087</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6387520525450973</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5451793721972986</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9971404541631533</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.793554817275863</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.85165652855288</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.54828666484978</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.478x + -20148.074</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.872725503930049e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2199.060141569402</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000183e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8210302304657228</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-262.8900000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.72619e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-66.294</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.04354587869363801</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5247563352826666</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7865070729054349</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.334049079754501</v>
+      </c>
+      <c r="J20" t="n">
+        <v>17.8084165862987</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.34739039629048</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.103x + -19204.153</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.781154353761066e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2179.398350205155</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.00000000000542e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8212928590414705</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-243.7900000000002</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.734e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-66.50700000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4278592375366325</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9012387387386892</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.432857142857106</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.961904761904775</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.38269113505972</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.88351923064154</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 11.168x + -21202.283</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.550094168873597e-14</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2159.728236925961</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.821558097952326</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-246.6500000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.73957e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-66.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1030266343825631</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7848809523809244</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.013526119402955</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.438801791713309</v>
+      </c>
+      <c r="J22" t="n">
+        <v>21.59577158869739</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.6600940446538</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.699x + -20063.871</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.459649451401785e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2139.959100126716</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000251e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8218301952795388</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-590.0200000000004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.28544e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-53.846</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>8.234688476041077</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.36431841194489</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 6.584x + -17992.938</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.425309557383945e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3081.059801711274</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000003688e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8161333206409143</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-411.4200000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.52144e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-59.005</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3834862385320884</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4263543191800724</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.195845190665972</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.889665127020793</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.10672055246469</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.19487280191028</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.380x + -20013.350</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.450349800561396e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2745.301739067062</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000679e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8171872320926066</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-362.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.57072e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-60.647</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.08645235361653589</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.395790458372292</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9033918128654946</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.694973070017998</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.5003643464166</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.52017807525401</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 8.804x + -20223.327</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.69938379951708e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2654.604223475348</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000151e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8174623314093123</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-335.2199999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.58989e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-61.393</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1851923076923117</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.742928039702247</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.338007380073789</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.979223536548399</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.21520044792798</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.02204049867409</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.550x + -21617.461</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.323591914397955e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2605.064474555924</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8176126109616081</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-328.71</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.60634e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.881</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1470503597122284</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.56597671410087</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.236050860134603</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.822561531449396</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.46317990057672</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.90344003211119</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.363x + -20812.288</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.962429432940161e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2564.296362406016</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000014483e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8177529448784333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-311.1500000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.62199e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-62.315</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3252735229759296</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9488742964351774</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.370902817711314</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.006579357655121</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.72156214473095</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.28566690441858</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.993x + -21994.796</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.776885641637098e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2526.265882645215</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.817920919922607</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-312.0499999999997</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.63582e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.69</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1038777908343106</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1373088685015246</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.025129725722789</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.796234939759024</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.75838870489735</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.11994026873391</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.710x + -21017.875</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.476418874005884e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2490.742438648057</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8180750580475632</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-303.1699999999996</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.65159e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.069</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4305309734513381</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7608784473953437</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.342674616695105</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.87209831588531</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.46812717691878</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.20785551503312</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.858x + -21064.627</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.723600175702745e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2456.832642935767</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8182563140784691</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-294.6900000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.66405e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-63.424</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3675646551723929</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4226032735775437</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.121720430107549</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.844479495268125</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.95898081541222</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.25992660385282</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.948x + -20997.092</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.065434141302727e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2424.319554397909</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000002584e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.818431322878423</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-285.3699999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.67788e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.748</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3976486860304238</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3613333333333243</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.020038659793785</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.027326440177282</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.49958851339385</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.35980011485024</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.126x + -21129.257</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.320895351229182e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2394.173291675013</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000006275e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8186182018649745</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-393.2799999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.5166e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-59.466</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1959183673469399</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6597989949748657</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.100452716297781</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.878398404103713</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.66364582666129</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.37913450888188</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.615x + -20573.544</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.170304303577866e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2723.277843501315</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000497e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8174266170452604</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-343.8899999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.5857e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-61.761</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02034104750304589</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5954849498328042</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.345410103204742</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.03013299732778</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.61803513372645</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 8.941x + -19997.393</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.002591032092316e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2587.165441155724</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8178427318459133</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-325.8600000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.60358e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-62.368</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.260554371002118</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4878522837706806</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9188461538460965</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.66925425207144</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.18992051636893</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.03481165514242</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.570x + -21071.539</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.571592674941024e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2538.874834447206</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000225e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8179661160573165</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-310.21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.61499e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.723</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4680147058823848</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.040714908456841</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.341228070175515</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.191389830508532</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27.82732694138629</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.42708391190912</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.249x + -22371.364</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.812708811615704e-13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2504.426155924969</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8180717381706577</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-311.8700000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.62565e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.063</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1642760487144584</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6416071428571334</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.185607196401746</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.75555555555556</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.81945140759208</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.23096453301466</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.898x + -21292.767</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.394252693007735e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2476.020271105374</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000113e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8181701141548615</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-307.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.63224e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.342</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.322698744769866</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6099735216240337</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9641877256317694</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.750423539901952</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.34848952029452</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.31447045918324</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.044x + -21420.927</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.546173903231464e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2453.672192265043</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000003121e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8182800585519358</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-299.0799999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.6399e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-63.591</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05043327556324714</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5197905759162222</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.186715867158696</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.765391304347803</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.79453431421497</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.38940004641381</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.179x + -21544.927</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.426944024014158e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2433.13047114036</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.00000000000092e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8184168526982933</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-293.9299999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.64761e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.819</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1254929577464822</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.782976324689993</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.156786171574951</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.79692168402001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.32205963369945</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.44831367860151</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.288x + -21613.733</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.16263633443452e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2413.248949911742</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8185938627657556</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-291.79</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.65302e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-64.02800000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.31796565389697</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.110242587601143</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.227420667209135</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.906088650754924</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.81025027808876</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.46216642747328</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 10.314x + -21505.441</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.345472417549289e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2393.858602499464</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000104e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8187742416076917</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-291.6300000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.66007e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-64.283</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001488833746904069</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4059617547806575</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.356790123456814</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.420941828254865</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.87809987552327</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.28096502357302</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.985x + -20594.971</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.825886906986223e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2374.418761341155</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000557e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8189891355133533</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-278.5899999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.66771e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-64.48699999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3273489932885895</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6273316062175948</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.353562447611091</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.952159468438487</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23.35922062666841</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.56837519777463</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.517x + -21599.756</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.372774734725803e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2355.567641591116</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.00000000000031e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8192327580215248</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-281.52</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.67451e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-64.69199999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.713541666666625</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6293772032902399</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7183282208588976</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.435401459854079</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.1503199371461</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.37076751565644</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 10.145x + -20608.624</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.190584146090764e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2336.211412167455</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8194843553541412</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-275.8000000000002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.68093e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-64.908</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1962174940898458</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2391719745222758</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.018621399176959</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.394614512471751</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19.36322230843254</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.43795714968284</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 10.269x + -20706.392</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.357878013934101e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2316.517725308374</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000188e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8197500442627443</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-265.1400000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.68826e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-65.13500000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3358722358722225</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4533849129594112</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.329816513761455</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.822842639593877</v>
+      </c>
+      <c r="J15" t="n">
+        <v>24.51467701874523</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.72405089865927</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 10.829x + -21745.415</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.443108879293533e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2297.117218662236</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000011993e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.820021308622045</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-275.5100000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.69432e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-65.307</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1125000000000102</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2786707882534825</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8694623655913647</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.441993720565193</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17.13175230033426</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.27659453564172</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.977x + -19745.063</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.511004981708023e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2277.833135732118</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000151e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8203141624254933</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-268.5599999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.7027e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-65.545</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.07367149758453706</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.158631921824107</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6905544147843979</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.365894039735122</v>
+      </c>
+      <c r="J17" t="n">
+        <v>17.11659033325271</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.286649382455</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 9.995x + -19617.170</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.522623202295483e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2258.148620359526</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.00000000002555e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8206048508333549</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-253.3800000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.70891e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5509554140126989</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.094622093023203</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.362405446293567</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.049121044701122</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25.50213388485793</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.82944702206727</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 11.051x + -21663.669</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.960059470758436e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2238.379325004129</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8208897780338125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-261.4500000000003</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.71565e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-65.958</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2010638297872467</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.820043811610139</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.29107901444348</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17.53740833600056</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.40794136611431</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.213x + -19724.611</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.969591339762135e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2218.255854321172</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000024667e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8211831260788123</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-266.0900000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.72242e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-66.15600000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.02925262411359317</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3329016411290147</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.345867295065355</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.317468293052444</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.79862059585109</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.19932005317142</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 9.844x + -18794.789</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.390666689570101e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2198.118659851394</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000002782e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8214780621471813</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-248.9100000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.73186e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-66.38</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1522550544323391</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6109782608695393</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9685929648241338</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.82022160664816</v>
+      </c>
+      <c r="J21" t="n">
+        <v>21.18034895660722</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.66776912249384</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 10.714x + -20401.189</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.62735696975217e-10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2177.562979443003</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8217749184601845</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-233.4300000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.73981e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-66.611</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7194871794871567</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5343832020997323</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.151388888888861</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.774398931433593</v>
+      </c>
+      <c r="J22" t="n">
+        <v>26.56287558678353</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.95685930851931</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.332x + -21468.212</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.714803429648379e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2157.333272256946</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000121306e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8220778198675921</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-634.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.31914e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-53.358</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1389931740614312</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7245493107105099</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.288827636898208</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.062925683610159</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.61971839664786</v>
+      </c>
+      <c r="K2" t="n">
+        <v>80.51210212876322</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 5.984x + -15874.346</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.72998546983139e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2993.862111401536</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8155172555282038</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-437.3099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.56388e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-58.882</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08793103448276125</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5272817460317337</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9409596662030196</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.586843211433382</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.56235382455064</v>
+      </c>
+      <c r="K3" t="n">
+        <v>82.8008771632378</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 7.917x + -18389.017</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.672037935581266e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2676.007602567666</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000011993e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8165086764521647</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-366.48</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.60971e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-60.653</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2468435498627512</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5976987447698477</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.274279123414075</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.032618296529959</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.89910652263104</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.800322581817</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.206x + -20764.144</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.209362632440205e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2592.350911856874</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8166992361082839</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-355.9099999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.6273e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-61.436</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1470588235294004</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.287663107947844</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.330056497175139</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15.30167275544352</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.56031029996976</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 8.860x + -19510.069</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.827790617756636e-13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2547.892585559964</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.816749196087574</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-324.8700000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.64217e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.976</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3713188220231063</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.653948462177858</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.572194199243367</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.183277814790173</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25.08181189675972</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.23501132711984</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 9.905x + -21674.404</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.462583577566745e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2510.960577695527</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000026449e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8168381229918887</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-327.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.65402e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-62.345</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2295757575757543</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.602048085485331</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.02297200287156</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.787950200088943</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19.25451336890452</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.10817881209063</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 9.690x + -20864.734</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.024751398629683e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2476.289429560517</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8169639935614609</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-315.5099999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.66921e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.762</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2239130434782363</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5164948453607965</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.226533864541761</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.923291626564001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.16479779337769</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.23032734038878</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.897x + -21043.623</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.065073969227068e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2443.014271513823</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000303e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8171037842308665</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-302.6999999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.68514e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.142</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01626984126982352</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7189767441860725</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.23158301158298</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.744984669294811</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.95283912038498</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.28896888205668</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.999x + -20996.501</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.25785676806503e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2410.64347555354</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001071e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8173117676151218</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-296.3499999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.69867e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-63.476</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.46795774647887</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5330365093499739</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.557218777679419</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.794229074889852</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.54304900235988</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.36956451087175</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 10.143x + -21047.239</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.595270494357625e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2379.623915660651</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000808e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8175302622281605</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-284.1400000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.71307e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.814</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4576051779935844</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8505714285714113</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.168970814132045</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.807663896583642</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.07616813643018</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.47507958186047</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.338x + -21213.489</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.211286328280494e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2350.232133890175</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000597e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8177875118159668</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-359.3999999999996</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.59609e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-61.009</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0748120300751902</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5361007462686694</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.137841625788382</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.479186413902029</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.46062478302137</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.5543991192702</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.852x + -19952.424</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.001749904773327e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2576.472967375066</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8173246663261311</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-316.77</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.65467e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-62.502</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1963380281689936</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5152654867256768</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.431133540372693</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.839020843431862</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.9011448805181</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.08925682497375</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.659x + -20793.571</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.250707467516904e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2473.10513730076</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8176015206148097</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-305.9499999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.67275e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-62.975</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0489112227805572</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6816784869975813</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.224822190611617</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.627798901563164</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.61133451116726</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.21018159591914</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.862x + -20881.196</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.719296877167754e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2432.704602150638</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8176559638828779</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-310.9699999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.68375e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-63.281</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.154945054945038</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8013353115726938</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9853202846974791</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.462901376146825</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17.25250939835447</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.0573327975454</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.607x + -20031.476</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.869679054820073e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2401.39949751879</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8177376544004198</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-298.3000000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.69563e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.596</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3045366795366647</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.807838983050774</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.258918918918867</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.09236076885161</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.48362324576938</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.34704382289181</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.103x + -20899.763</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.458778026601151e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2372.219847912399</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000017e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8178344398151369</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-291.53</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.70626e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.888</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4997633136094589</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4712918660287061</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.099537037037107</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.863270142180041</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.8429634525422</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.43734079830348</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.268x + -21030.504</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.099135095323489e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2346.14593972893</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8179709595681299</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-295.6199999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.71799e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-64.15900000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1372093023255872</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1632102272727234</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5744755244754897</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.480989180834662</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15.95354433378363</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.99080242413268</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 9.500x + -19138.339</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.029933164846459e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2322.046114774923</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8181370194560634</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-277.3899999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.7292e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-64.395</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3059602649006583</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8247311827957384</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.302034428795044</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.969181141439258</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.79719582802324</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.51384114708173</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.412x + -20923.408</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.119070493671383e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2299.791109757578</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8183280814833082</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-280.5899999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.73763e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-64.60299999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2335897435897476</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8039503386004322</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.107149758454123</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.541460470730267</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.68171960298863</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.32091260584585</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 10.056x + -19972.246</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.002957545166091e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2279.53393126862</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8185505935177548</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-278.5300000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.74687e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-64.825</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1552875695732857</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1848314606741487</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8980362537763764</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.501993355481739</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16.63378257857468</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.14704381011862</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.755x + -19163.824</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.876029599413158e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2259.616609348771</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8187869365856546</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-272.1799999999998</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.75528e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-65.027</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1801611278952677</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5463903743315345</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.398526315789415</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.467764298093565</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19.41236923403016</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.40980167338525</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.217x + -19974.308</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.652424625790092e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2240.029239039912</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000876e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8190313616880684</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-268.0200000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.76469e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-65.264</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1640465793304201</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.03872832369942201</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8859234234234478</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.538610378188251</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16.80655903712441</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.21281745699126</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.867x + -19071.302</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.405646836199243e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2220.45164926095</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000038715e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8192951388287493</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-263.23</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.77318e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-65.47199999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.02061349693251201</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1388489208633126</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8564722617353453</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.370229007633536</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.86446670764263</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.26872441677907</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.964x + -19107.991</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.68519159908061e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2201.364861816771</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8195449557188662</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-256.96</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.78166e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-65.669</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3023904382470256</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3964664310954357</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.107221542227598</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.493669803250675</v>
+      </c>
+      <c r="J15" t="n">
+        <v>17.14309350332852</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.27469124761832</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 9.974x + -18975.231</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.309785625433233e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2182.479627035726</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8198153963052757</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-252.7500000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.79004e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-65.892</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.03828124999999826</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4239454094293033</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9264634146341579</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.408581138487672</v>
+      </c>
+      <c r="J16" t="n">
+        <v>17.38867140859042</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.28098358509754</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.985x + -18841.880</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.073822070376296e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2164.218695951675</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000098e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8200853084615732</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-242.3899999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.79878e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-66.048</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6505555555556124</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6110091743119126</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.258864541832704</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.65665829145731</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20.44918926322903</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.58584851380431</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.551x + -19826.849</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.613226763162385e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2145.953973210237</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8203575111761711</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-241.3600000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.80715e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-66.29000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.03673110720562076</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3247524752475102</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8567360350493016</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.592844677137885</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17.52263532439852</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.33590775682683</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.083x + -18725.292</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.620729427644264e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2127.456486914492</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.00000000000006e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8206301626029076</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-228.4099999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.8148e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-66.46299999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6942381562099648</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.345919778699847</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.652189781021872</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.003128103277153</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25.5149896845222</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.8472275073682</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 11.089x + -20569.156</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.46674741496479e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2109.284482831431</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000001002e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8209033797924614</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-232.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.82385e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-66.68000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3023853211009121</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.4100502512563085</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.025245901639266</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.494798657718168</v>
+      </c>
+      <c r="J20" t="n">
+        <v>17.44413620813657</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.3718801124962</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 10.148x + -18543.725</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.522106775312913e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2091.518776425849</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8211643784372921</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-229.6000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.8306e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-66.855</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1186046511628068</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7689463955637642</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.188563829787132</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.226170376055194</v>
+      </c>
+      <c r="J21" t="n">
+        <v>17.81629726446116</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.41751953333907</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 10.231x + -18551.967</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.055729918591458e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2073.324016333495</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8214385401595771</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-218.1800000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.83893e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-67.05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5647696476963108</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5908685968819308</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.217177242888365</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.905502567865054</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20.84607862213791</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.674206150773</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.727x + -19356.706</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.08786599857168e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2054.917622897904</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8217239236305618</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-537.3899999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.56611e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-58.574</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3486046511627698</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5514157014157092</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.232695139911637</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.885199076745522</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.81704803791686</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.94691809876741</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.068x + -15811.897</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.790087011635379e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2451.890993791166</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000365e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8175070335430823</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-354.3599999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.79414e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-64.09399999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3588477366254406</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5127753303964417</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6373447946513836</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.477863910422069</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.98046504472647</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.70293679891785</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.062x + -17208.840</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.976602508334061e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2154.014554009581</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000007021e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8184154589588939</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-304.6500000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.82684e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-65.599</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1738582677165369</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3570347957640028</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.357492795388785</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.372817764165362</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.10290299005365</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.20803156131308</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.859x + -18040.811</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.664386647689722e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2082.038696500387</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8185937882319108</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-290.28</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.83732e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-66.264</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08115696536102841</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6274840578390521</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.292061199343341</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.299978270548977</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32.33805799693324</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.22866483204541</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 9.894x + -17730.187</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.107602193868262e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2044.046495209578</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001067e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8187290695597692</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-280.4200000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.84756e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-66.679</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04210455880302637</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7824916385878236</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.517462033495072</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.290929851793189</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.38576633600083</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.32231179456203</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.058x + -17767.150</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.054403846345418e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2012.678866720348</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000221e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8188776381573664</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-268.8299999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.85869e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-67.093</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1457748853064295</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7718386937785487</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.508840863099997</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.307237582321114</v>
+      </c>
+      <c r="J7" t="n">
+        <v>36.71233965526284</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.40353029469115</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.205x + -17781.512</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.114979369353384e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1982.892256509418</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000158e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8190833049760865</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-266.1499999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.86851e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-67.431</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2994496512641588</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5417194830273654</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.222136092536269</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.996206807629712</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.3574052993444</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.31086005262659</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.038x + -17207.218</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.418852326674026e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1953.937251649365</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000006949e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8193265740749397</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-259.55</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.88131e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-67.727</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7832055013424076</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.141664433747493</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.047436710604299</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.25101787174676</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.39118073912169</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.183x + -17229.113</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.077135247975173e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1925.844962918161</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000086e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8195900053713181</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-245.98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.89084e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-68.029</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1387692307692332</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5932170542635534</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8230834035383143</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.506753458096021</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.71147425255148</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.81318980529782</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.016x + -18499.841</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.151239635401392e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1898.99815532462</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000042839e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.819881167266154</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-246.7399999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.90098e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-68.342</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1797860043332367</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4857745568484353</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.213098180450833</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.044100565635068</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.27694640384896</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.49627319990968</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.378x + -17120.933</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.579921850165052e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1873.937511008381</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000042385e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8201622407633004</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-473.96</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.47316e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-56.819</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.196392617449662</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7033579965851531</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.305686205686208</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.089555517998962</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.71452402252282</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.46736018888438</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 7.562x + -18797.531</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-18797.5310808025</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.53059518513909e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>473.96</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000036296e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8167711133695439</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-401.3600000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.53993e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-59.185</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03747795414462193</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8657534246575769</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.250913705583778</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.705566012368892</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.2455581810793</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.19808207998913</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 8.384x + -19879.695</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-19879.69519812554</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.268148809046955e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>401.3600000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8170985786547826</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-372.9200000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.56606e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-60.135</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5407838983050834</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7072122052704208</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.463977272727263</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.829421817146058</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.395010753338</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.53630557181546</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 8.827x + -20482.232</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20482.23161651968</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.069725929926401e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>372.9200000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8172552841217894</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-359.3600000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.58279e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.746</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3248896734333596</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9201657458564007</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.066175115207367</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.781132075471695</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.86308698379345</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.73705993304102</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 9.112x + -20816.781</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20816.7812114036</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.033644803438425e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>359.3600000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000002743e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8173227183843529</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-355.1200000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.59908e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.209</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2128230616302022</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7168784029037711</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9632145258910516</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.547996794871786</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.34302339477952</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.54559931867567</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 8.839x + -19846.414</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19846.41411952285</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.25560870921364e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>355.1200000000003</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8174198236172382</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-342.6699999999996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.61229e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.639</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1495000000000117</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4722554890219663</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9614684466019159</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.60989106753813</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.7961360208567</v>
+      </c>
+      <c r="K7" t="n">
+        <v>83.67340039265403</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 9.019x + -20002.596</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-20002.59579901699</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.987011567362903e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>342.6699999999996</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000002028e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8175664051140747</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-334.4399999999996</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.6261e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.004</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09293193717277154</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2840198863636422</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.042970822281184</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.661189683860235</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.51033246693692</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.78452013252992</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 9.182x + -20126.953</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-20126.9531701673</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.758849038161764e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>334.4399999999996</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000238e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8177346224402359</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-314.5099999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.63999e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.394</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7237366003063038</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.877333333333396</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.259237246161507</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.083392226148422</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.83201034958929</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.14860515850387</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 9.758x + -21226.347</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21226.34727106131</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.828193003699344e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>314.5099999999998</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000062e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8179248010997409</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-321.2599999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.64978e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-62.694</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.09751984126984883</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5292568203198169</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.183730158730159</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.644236371202658</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.59680704060719</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.95881316459732</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 9.449x + -20264.892</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20264.89165288859</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.146666063726302e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>321.2599999999998</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8181297373002657</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-314.0999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.65937e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-62.993</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4125842696629033</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.259853121174958</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.269389373513136</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.919780743565296</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.93087611708754</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.03429603958867</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 9.569x + -20317.455</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20317.45519032307</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.047578772244435e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>314.0999999999999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000001203e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8183555707089423</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>83.66871024912238</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.013x + -20428.708</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-20428.7082248694</v>
       </c>
       <c r="Y2" t="n">
         <v>1.323747969975969e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2586.84725592886</v>
+        <v>350.0300000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000845e-08</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>84.14594536917514</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.753x + -20994.100</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-20994.09988761647</v>
       </c>
       <c r="Y3" t="n">
         <v>2.243424914054024e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2472.02471984687</v>
+        <v>311.8800000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001272e-08</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>84.25946863714121</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.947x + -21042.937</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-21042.93744743958</v>
       </c>
       <c r="Y4" t="n">
         <v>3.487304966651269e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2429.667557780532</v>
+        <v>302.9500000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000008256e-08</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>84.35350925532681</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.114x + -21143.332</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21143.3318205291</v>
       </c>
       <c r="Y5" t="n">
         <v>2.412624397153866e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2398.365200523783</v>
+        <v>301.46</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002506e-08</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>84.16583802044572</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.787x + -20152.544</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20152.54411207497</v>
       </c>
       <c r="Y6" t="n">
         <v>6.487790344343117e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2369.019706315526</v>
+        <v>302.26</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000115e-08</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>84.46460540010293</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.319x + -21099.596</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21099.59584119752</v>
       </c>
       <c r="Y7" t="n">
         <v>3.122977023555733e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2342.644976134678</v>
+        <v>285.9899999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000048e-08</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>84.51424850142372</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.413x + -21088.496</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21088.49644340535</v>
       </c>
       <c r="Y8" t="n">
         <v>4.234150516350621e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2318.814309752132</v>
+        <v>281.4999999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000076e-08</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>84.3479571801164</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.104x + -20220.069</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20220.06887163307</v>
       </c>
       <c r="Y9" t="n">
         <v>8.632902926560166e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2297.196617573889</v>
+        <v>284.3100000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000877e-08</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>84.39902851910159</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 10.197x + -20248.027</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20248.02688448182</v>
       </c>
       <c r="Y10" t="n">
         <v>4.828493312931939e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>2277.325681088746</v>
+        <v>274.7</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>84.39091253370604</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.182x + -20050.911</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20050.91065421495</v>
       </c>
       <c r="Y11" t="n">
         <v>2.122233241569001e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2258.278862675067</v>
+        <v>274.5699999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004632e-08</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>84.45181317356524</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.295x + -20123.388</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-20123.38766908173</v>
       </c>
       <c r="Y12" t="n">
         <v>6.206565981022582e-14</v>
       </c>
       <c r="Z12" t="n">
-        <v>2240.091406700813</v>
+        <v>270.4099999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>84.47601219736865</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 10.340x + -20061.183</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-20061.183436252</v>
       </c>
       <c r="Y13" t="n">
         <v>1.002991068050196e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2222.104134904337</v>
+        <v>262.7</v>
       </c>
       <c r="AA13" t="n">
         <v>1.00000000000118e-08</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>84.29369569325458</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 10.008x + -19212.895</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-19212.8954625368</v>
       </c>
       <c r="Y14" t="n">
         <v>6.037389633769716e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>2204.560726432944</v>
+        <v>262.8500000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.00000000000048e-08</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>84.55171167265325</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 10.485x + -20039.837</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-20039.83720390238</v>
       </c>
       <c r="Y15" t="n">
         <v>2.89597990234963e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2186.438826776923</v>
+        <v>250.9400000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>84.57235353542768</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 10.525x + -19962.328</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-19962.32828533247</v>
       </c>
       <c r="Y16" t="n">
         <v>3.88081800803275e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2168.44960213808</v>
+        <v>246.79</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000814e-08</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>84.58906510992153</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 10.557x + -19870.824</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-19870.82377851203</v>
       </c>
       <c r="Y17" t="n">
         <v>1.394618212055567e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>2150.697390267059</v>
+        <v>243.71</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000105e-08</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>84.61605159952668</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 10.611x + -19817.718</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-19817.71831674836</v>
       </c>
       <c r="Y18" t="n">
         <v>3.780509939592464e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>2132.505116102536</v>
+        <v>236.8999999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000376e-08</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>84.63667721716214</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.652x + -19731.541</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-19731.54103314185</v>
       </c>
       <c r="Y19" t="n">
         <v>1.256970417595998e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2114.301664692274</v>
+        <v>231.95</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000429e-08</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>84.65233205633582</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 10.683x + -19632.737</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-19632.73673105193</v>
       </c>
       <c r="Y20" t="n">
         <v>2.1907409611764e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>2096.065770975982</v>
+        <v>229.98</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000033e-08</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>84.44383619669455</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 10.280x + -18671.840</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-18671.83959492642</v>
       </c>
       <c r="Y21" t="n">
         <v>3.196065742501888e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2077.467099719895</v>
+        <v>228.5699999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1.00000000000388e-08</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>84.72507677859303</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 10.831x + -19571.366</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-19571.3656559198</v>
       </c>
       <c r="Y22" t="n">
         <v>1.672082578549202e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2057.764452642697</v>
+        <v>221.3499999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.00000000000319e-08</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-367.96</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.50243e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-59.666</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6308123249299794</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8008349389851893</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.409814612868113</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.320956086714828</v>
+      </c>
+      <c r="J2" t="n">
+        <v>37.8542682315176</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.69378511491739</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.049x + -21891.960</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-21891.96037960164</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.138344611660326e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>367.96</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000902e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8170672020976124</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-334.3999999999996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.5758e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-61.235</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07142857142857578</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6799620733249256</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.39320882852295</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.955216360403119</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.64267270908129</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.90657962404948</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 9.367x + -21436.881</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-21436.88077054089</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.754115348614548e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>334.3999999999996</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000166e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8174320846404626</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-336.02</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.59576e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-61.74</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1773462783171516</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1726147123088067</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.030661040787675</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.448363774733604</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.35448719668512</v>
+      </c>
+      <c r="K4" t="n">
+        <v>83.72045429682552</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 9.088x + -20318.601</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20318.60135010019</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.478673788885344e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>336.02</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8175336911349108</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-326.52</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.61069e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.122</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0001312335958140222</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2058171745152704</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.020588235294137</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.592317380352629</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.95135763101045</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83.81604540887508</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 9.229x + -20376.437</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20376.43661082203</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.20139928796489e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>326.52</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8176155112344339</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-329.3499999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.62175e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-62.422</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2835185185185199</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5346425765907309</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.471122011036214</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.66740806818526</v>
+      </c>
+      <c r="K6" t="n">
+        <v>83.59765404793657</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 8.912x + -19387.001</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19387.00131202219</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.883837761576438e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>329.3499999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8177240154395706</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-308.3299999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.63351e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-62.698</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6456140350876758</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7490399999999865</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.273733255678555</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.79906976744186</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.01772231390578</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.23216218771115</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 9.900x + -21490.539</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21490.53898041881</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.319542082488493e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>308.3299999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.817867089439878</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-314.73</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.64473e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.988</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1241184767277723</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7013468013468027</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.102117863720142</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.311625460284108</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17.18478488349748</v>
+      </c>
+      <c r="K8" t="n">
+        <v>83.75423241396796</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 9.137x + -19499.414</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-19499.41387650481</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.56028147395294e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>314.73</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8180365574728585</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-300.3899999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.65448e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.265</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4072765072764948</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6350114416475688</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9334174022698225</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.783826164874576</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.84578478440752</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.10581044209108</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 9.686x + -20565.567</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20565.56710754223</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.345642398065806e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>300.3899999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8182333383683441</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-291.3599999999997</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.66297e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-63.482</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4011916583912551</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8661403508771675</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.464665911664746</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.149415692821335</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.29046946008798</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.41428634945154</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 10.225x + -21605.808</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21605.80827750863</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.392507189518107e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>291.3599999999997</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8184443633002594</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-297.77</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.67271e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.731</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1878357030015745</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2349502487562166</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.019274809160269</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.174963890226261</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.13966724688534</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.91441608444889</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 9.380x + -19503.037</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-19503.03704594555</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.263849689963189e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>297.77</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000078e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.818677322426041</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-287.3099999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.68187e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-63.946</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4053805774278482</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7264907135875026</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8819857312722535</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.777513464991051</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23.09239173394585</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.22814971961796</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 9.893x + -20471.950</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-20471.94954415383</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.502207539141519e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>287.3099999999999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8189065265328207</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-288.71</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.68934e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-64.187</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2354399008673988</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3663953488371757</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8065217391303824</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.23640948058495</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.63434081105737</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.01105019342835</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 9.532x + -19494.716</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19494.71640114519</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.665955034596872e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>288.71</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000002573e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8191680807773446</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-274.25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.6978e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-64.42100000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4467966573816213</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8425659472421455</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.106403940886703</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.749525101763896</v>
+      </c>
+      <c r="J14" t="n">
+        <v>23.38835407550272</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.33994571805323</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 10.090x + -20545.214</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-20545.21390106838</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.856140758154704e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>274.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8194266197450795</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-270.3899999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.70643e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-64.65300000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3699408284023595</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5475915221579801</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.117126269956377</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.736452328159637</v>
+      </c>
+      <c r="J15" t="n">
+        <v>23.89679150068261</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.33925983606377</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 10.089x + -20368.102</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-20368.10164579641</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>123.1584967167218</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>270.3899999999999</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.499795632128715e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.7988401975565512</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-262.9400000000003</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.71554e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-64.883</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5423475258918582</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4817153628652396</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.228179190751497</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.922355193872732</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24.14951231951334</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.40001111425599</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 10.199x + -20435.360</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-20435.36029162877</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5.137276585033875e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>262.9400000000003</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8199641689625303</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-258.71</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.72198e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-65.09399999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3480561555075393</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.003853564547159</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.428178963893274</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.765049415992795</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.39138543555431</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.43303214988309</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 10.260x + -20396.657</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-20396.65667646144</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.91240828538836e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>258.71</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000009001e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8202555761943258</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-254.1900000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.73004e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-65.322</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3170825335892302</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8773844641101496</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.395030581039688</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.791106993978688</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.88029530600378</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.46092811865101</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 10.312x + -20335.016</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-20335.01623703157</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.248311337201449e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>254.1900000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000003353e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.820535013514108</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-257.6599999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.73552e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-65.51300000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.07020602218699427</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7738624338625241</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9832000000000074</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.410034013605425</v>
+      </c>
+      <c r="J19" t="n">
+        <v>19.82829025316722</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.24472827825706</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 9.922x + -19346.806</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-19346.80571314451</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.615370707962783e-12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>257.6599999999999</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8208304562524634</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-253.1300000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.74227e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-65.73999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3252525252525371</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5628458498023391</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9610226320201497</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.318688901667636</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20.00447072950847</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.25427488926518</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 9.938x + -19225.547</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-19225.54669226714</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.920315953475424e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>253.1300000000001</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8211177620050742</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-247.51</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.7485e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-65.953</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.341711229946507</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3653618906942309</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.316479017400163</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.491004672897216</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20.19462359542494</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.30323224331785</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 10.024x + -19240.601</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-19240.60136413622</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4.015057859175186e-10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>247.51</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8214079875070345</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-243.05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.75752e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-66.152</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1740276035131765</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4865577889447271</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.266209081309417</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.667608545830489</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20.11115858716999</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.32978047774316</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 10.072x + -19177.581</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-19177.58072070149</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.770150961833606e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>243.05</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8217336582581808</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>80.46022753213575</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 5.950x + -16596.437</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-16596.43705457958</v>
       </c>
       <c r="Y2" t="n">
         <v>1.086883614155678e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3150.041474697055</v>
+        <v>642.1500000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002127e-08</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>82.29931049878363</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 7.395x + -18039.687</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-18039.68739839427</v>
       </c>
       <c r="Y3" t="n">
         <v>1.953758495807705e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2813.683736807206</v>
+        <v>473.1900000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000092e-08</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>83.12721420698479</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 8.297x + -19576.865</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-19576.86477097476</v>
       </c>
       <c r="Y4" t="n">
         <v>8.587305870153576e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2723.73192417196</v>
+        <v>404.27</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000007256e-08</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>83.82196546708683</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.238x + -21528.525</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21528.52451899476</v>
       </c>
       <c r="Y5" t="n">
         <v>1.017523991552934e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2674.843221352956</v>
+        <v>359.5299999999997</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000008e-08</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>83.17851291028614</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 8.360x + -18971.860</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-18971.86041012717</v>
       </c>
       <c r="Y6" t="n">
         <v>7.564685976818668e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2633.010412677293</v>
+        <v>366.6800000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000135e-08</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>83.90111205292037</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 9.359x + -21101.023</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21101.02260573204</v>
       </c>
       <c r="Y7" t="n">
         <v>7.699355603460853e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>2592.781821596367</v>
+        <v>336.4000000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>83.7154442810232</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.080x + -20113.860</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-20113.85998948934</v>
       </c>
       <c r="Y8" t="n">
         <v>2.600960766084204e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2554.027386601243</v>
+        <v>335.4899999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000001678e-08</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>83.85014603447942</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.281x + -20281.378</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20281.37775214522</v>
       </c>
       <c r="Y9" t="n">
         <v>2.421581870159603e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2516.5753119736</v>
+        <v>321.52</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000057e-08</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>84.21828066961335</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.876x + -21379.636</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21379.63591990633</v>
       </c>
       <c r="Y10" t="n">
         <v>1.339855109240715e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2480.550825597673</v>
+        <v>307.1000000000004</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>84.04447768895014</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 9.586x + -20420.200</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20420.19956460702</v>
       </c>
       <c r="Y11" t="n">
         <v>1.036382452996853e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2446.944159903048</v>
+        <v>305.1800000000003</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>83.16577915132731</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.344x + -19828.458</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-19828.45798244592</v>
       </c>
       <c r="Y2" t="n">
         <v>2.542881904764241e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2701.831590606215</v>
+        <v>414.4500000000003</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000112e-08</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>83.62452825045602</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 8.950x + -20067.307</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-20067.30724886391</v>
       </c>
       <c r="Y3" t="n">
         <v>1.142657200067725e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2583.229542437809</v>
+        <v>342.4899999999998</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000002826e-08</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>83.83055126744466</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.251x + -20370.423</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20370.42307694079</v>
       </c>
       <c r="Y4" t="n">
         <v>1.025575325807361e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2538.714699164927</v>
+        <v>326.6300000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001918e-08</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>83.9650348185034</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.459x + -20597.931</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20597.93088147454</v>
       </c>
       <c r="Y5" t="n">
         <v>3.135952387318772e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>2507.926963519586</v>
+        <v>320.5900000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000226e-08</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>83.77616862547849</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.170x + -19693.177</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19693.17686534335</v>
       </c>
       <c r="Y6" t="n">
         <v>1.115334331640313e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2480.208714911109</v>
+        <v>322.96</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000002e-08</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>83.87018936677882</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 9.311x + -19793.929</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-19793.92875758646</v>
       </c>
       <c r="Y7" t="n">
         <v>1.497925975947455e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2452.968327995208</v>
+        <v>311.4599999999996</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>84.21531341296713</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.871x + -20864.349</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-20864.34924827407</v>
       </c>
       <c r="Y8" t="n">
         <v>2.759762479546224e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2427.61287404634</v>
+        <v>302.3600000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000017e-08</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>84.32075407376576</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.056x + -21066.680</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21066.67986262115</v>
       </c>
       <c r="Y9" t="n">
         <v>2.784359300133081e-13</v>
       </c>
       <c r="Z9" t="n">
-        <v>2403.38300821044</v>
+        <v>298.0699999999997</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>84.10431499623327</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.684x + -20034.878</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20034.87837944888</v>
       </c>
       <c r="Y10" t="n">
         <v>1.268957503321733e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2380.142599188782</v>
+        <v>301.3700000000003</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000081e-08</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>84.39459888704101</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.189x + -20962.993</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20962.99332618411</v>
       </c>
       <c r="Y11" t="n">
         <v>3.243229995285135e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2357.842904353146</v>
+        <v>288.0599999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000188e-08</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>84.48819197142076</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.363x + -21147.042</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-21147.04181470851</v>
       </c>
       <c r="Y12" t="n">
         <v>4.786353359074191e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2336.549176340451</v>
+        <v>281.74</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>84.27667473740605</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 9.978x + -20121.952</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-20121.95237616786</v>
       </c>
       <c r="Y13" t="n">
         <v>1.320292495968892e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2315.660692212417</v>
+        <v>286.6199999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000522e-08</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>84.06863647500586</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 9.625x + -19184.507</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-19184.5073901818</v>
       </c>
       <c r="Y14" t="n">
         <v>2.650732854260847e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>2295.033058050712</v>
+        <v>284.7200000000003</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000036e-08</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>84.12331800311765</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 9.715x + -19215.074</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-19215.07432547842</v>
       </c>
       <c r="Y15" t="n">
         <v>4.267501041664768e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2275.765793905397</v>
+        <v>282.23</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000099e-08</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>84.66097067907468</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 10.700x + -21160.371</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-21160.37137131668</v>
       </c>
       <c r="Y16" t="n">
         <v>1.791518274147209e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>2257.770160290217</v>
+        <v>265.97</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>84.46436919022685</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 10.318x + -20173.417</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-20173.41678449231</v>
       </c>
       <c r="Y17" t="n">
         <v>1.177594460518473e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>2238.235005567555</v>
+        <v>270.3299999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>84.24640570436796</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 9.925x + -19172.143</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-19172.14252275833</v>
       </c>
       <c r="Y18" t="n">
         <v>1.620803406553089e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>2218.787863907711</v>
+        <v>269.1999999999998</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000045e-08</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>84.54828666484978</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.478x + -20148.074</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-20148.07418397862</v>
       </c>
       <c r="Y19" t="n">
         <v>6.872725503930049e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>2199.060141569402</v>
+        <v>259.6100000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000183e-08</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>84.34739039629048</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 10.103x + -19204.153</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-19204.15331752017</v>
       </c>
       <c r="Y20" t="n">
         <v>1.781154353761066e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2179.398350205155</v>
+        <v>262.8900000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000542e-08</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>84.88351923064154</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 11.168x + -21202.283</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-21202.28289242541</v>
       </c>
       <c r="Y21" t="n">
         <v>2.550094168873597e-14</v>
       </c>
       <c r="Z21" t="n">
-        <v>2159.728236925961</v>
+        <v>243.7900000000002</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>84.6600940446538</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 10.699x + -20063.871</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-20063.87136094583</v>
       </c>
       <c r="Y22" t="n">
         <v>2.459649451401785e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2139.959100126716</v>
+        <v>246.6500000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000251e-08</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>81.36431841194489</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 6.584x + -17992.938</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-17992.93817047779</v>
       </c>
       <c r="Y2" t="n">
         <v>3.425309557383945e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3081.059801711274</v>
+        <v>590.0200000000004</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003688e-08</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>83.19487280191028</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 8.380x + -20013.350</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-20013.35023767647</v>
       </c>
       <c r="Y3" t="n">
         <v>1.450349800561396e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2745.301739067062</v>
+        <v>411.4200000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000679e-08</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>83.52017807525401</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 8.804x + -20223.327</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20223.32743608797</v>
       </c>
       <c r="Y4" t="n">
         <v>7.69938379951708e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2654.604223475348</v>
+        <v>362.29</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000151e-08</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>84.02204049867409</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.550x + -21617.461</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21617.461420332</v>
       </c>
       <c r="Y5" t="n">
         <v>5.323591914397955e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2605.064474555924</v>
+        <v>335.2199999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>83.90344003211119</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.363x + -20812.288</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20812.28805137096</v>
       </c>
       <c r="Y6" t="n">
         <v>1.962429432940161e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2564.296362406016</v>
+        <v>328.71</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000014483e-08</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>84.28566690441858</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 9.993x + -21994.796</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21994.79614495493</v>
       </c>
       <c r="Y7" t="n">
         <v>2.776885641637098e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2526.265882645215</v>
+        <v>311.1500000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>84.11994026873391</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.710x + -21017.875</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21017.87469777355</v>
       </c>
       <c r="Y8" t="n">
         <v>2.476418874005884e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2490.742438648057</v>
+        <v>312.0499999999997</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000003e-08</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>84.20785551503312</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.858x + -21064.627</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21064.62675204686</v>
       </c>
       <c r="Y9" t="n">
         <v>1.723600175702745e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2456.832642935767</v>
+        <v>303.1699999999996</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000026e-08</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>84.25992660385282</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.948x + -20997.092</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20997.09228365609</v>
       </c>
       <c r="Y10" t="n">
         <v>1.065434141302727e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2424.319554397909</v>
+        <v>294.6900000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002584e-08</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>84.35980011485024</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.126x + -21129.257</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-21129.25677728041</v>
       </c>
       <c r="Y11" t="n">
         <v>5.320895351229182e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2394.173291675013</v>
+        <v>285.3699999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000006275e-08</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>83.37913450888188</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.615x + -20573.544</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-20573.54412001033</v>
       </c>
       <c r="Y2" t="n">
         <v>1.170304303577866e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2723.277843501315</v>
+        <v>393.2799999999997</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000497e-08</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>83.61803513372645</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 8.941x + -19997.393</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-19997.39323335383</v>
       </c>
       <c r="Y3" t="n">
         <v>1.002591032092316e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2587.165441155724</v>
+        <v>343.8899999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>84.03481165514242</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.570x + -21071.539</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-21071.5388380355</v>
       </c>
       <c r="Y4" t="n">
         <v>7.571592674941024e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2538.874834447206</v>
+        <v>325.8600000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000225e-08</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>84.42708391190912</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.249x + -22371.364</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-22371.36367057697</v>
       </c>
       <c r="Y5" t="n">
         <v>4.812708811615704e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>2504.426155924969</v>
+        <v>310.21</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>84.23096453301466</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.898x + -21292.767</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-21292.76737316284</v>
       </c>
       <c r="Y6" t="n">
         <v>1.394252693007735e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2476.020271105374</v>
+        <v>311.8700000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000113e-08</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>84.31447045918324</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.044x + -21420.927</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21420.92662160226</v>
       </c>
       <c r="Y7" t="n">
         <v>1.546173903231464e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2453.672192265043</v>
+        <v>307.25</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003121e-08</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>84.38940004641381</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.179x + -21544.927</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21544.92691483485</v>
       </c>
       <c r="Y8" t="n">
         <v>1.426944024014158e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2433.13047114036</v>
+        <v>299.0799999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000092e-08</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>84.44831367860151</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.288x + -21613.733</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21613.73295523469</v>
       </c>
       <c r="Y9" t="n">
         <v>1.16263633443452e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>2413.248949911742</v>
+        <v>293.9299999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>84.46216642747328</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 10.314x + -21505.441</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21505.44090915568</v>
       </c>
       <c r="Y10" t="n">
         <v>2.345472417549289e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2393.858602499464</v>
+        <v>291.79</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000104e-08</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>84.28096502357302</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 9.985x + -20594.971</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20594.97147993325</v>
       </c>
       <c r="Y11" t="n">
         <v>4.825886906986223e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2374.418761341155</v>
+        <v>291.6300000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000557e-08</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>84.56837519777463</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.517x + -21599.756</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-21599.7562513388</v>
       </c>
       <c r="Y12" t="n">
         <v>1.372774734725803e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2355.567641591116</v>
+        <v>278.5899999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000031e-08</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>84.37076751565644</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 10.145x + -20608.624</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-20608.62393983498</v>
       </c>
       <c r="Y13" t="n">
         <v>1.190584146090764e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2336.211412167455</v>
+        <v>281.52</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000008e-08</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>84.43795714968284</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 10.269x + -20706.392</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-20706.39173097324</v>
       </c>
       <c r="Y14" t="n">
         <v>1.357878013934101e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2316.517725308374</v>
+        <v>275.8000000000002</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000188e-08</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>84.72405089865927</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 10.829x + -21745.415</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-21745.41487247886</v>
       </c>
       <c r="Y15" t="n">
         <v>2.443108879293533e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2297.117218662236</v>
+        <v>265.1400000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000011993e-08</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>84.27659453564172</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 9.977x + -19745.063</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-19745.06294729883</v>
       </c>
       <c r="Y16" t="n">
         <v>1.511004981708023e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2277.833135732118</v>
+        <v>275.5100000000002</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000151e-08</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>84.286649382455</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 9.995x + -19617.170</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-19617.17045832672</v>
       </c>
       <c r="Y17" t="n">
         <v>9.522623202295483e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2258.148620359526</v>
+        <v>268.5599999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000002555e-08</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>84.82944702206727</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 11.051x + -21663.669</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-21663.66872149138</v>
       </c>
       <c r="Y18" t="n">
         <v>2.960059470758436e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>2238.379325004129</v>
+        <v>253.3800000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000034e-08</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>84.40794136611431</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.213x + -19724.611</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-19724.6107521858</v>
       </c>
       <c r="Y19" t="n">
         <v>6.969591339762135e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>2218.255854321172</v>
+        <v>261.4500000000003</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000024667e-08</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>84.19932005317142</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 9.844x + -18794.789</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-18794.78887703615</v>
       </c>
       <c r="Y20" t="n">
         <v>7.390666689570101e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2198.118659851394</v>
+        <v>266.0900000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000002782e-08</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>84.66776912249384</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 10.714x + -20401.189</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-20401.18930379382</v>
       </c>
       <c r="Y21" t="n">
         <v>3.62735696975217e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>2177.562979443003</v>
+        <v>248.9100000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>84.95685930851931</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 11.332x + -21468.212</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-21468.21191511771</v>
       </c>
       <c r="Y22" t="n">
         <v>5.714803429648379e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2157.333272256946</v>
+        <v>233.4300000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000121306e-08</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>80.51210212876322</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 5.984x + -15874.346</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-15874.34624754627</v>
       </c>
       <c r="Y2" t="n">
         <v>1.72998546983139e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2993.862111401536</v>
+        <v>634.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000031e-08</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>82.8008771632378</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 7.917x + -18389.017</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-18389.01727795352</v>
       </c>
       <c r="Y3" t="n">
         <v>6.672037935581266e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2676.007602567666</v>
+        <v>437.3099999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000011993e-08</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>83.800322581817</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.206x + -20764.144</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20764.14428771099</v>
       </c>
       <c r="Y4" t="n">
         <v>1.209362632440205e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2592.350911856874</v>
+        <v>366.48</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000015e-08</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>83.56031029996976</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 8.860x + -19510.069</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-19510.06915356576</v>
       </c>
       <c r="Y5" t="n">
         <v>2.827790617756636e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>2547.892585559964</v>
+        <v>355.9099999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>84.23501132711984</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 9.905x + -21674.404</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-21674.40370160397</v>
       </c>
       <c r="Y6" t="n">
         <v>6.462583577566745e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2510.960577695527</v>
+        <v>324.8700000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000026449e-08</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>84.10817881209063</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 9.690x + -20864.734</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-20864.73366181109</v>
       </c>
       <c r="Y7" t="n">
         <v>2.024751398629683e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2476.289429560517</v>
+        <v>327.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000002e-08</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>84.23032734038878</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.897x + -21043.623</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21043.62329328149</v>
       </c>
       <c r="Y8" t="n">
         <v>1.065073969227068e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2443.014271513823</v>
+        <v>315.5099999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000303e-08</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>84.28896888205668</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.999x + -20996.501</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20996.50124691442</v>
       </c>
       <c r="Y9" t="n">
         <v>7.25785676806503e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>2410.64347555354</v>
+        <v>302.6999999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001071e-08</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>84.36956451087175</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 10.143x + -21047.239</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21047.23939884337</v>
       </c>
       <c r="Y10" t="n">
         <v>9.595270494357625e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2379.623915660651</v>
+        <v>296.3499999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000808e-08</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>84.47507958186047</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.338x + -21213.489</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-21213.48890531447</v>
       </c>
       <c r="Y11" t="n">
         <v>2.211286328280494e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2350.232133890175</v>
+        <v>284.1400000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000597e-08</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>83.5543991192702</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.852x + -19952.424</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-19952.42369852823</v>
       </c>
       <c r="Y2" t="n">
         <v>2.001749904773327e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2576.472967375066</v>
+        <v>359.3999999999996</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000005e-08</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>84.08925682497375</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.659x + -20793.571</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-20793.57053931227</v>
       </c>
       <c r="Y3" t="n">
         <v>2.250707467516904e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2473.10513730076</v>
+        <v>316.77</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000003e-08</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>84.21018159591914</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.862x + -20881.196</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20881.19554562695</v>
       </c>
       <c r="Y4" t="n">
         <v>1.719296877167754e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2432.704602150638</v>
+        <v>305.9499999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>84.0573327975454</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.607x + -20031.476</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-20031.4761887961</v>
       </c>
       <c r="Y5" t="n">
         <v>3.869679054820073e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2401.39949751879</v>
+        <v>310.9699999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000015e-08</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>84.34704382289181</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.103x + -20899.763</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20899.76336249191</v>
       </c>
       <c r="Y6" t="n">
         <v>1.458778026601151e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2372.219847912399</v>
+        <v>298.3000000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000017e-08</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>84.43734079830348</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.268x + -21030.504</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21030.50437148828</v>
       </c>
       <c r="Y7" t="n">
         <v>1.099135095323489e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2346.14593972893</v>
+        <v>291.53</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000009e-08</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>83.99080242413268</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 9.500x + -19138.339</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-19138.33906001406</v>
       </c>
       <c r="Y8" t="n">
         <v>6.029933164846459e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2322.046114774923</v>
+        <v>295.6199999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000007e-08</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>84.51384114708173</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.412x + -20923.408</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20923.40766616633</v>
       </c>
       <c r="Y9" t="n">
         <v>7.119070493671383e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>2299.791109757578</v>
+        <v>277.3899999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>84.32091260584585</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 10.056x + -19972.246</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19972.2463116406</v>
       </c>
       <c r="Y10" t="n">
         <v>4.002957545166091e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2279.53393126862</v>
+        <v>280.5899999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>84.14704381011862</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 9.755x + -19163.824</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-19163.82370747895</v>
       </c>
       <c r="Y11" t="n">
         <v>4.876029599413158e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2259.616609348771</v>
+        <v>278.5300000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000033e-08</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>84.40980167338525</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.217x + -19974.308</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-19974.30768321452</v>
       </c>
       <c r="Y12" t="n">
         <v>5.652424625790092e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2240.029239039912</v>
+        <v>272.1799999999998</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000876e-08</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>84.21281745699126</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 9.867x + -19071.302</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19071.30151111697</v>
       </c>
       <c r="Y13" t="n">
         <v>4.405646836199243e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2220.45164926095</v>
+        <v>268.0200000000002</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000038715e-08</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>84.26872441677907</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 9.964x + -19107.991</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-19107.99141286724</v>
       </c>
       <c r="Y14" t="n">
         <v>6.68519159908061e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2201.364861816771</v>
+        <v>263.23</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000046e-08</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>84.27469124761832</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 9.974x + -18975.231</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-18975.23095006755</v>
       </c>
       <c r="Y15" t="n">
         <v>2.309785625433233e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2182.479627035726</v>
+        <v>256.96</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>84.28098358509754</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 9.985x + -18841.880</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-18841.88034951055</v>
       </c>
       <c r="Y16" t="n">
         <v>3.073822070376296e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2164.218695951675</v>
+        <v>252.7500000000002</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000098e-08</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>84.58584851380431</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 10.551x + -19826.849</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-19826.84922533125</v>
       </c>
       <c r="Y17" t="n">
         <v>3.613226763162385e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>2145.953973210237</v>
+        <v>242.3899999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000002e-08</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>84.33590775682683</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 10.083x + -18725.292</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-18725.29177948506</v>
       </c>
       <c r="Y18" t="n">
         <v>6.620729427644264e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>2127.456486914492</v>
+        <v>241.3600000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000000006e-08</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>84.8472275073682</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 11.089x + -20569.156</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-20569.15604088516</v>
       </c>
       <c r="Y19" t="n">
         <v>5.46674741496479e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2109.284482831431</v>
+        <v>228.4099999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000001002e-08</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>84.3718801124962</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 10.148x + -18543.725</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-18543.72508123181</v>
       </c>
       <c r="Y20" t="n">
         <v>1.522106775312913e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2091.518776425849</v>
+        <v>232.3</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>84.41751953333907</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 10.231x + -18551.967</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-18551.96748768415</v>
       </c>
       <c r="Y21" t="n">
         <v>1.055729918591458e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2073.324016333495</v>
+        <v>229.6000000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000001e-08</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>84.674206150773</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 10.727x + -19356.706</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-19356.70630630733</v>
       </c>
       <c r="Y22" t="n">
         <v>5.08786599857168e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>2054.917622897904</v>
+        <v>218.1800000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000043e-08</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>81.94691809876741</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.068x + -15811.897</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-15811.89697297614</v>
       </c>
       <c r="Y2" t="n">
         <v>1.790087011635379e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2451.890993791166</v>
+        <v>537.3899999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000365e-08</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>83.70293679891785</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.062x + -17208.840</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-17208.84006990088</v>
       </c>
       <c r="Y3" t="n">
         <v>9.976602508334061e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2154.014554009581</v>
+        <v>354.3599999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000007021e-08</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>84.20803156131308</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.859x + -18040.811</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-18040.81103764051</v>
       </c>
       <c r="Y4" t="n">
         <v>3.664386647689722e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2082.038696500387</v>
+        <v>304.6500000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>84.22866483204541</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 9.894x + -17730.187</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-17730.1866662091</v>
       </c>
       <c r="Y5" t="n">
         <v>1.107602193868262e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>2044.046495209578</v>
+        <v>290.28</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001067e-08</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>84.32231179456203</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.058x + -17767.150</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-17767.14966146949</v>
       </c>
       <c r="Y6" t="n">
         <v>4.054403846345418e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2012.678866720348</v>
+        <v>280.4200000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000221e-08</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>84.40353029469115</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.205x + -17781.512</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-17781.51214802358</v>
       </c>
       <c r="Y7" t="n">
         <v>3.114979369353384e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>1982.892256509418</v>
+        <v>268.8299999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000158e-08</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>84.31086005262659</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.038x + -17207.218</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17207.21778862729</v>
       </c>
       <c r="Y8" t="n">
         <v>1.418852326674026e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1953.937251649365</v>
+        <v>266.1499999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000006949e-08</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>84.39118073912169</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.183x + -17229.113</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-17229.11253867616</v>
       </c>
       <c r="Y9" t="n">
         <v>4.077135247975173e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>1925.844962918161</v>
+        <v>259.55</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000086e-08</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>84.81318980529782</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.016x + -18499.841</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-18499.84125285816</v>
       </c>
       <c r="Y10" t="n">
         <v>2.151239635401392e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>1898.99815532462</v>
+        <v>245.98</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000042839e-08</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>84.49627319990968</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.378x + -17120.933</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-17120.9332421032</v>
       </c>
       <c r="Y11" t="n">
         <v>9.579921850165052e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1873.937511008381</v>
+        <v>246.7399999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000042385e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>82.46736018888438</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.562x + -18797.531</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.562460989615774</v>
       </c>
       <c r="X2" t="n">
         <v>-18797.5310808025</v>
@@ -600,7 +598,7 @@
         <v>1.53059518513909e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>473.96</v>
+        <v>2849.137192048378</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000036296e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>83.19808207998913</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 8.384x + -19879.695</t>
-        </is>
+      <c r="W3" t="n">
+        <v>8.383864927548856</v>
       </c>
       <c r="X3" t="n">
         <v>-19879.69519812554</v>
@@ -652,7 +648,7 @@
         <v>1.268148809046955e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>401.3600000000001</v>
+        <v>2733.239153431004</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000004e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>83.53630557181546</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 8.827x + -20482.232</t>
-        </is>
+      <c r="W4" t="n">
+        <v>8.826610120665062</v>
       </c>
       <c r="X4" t="n">
         <v>-20482.23161651968</v>
@@ -704,7 +698,7 @@
         <v>1.069725929926401e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>372.9200000000001</v>
+        <v>2672.031911764515</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000046e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>83.73705993304102</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.112x + -20816.781</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.11191844502801</v>
       </c>
       <c r="X5" t="n">
         <v>-20816.7812114036</v>
@@ -756,7 +748,7 @@
         <v>1.033644803438425e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>359.3600000000001</v>
+        <v>2628.085206854489</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002743e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>83.54559931867567</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 8.839x + -19846.414</t>
-        </is>
+      <c r="W6" t="n">
+        <v>8.839428031437869</v>
       </c>
       <c r="X6" t="n">
         <v>-19846.41411952285</v>
@@ -808,7 +798,7 @@
         <v>9.25560870921364e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>355.1200000000003</v>
+        <v>2590.7180302887</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>83.67340039265403</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.019x + -20002.596</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.019494282363736</v>
       </c>
       <c r="X7" t="n">
         <v>-20002.59579901699</v>
@@ -860,7 +848,7 @@
         <v>2.987011567362903e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>342.6699999999996</v>
+        <v>2556.556331153966</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000002028e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>83.78452013252992</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.182x + -20126.953</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.182050498841342</v>
       </c>
       <c r="X8" t="n">
         <v>-20126.9531701673</v>
@@ -912,7 +898,7 @@
         <v>4.758849038161764e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>334.4399999999996</v>
+        <v>2524.069810098983</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000238e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>84.14860515850387</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.758x + -21226.347</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.757749909217273</v>
       </c>
       <c r="X9" t="n">
         <v>-21226.34727106131</v>
@@ -964,7 +948,7 @@
         <v>1.828193003699344e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>314.5099999999998</v>
+        <v>2493.646315708108</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000062e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>83.95881316459732</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.449x + -20264.892</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.449020328885336</v>
       </c>
       <c r="X10" t="n">
         <v>-20264.89165288859</v>
@@ -1016,7 +998,7 @@
         <v>1.146666063726302e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>321.2599999999998</v>
+        <v>2465.268795843359</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000018e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>84.03429603958867</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.569x + -20317.455</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.569462053909261</v>
       </c>
       <c r="X11" t="n">
         <v>-20317.45519032307</v>
@@ -1068,7 +1048,7 @@
         <v>2.047578772244435e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>314.0999999999999</v>
+        <v>2438.58882605475</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000001203e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>83.66871024912238</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.013x + -20428.708</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.012758108158772</v>
       </c>
       <c r="X2" t="n">
         <v>-20428.7082248694</v>
@@ -1266,7 +1244,7 @@
         <v>1.323747969975969e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>350.0300000000002</v>
+        <v>2586.84725592886</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000845e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>84.14594536917514</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.753x + -20994.100</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.753285492065807</v>
       </c>
       <c r="X3" t="n">
         <v>-20994.09988761647</v>
@@ -1318,7 +1294,7 @@
         <v>2.243424914054024e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>311.8800000000001</v>
+        <v>2472.02471984687</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001272e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>84.25946863714121</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.947x + -21042.937</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.947499738827316</v>
       </c>
       <c r="X4" t="n">
         <v>-21042.93744743958</v>
@@ -1370,7 +1344,7 @@
         <v>3.487304966651269e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>302.9500000000003</v>
+        <v>2429.667557780532</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000008256e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>84.35350925532681</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.114x + -21143.332</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.11427715715188</v>
       </c>
       <c r="X5" t="n">
         <v>-21143.3318205291</v>
@@ -1422,7 +1394,7 @@
         <v>2.412624397153866e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>301.46</v>
+        <v>2398.365200523783</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002506e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>84.16583802044572</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.787x + -20152.544</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.786773295977596</v>
       </c>
       <c r="X6" t="n">
         <v>-20152.54411207497</v>
@@ -1474,7 +1444,7 @@
         <v>6.487790344343117e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>302.26</v>
+        <v>2369.019706315526</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000115e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>84.46460540010293</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.319x + -21099.596</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.31857941040324</v>
       </c>
       <c r="X7" t="n">
         <v>-21099.59584119752</v>
@@ -1526,7 +1494,7 @@
         <v>3.122977023555733e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>285.9899999999998</v>
+        <v>2342.644976134678</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000048e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>84.51424850142372</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.413x + -21088.496</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.41253795957086</v>
       </c>
       <c r="X8" t="n">
         <v>-21088.49644340535</v>
@@ -1578,7 +1544,7 @@
         <v>4.234150516350621e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>281.4999999999998</v>
+        <v>2318.814309752132</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000076e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>84.3479571801164</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.104x + -20220.069</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.10427711767442</v>
       </c>
       <c r="X9" t="n">
         <v>-20220.06887163307</v>
@@ -1630,7 +1594,7 @@
         <v>8.632902926560166e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>284.3100000000002</v>
+        <v>2297.196617573889</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000877e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>84.39902851910159</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.197x + -20248.027</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.19700866891676</v>
       </c>
       <c r="X10" t="n">
         <v>-20248.02688448182</v>
@@ -1682,7 +1644,7 @@
         <v>4.828493312931939e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>274.7</v>
+        <v>2277.325681088746</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>84.39091253370604</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.182x + -20050.911</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.18215977337713</v>
       </c>
       <c r="X11" t="n">
         <v>-20050.91065421495</v>
@@ -1734,7 +1694,7 @@
         <v>2.122233241569001e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>274.5699999999999</v>
+        <v>2258.278862675067</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004632e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>84.45181317356524</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.295x + -20123.388</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.29463942715375</v>
       </c>
       <c r="X12" t="n">
         <v>-20123.38766908173</v>
@@ -1786,7 +1744,7 @@
         <v>6.206565981022582e-14</v>
       </c>
       <c r="Z12" t="n">
-        <v>270.4099999999999</v>
+        <v>2240.091406700813</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>84.47601219736865</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 10.340x + -20061.183</t>
-        </is>
+      <c r="W13" t="n">
+        <v>10.34001985952958</v>
       </c>
       <c r="X13" t="n">
         <v>-20061.183436252</v>
@@ -1838,7 +1794,7 @@
         <v>1.002991068050196e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>262.7</v>
+        <v>2222.104134904337</v>
       </c>
       <c r="AA13" t="n">
         <v>1.00000000000118e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>84.29369569325458</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 10.008x + -19212.895</t>
-        </is>
+      <c r="W14" t="n">
+        <v>10.00756593942882</v>
       </c>
       <c r="X14" t="n">
         <v>-19212.8954625368</v>
@@ -1890,7 +1844,7 @@
         <v>6.037389633769716e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>262.8500000000001</v>
+        <v>2204.560726432944</v>
       </c>
       <c r="AA14" t="n">
         <v>1.00000000000048e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>84.55171167265325</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 10.485x + -20039.837</t>
-        </is>
+      <c r="W15" t="n">
+        <v>10.48457392029028</v>
       </c>
       <c r="X15" t="n">
         <v>-20039.83720390238</v>
@@ -1942,7 +1894,7 @@
         <v>2.89597990234963e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>250.9400000000001</v>
+        <v>2186.438826776923</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>84.57235353542768</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 10.525x + -19962.328</t>
-        </is>
+      <c r="W16" t="n">
+        <v>10.5246886907921</v>
       </c>
       <c r="X16" t="n">
         <v>-19962.32828533247</v>
@@ -1994,7 +1944,7 @@
         <v>3.88081800803275e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>246.79</v>
+        <v>2168.44960213808</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000814e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>84.58906510992153</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.557x + -19870.824</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.55738898223555</v>
       </c>
       <c r="X17" t="n">
         <v>-19870.82377851203</v>
@@ -2046,7 +1994,7 @@
         <v>1.394618212055567e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>243.71</v>
+        <v>2150.697390267059</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000105e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>84.61605159952668</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 10.611x + -19817.718</t>
-        </is>
+      <c r="W18" t="n">
+        <v>10.61062197453706</v>
       </c>
       <c r="X18" t="n">
         <v>-19817.71831674836</v>
@@ -2098,7 +2044,7 @@
         <v>3.780509939592464e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>236.8999999999999</v>
+        <v>2132.505116102536</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000376e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>84.63667721716214</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.652x + -19731.541</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.65166775410546</v>
       </c>
       <c r="X19" t="n">
         <v>-19731.54103314185</v>
@@ -2150,7 +2094,7 @@
         <v>1.256970417595998e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>231.95</v>
+        <v>2114.301664692274</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000429e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>84.65233205633582</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 10.683x + -19632.737</t>
-        </is>
+      <c r="W20" t="n">
+        <v>10.68303222944918</v>
       </c>
       <c r="X20" t="n">
         <v>-19632.73673105193</v>
@@ -2202,7 +2144,7 @@
         <v>2.1907409611764e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>229.98</v>
+        <v>2096.065770975982</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000033e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>84.44383619669455</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 10.280x + -18671.840</t>
-        </is>
+      <c r="W21" t="n">
+        <v>10.27976656123243</v>
       </c>
       <c r="X21" t="n">
         <v>-18671.83959492642</v>
@@ -2254,7 +2194,7 @@
         <v>3.196065742501888e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>228.5699999999999</v>
+        <v>2077.467099719895</v>
       </c>
       <c r="AA21" t="n">
         <v>1.00000000000388e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>84.72507677859303</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 10.831x + -19571.366</t>
-        </is>
+      <c r="W22" t="n">
+        <v>10.83121163249838</v>
       </c>
       <c r="X22" t="n">
         <v>-19571.3656559198</v>
@@ -2306,7 +2244,7 @@
         <v>1.672082578549202e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>221.3499999999999</v>
+        <v>2057.764452642697</v>
       </c>
       <c r="AA22" t="n">
         <v>1.00000000000319e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>83.69378511491739</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.049x + -21891.960</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.048887585791975</v>
       </c>
       <c r="X2" t="n">
         <v>-21891.96037960164</v>
@@ -2504,7 +2440,7 @@
         <v>8.138344611660326e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>367.96</v>
+        <v>2752.842315600089</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000902e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>83.90657962404948</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.367x + -21436.881</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.367416111232719</v>
       </c>
       <c r="X3" t="n">
         <v>-21436.88077054089</v>
@@ -2556,7 +2490,7 @@
         <v>5.754115348614548e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>334.3999999999996</v>
+        <v>2628.283211287756</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000166e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>83.72045429682552</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.088x + -20318.601</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.087629611191723</v>
       </c>
       <c r="X4" t="n">
         <v>-20318.60135010019</v>
@@ -2608,7 +2540,7 @@
         <v>5.478673788885344e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>336.02</v>
+        <v>2579.531278787112</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000042e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>83.81604540887508</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.229x + -20376.437</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.229228137305199</v>
       </c>
       <c r="X5" t="n">
         <v>-20376.43661082203</v>
@@ -2660,7 +2590,7 @@
         <v>2.20139928796489e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>326.52</v>
+        <v>2544.806429736098</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000003e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>83.59765404793657</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 8.912x + -19387.001</t>
-        </is>
+      <c r="W6" t="n">
+        <v>8.911906799058885</v>
       </c>
       <c r="X6" t="n">
         <v>-19387.00131202219</v>
@@ -2712,7 +2640,7 @@
         <v>1.883837761576438e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>329.3499999999999</v>
+        <v>2514.833913368448</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000031e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>84.23216218771115</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.900x + -21490.539</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.900088279319178</v>
       </c>
       <c r="X7" t="n">
         <v>-21490.53898041881</v>
@@ -2764,7 +2690,7 @@
         <v>8.319542082488493e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>308.3299999999999</v>
+        <v>2488.611740322311</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000043e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>83.75423241396796</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.137x + -19499.414</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.137171693787529</v>
       </c>
       <c r="X8" t="n">
         <v>-19499.41387650481</v>
@@ -2816,7 +2740,7 @@
         <v>1.56028147395294e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>314.73</v>
+        <v>2463.0707411901</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>84.10581044209108</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.686x + -20565.567</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.686407016058292</v>
       </c>
       <c r="X9" t="n">
         <v>-20565.56710754223</v>
@@ -2868,7 +2790,7 @@
         <v>1.345642398065806e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>300.3899999999999</v>
+        <v>2439.317835678697</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>84.41428634945154</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.225x + -21605.808</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.22504062760255</v>
       </c>
       <c r="X10" t="n">
         <v>-21605.80827750863</v>
@@ -2920,7 +2840,7 @@
         <v>3.392507189518107e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>291.3599999999997</v>
+        <v>2416.275690543898</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000314e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>83.91441608444889</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.380x + -19503.037</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.379569993771415</v>
       </c>
       <c r="X11" t="n">
         <v>-19503.03704594555</v>
@@ -2972,7 +2890,7 @@
         <v>2.263849689963189e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>297.77</v>
+        <v>2394.38591193977</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000078e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>84.22814971961796</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 9.893x + -20471.950</t>
-        </is>
+      <c r="W12" t="n">
+        <v>9.893159213431094</v>
       </c>
       <c r="X12" t="n">
         <v>-20471.94954415383</v>
@@ -3024,7 +2940,7 @@
         <v>1.502207539141519e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>287.3099999999999</v>
+        <v>2372.78961248076</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000131e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>84.01105019342835</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 9.532x + -19494.716</t>
-        </is>
+      <c r="W13" t="n">
+        <v>9.532048261278273</v>
       </c>
       <c r="X13" t="n">
         <v>-19494.71640114519</v>
@@ -3076,7 +2990,7 @@
         <v>3.665955034596872e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>288.71</v>
+        <v>2351.856645666194</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000002573e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>84.33994571805323</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 10.090x + -20545.214</t>
-        </is>
+      <c r="W14" t="n">
+        <v>10.08988185607426</v>
       </c>
       <c r="X14" t="n">
         <v>-20545.21390106838</v>
@@ -3128,7 +3040,7 @@
         <v>6.856140758154704e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>274.25</v>
+        <v>2331.681342579034</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000002e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>84.33925983606377</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 10.089x + -20368.102</t>
-        </is>
+      <c r="W15" t="n">
+        <v>10.08865132786261</v>
       </c>
       <c r="X15" t="n">
         <v>-20368.10164579641</v>
@@ -3180,7 +3090,7 @@
         <v>123.1584967167218</v>
       </c>
       <c r="Z15" t="n">
-        <v>270.3899999999999</v>
+        <v>2420.312072086623</v>
       </c>
       <c r="AA15" t="n">
         <v>1.499795632128715e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>84.40001111425599</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 10.199x + -20435.360</t>
-        </is>
+      <c r="W16" t="n">
+        <v>10.19880932308978</v>
       </c>
       <c r="X16" t="n">
         <v>-20435.36029162877</v>
@@ -3232,7 +3140,7 @@
         <v>5.137276585033875e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>262.9400000000003</v>
+        <v>2291.385284074499</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000007e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>84.43303214988309</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.260x + -20396.657</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.25969044250655</v>
       </c>
       <c r="X17" t="n">
         <v>-20396.65667646144</v>
@@ -3284,7 +3190,7 @@
         <v>1.91240828538836e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>258.71</v>
+        <v>2272.177152141455</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000009001e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>84.46092811865101</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 10.312x + -20335.016</t>
-        </is>
+      <c r="W18" t="n">
+        <v>10.31168628116558</v>
       </c>
       <c r="X18" t="n">
         <v>-20335.01623703157</v>
@@ -3336,7 +3240,7 @@
         <v>3.248311337201449e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>254.1900000000001</v>
+        <v>2253.051247256828</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000003353e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>84.24472827825706</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 9.922x + -19346.806</t>
-        </is>
+      <c r="W19" t="n">
+        <v>9.921850754493514</v>
       </c>
       <c r="X19" t="n">
         <v>-19346.80571314451</v>
@@ -3388,7 +3290,7 @@
         <v>2.615370707962783e-12</v>
       </c>
       <c r="Z19" t="n">
-        <v>257.6599999999999</v>
+        <v>2234.039382056779</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>84.25427488926518</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 9.938x + -19225.547</t>
-        </is>
+      <c r="W20" t="n">
+        <v>9.938447384427251</v>
       </c>
       <c r="X20" t="n">
         <v>-19225.54669226714</v>
@@ -3440,7 +3340,7 @@
         <v>3.920315953475424e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>253.1300000000001</v>
+        <v>2215.098580596615</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000001e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>84.30323224331785</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 10.024x + -19240.601</t>
-        </is>
+      <c r="W21" t="n">
+        <v>10.02443008987026</v>
       </c>
       <c r="X21" t="n">
         <v>-19240.60136413622</v>
@@ -3492,7 +3390,7 @@
         <v>4.015057859175186e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>247.51</v>
+        <v>2196.289567146322</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000031e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>84.32978047774316</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 10.072x + -19177.581</t>
-        </is>
+      <c r="W22" t="n">
+        <v>10.0716749755915</v>
       </c>
       <c r="X22" t="n">
         <v>-19177.58072070149</v>
@@ -3544,7 +3440,7 @@
         <v>8.770150961833606e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>243.05</v>
+        <v>2177.645820512686</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000002e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>80.46022753213575</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 5.950x + -16596.437</t>
-        </is>
+      <c r="W2" t="n">
+        <v>5.95038716277577</v>
       </c>
       <c r="X2" t="n">
         <v>-16596.43705457958</v>
@@ -3742,7 +3636,7 @@
         <v>1.086883614155678e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>642.1500000000001</v>
+        <v>3150.041474697055</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002127e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>82.29931049878363</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 7.395x + -18039.687</t>
-        </is>
+      <c r="W3" t="n">
+        <v>7.395489235621429</v>
       </c>
       <c r="X3" t="n">
         <v>-18039.68739839427</v>
@@ -3794,7 +3686,7 @@
         <v>1.953758495807705e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>473.1900000000001</v>
+        <v>2813.683736807206</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000092e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>83.12721420698479</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 8.297x + -19576.865</t>
-        </is>
+      <c r="W4" t="n">
+        <v>8.296593855953182</v>
       </c>
       <c r="X4" t="n">
         <v>-19576.86477097476</v>
@@ -3846,7 +3736,7 @@
         <v>8.587305870153576e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>404.27</v>
+        <v>2723.73192417196</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000007256e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>83.82196546708683</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.238x + -21528.525</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.238141003488344</v>
       </c>
       <c r="X5" t="n">
         <v>-21528.52451899476</v>
@@ -3898,7 +3786,7 @@
         <v>1.017523991552934e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>359.5299999999997</v>
+        <v>2674.843221352956</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000008e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>83.17851291028614</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 8.360x + -18971.860</t>
-        </is>
+      <c r="W6" t="n">
+        <v>8.359585879488316</v>
       </c>
       <c r="X6" t="n">
         <v>-18971.86041012717</v>
@@ -3950,7 +3836,7 @@
         <v>7.564685976818668e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>366.6800000000003</v>
+        <v>2633.010412677293</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000135e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>83.90111205292037</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.359x + -21101.023</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.35895466280445</v>
       </c>
       <c r="X7" t="n">
         <v>-21101.02260573204</v>
@@ -4002,7 +3886,7 @@
         <v>7.699355603460853e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>336.4000000000001</v>
+        <v>2592.781821596367</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>83.7154442810232</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.080x + -20113.860</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.080326634656894</v>
       </c>
       <c r="X8" t="n">
         <v>-20113.85998948934</v>
@@ -4054,7 +3936,7 @@
         <v>2.600960766084204e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>335.4899999999998</v>
+        <v>2554.027386601243</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000001678e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>83.85014603447942</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.281x + -20281.378</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.28080222960611</v>
       </c>
       <c r="X9" t="n">
         <v>-20281.37775214522</v>
@@ -4106,7 +3986,7 @@
         <v>2.421581870159603e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>321.52</v>
+        <v>2516.5753119736</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000057e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>84.21828066961335</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.876x + -21379.636</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.876157291461302</v>
       </c>
       <c r="X10" t="n">
         <v>-21379.63591990633</v>
@@ -4158,7 +4036,7 @@
         <v>1.339855109240715e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>307.1000000000004</v>
+        <v>2480.550825597673</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>84.04447768895014</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.586x + -20420.200</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.585940889812488</v>
       </c>
       <c r="X11" t="n">
         <v>-20420.19956460702</v>
@@ -4210,7 +4086,7 @@
         <v>1.036382452996853e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>305.1800000000003</v>
+        <v>2446.944159903048</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>83.16577915132731</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.344x + -19828.458</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.343861700297175</v>
       </c>
       <c r="X2" t="n">
         <v>-19828.45798244592</v>
@@ -4408,7 +4282,7 @@
         <v>2.542881904764241e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>414.4500000000003</v>
+        <v>2701.831590606215</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000112e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>83.62452825045602</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 8.950x + -20067.307</t>
-        </is>
+      <c r="W3" t="n">
+        <v>8.949786582535486</v>
       </c>
       <c r="X3" t="n">
         <v>-20067.30724886391</v>
@@ -4460,7 +4332,7 @@
         <v>1.142657200067725e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>342.4899999999998</v>
+        <v>2583.229542437809</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000002826e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>83.83055126744466</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.251x + -20370.423</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.251097517588128</v>
       </c>
       <c r="X4" t="n">
         <v>-20370.42307694079</v>
@@ -4512,7 +4382,7 @@
         <v>1.025575325807361e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>326.6300000000001</v>
+        <v>2538.714699164927</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001918e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>83.9650348185034</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.459x + -20597.931</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.458834187049936</v>
       </c>
       <c r="X5" t="n">
         <v>-20597.93088147454</v>
@@ -4564,7 +4432,7 @@
         <v>3.135952387318772e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>320.5900000000001</v>
+        <v>2507.926963519586</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000226e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>83.77616862547849</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.170x + -19693.177</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.16963221561913</v>
       </c>
       <c r="X6" t="n">
         <v>-19693.17686534335</v>
@@ -4616,7 +4482,7 @@
         <v>1.115334331640313e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>322.96</v>
+        <v>2480.208714911109</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000002e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>83.87018936677882</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.311x + -19793.929</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.3113826683564</v>
       </c>
       <c r="X7" t="n">
         <v>-19793.92875758646</v>
@@ -4668,7 +4532,7 @@
         <v>1.497925975947455e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>311.4599999999996</v>
+        <v>2452.968327995208</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>84.21531341296713</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.871x + -20864.349</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.87105675004211</v>
       </c>
       <c r="X8" t="n">
         <v>-20864.34924827407</v>
@@ -4720,7 +4582,7 @@
         <v>2.759762479546224e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>302.3600000000001</v>
+        <v>2427.61287404634</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000017e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>84.32075407376576</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.056x + -21066.680</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.05556231047639</v>
       </c>
       <c r="X9" t="n">
         <v>-21066.67986262115</v>
@@ -4772,7 +4632,7 @@
         <v>2.784359300133081e-13</v>
       </c>
       <c r="Z9" t="n">
-        <v>298.0699999999997</v>
+        <v>2403.38300821044</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>84.10431499623327</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.684x + -20034.878</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.683932627429103</v>
       </c>
       <c r="X10" t="n">
         <v>-20034.87837944888</v>
@@ -4824,7 +4682,7 @@
         <v>1.268957503321733e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>301.3700000000003</v>
+        <v>2380.142599188782</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000081e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>84.39459888704101</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.189x + -20962.993</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.18889896208118</v>
       </c>
       <c r="X11" t="n">
         <v>-20962.99332618411</v>
@@ -4876,7 +4732,7 @@
         <v>3.243229995285135e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>288.0599999999999</v>
+        <v>2357.842904353146</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000188e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>84.48819197142076</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.363x + -21147.042</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.36301087432603</v>
       </c>
       <c r="X12" t="n">
         <v>-21147.04181470851</v>
@@ -4928,7 +4782,7 @@
         <v>4.786353359074191e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>281.74</v>
+        <v>2336.549176340451</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>84.27667473740605</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 9.978x + -20121.952</t>
-        </is>
+      <c r="W13" t="n">
+        <v>9.977605795602566</v>
       </c>
       <c r="X13" t="n">
         <v>-20121.95237616786</v>
@@ -4980,7 +4832,7 @@
         <v>1.320292495968892e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>286.6199999999999</v>
+        <v>2315.660692212417</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000522e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>84.06863647500586</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 9.625x + -19184.507</t>
-        </is>
+      <c r="W14" t="n">
+        <v>9.625267057910696</v>
       </c>
       <c r="X14" t="n">
         <v>-19184.5073901818</v>
@@ -5032,7 +4882,7 @@
         <v>2.650732854260847e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>284.7200000000003</v>
+        <v>2295.033058050712</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000036e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>84.12331800311765</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 9.715x + -19215.074</t>
-        </is>
+      <c r="W15" t="n">
+        <v>9.715468648422329</v>
       </c>
       <c r="X15" t="n">
         <v>-19215.07432547842</v>
@@ -5084,7 +4932,7 @@
         <v>4.267501041664768e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>282.23</v>
+        <v>2275.765793905397</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000099e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>84.66097067907468</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 10.700x + -21160.371</t>
-        </is>
+      <c r="W16" t="n">
+        <v>10.70041823531683</v>
       </c>
       <c r="X16" t="n">
         <v>-21160.37137131668</v>
@@ -5136,7 +4982,7 @@
         <v>1.791518274147209e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>265.97</v>
+        <v>2257.770160290217</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>84.46436919022685</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.318x + -20173.417</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.318136356421</v>
       </c>
       <c r="X17" t="n">
         <v>-20173.41678449231</v>
@@ -5188,7 +5032,7 @@
         <v>1.177594460518473e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>270.3299999999999</v>
+        <v>2238.235005567555</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>84.24640570436796</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 9.925x + -19172.143</t>
-        </is>
+      <c r="W18" t="n">
+        <v>9.924762957797471</v>
       </c>
       <c r="X18" t="n">
         <v>-19172.14252275833</v>
@@ -5240,7 +5082,7 @@
         <v>1.620803406553089e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>269.1999999999998</v>
+        <v>2218.787863907711</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000045e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>84.54828666484978</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.478x + -20148.074</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.47794715915338</v>
       </c>
       <c r="X19" t="n">
         <v>-20148.07418397862</v>
@@ -5292,7 +5132,7 @@
         <v>6.872725503930049e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>259.6100000000001</v>
+        <v>2199.060141569402</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000183e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>84.34739039629048</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 10.103x + -19204.153</t>
-        </is>
+      <c r="W20" t="n">
+        <v>10.1032573647088</v>
       </c>
       <c r="X20" t="n">
         <v>-19204.15331752017</v>
@@ -5344,7 +5182,7 @@
         <v>1.781154353761066e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>262.8900000000001</v>
+        <v>2179.398350205155</v>
       </c>
       <c r="AA20" t="n">
         <v>1.00000000000542e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>84.88351923064154</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 11.168x + -21202.283</t>
-        </is>
+      <c r="W21" t="n">
+        <v>11.16849675512312</v>
       </c>
       <c r="X21" t="n">
         <v>-21202.28289242541</v>
@@ -5396,7 +5232,7 @@
         <v>2.550094168873597e-14</v>
       </c>
       <c r="Z21" t="n">
-        <v>243.7900000000002</v>
+        <v>2159.728236925961</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>84.6600940446538</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 10.699x + -20063.871</t>
-        </is>
+      <c r="W22" t="n">
+        <v>10.69865137251171</v>
       </c>
       <c r="X22" t="n">
         <v>-20063.87136094583</v>
@@ -5448,7 +5282,7 @@
         <v>2.459649451401785e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>246.6500000000001</v>
+        <v>2139.959100126716</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000251e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>81.36431841194489</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 6.584x + -17992.938</t>
-        </is>
+      <c r="W2" t="n">
+        <v>6.584455517970201</v>
       </c>
       <c r="X2" t="n">
         <v>-17992.93817047779</v>
@@ -5646,7 +5478,7 @@
         <v>3.425309557383945e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>590.0200000000004</v>
+        <v>3081.059801711274</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003688e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>83.19487280191028</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 8.380x + -20013.350</t>
-        </is>
+      <c r="W3" t="n">
+        <v>8.379873718206376</v>
       </c>
       <c r="X3" t="n">
         <v>-20013.35023767647</v>
@@ -5698,7 +5528,7 @@
         <v>1.450349800561396e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>411.4200000000001</v>
+        <v>2745.301739067062</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000679e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>83.52017807525401</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 8.804x + -20223.327</t>
-        </is>
+      <c r="W4" t="n">
+        <v>8.804454013023333</v>
       </c>
       <c r="X4" t="n">
         <v>-20223.32743608797</v>
@@ -5750,7 +5578,7 @@
         <v>7.69938379951708e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>362.29</v>
+        <v>2654.604223475348</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000151e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>84.02204049867409</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.550x + -21617.461</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.549700837646792</v>
       </c>
       <c r="X5" t="n">
         <v>-21617.461420332</v>
@@ -5802,7 +5628,7 @@
         <v>5.323591914397955e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>335.2199999999998</v>
+        <v>2605.064474555924</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>83.90344003211119</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.363x + -20812.288</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.36255552498617</v>
       </c>
       <c r="X6" t="n">
         <v>-20812.28805137096</v>
@@ -5854,7 +5678,7 @@
         <v>1.962429432940161e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>328.71</v>
+        <v>2564.296362406016</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000014483e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>84.28566690441858</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.993x + -21994.796</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.993411567738487</v>
       </c>
       <c r="X7" t="n">
         <v>-21994.79614495493</v>
@@ -5906,7 +5728,7 @@
         <v>2.776885641637098e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>311.1500000000001</v>
+        <v>2526.265882645215</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>84.11994026873391</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.710x + -21017.875</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.709848360727335</v>
       </c>
       <c r="X8" t="n">
         <v>-21017.87469777355</v>
@@ -5958,7 +5778,7 @@
         <v>2.476418874005884e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>312.0499999999997</v>
+        <v>2490.742438648057</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000003e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>84.20785551503312</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.858x + -21064.627</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.858260053169104</v>
       </c>
       <c r="X9" t="n">
         <v>-21064.62675204686</v>
@@ -6010,7 +5828,7 @@
         <v>1.723600175702745e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>303.1699999999996</v>
+        <v>2456.832642935767</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000026e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>84.25992660385282</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.948x + -20997.092</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.948298727391515</v>
       </c>
       <c r="X10" t="n">
         <v>-20997.09228365609</v>
@@ -6062,7 +5878,7 @@
         <v>1.065434141302727e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>294.6900000000001</v>
+        <v>2424.319554397909</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002584e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>84.35980011485024</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.126x + -21129.257</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.1256315615637</v>
       </c>
       <c r="X11" t="n">
         <v>-21129.25677728041</v>
@@ -6114,7 +5928,7 @@
         <v>5.320895351229182e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>285.3699999999999</v>
+        <v>2394.173291675013</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000006275e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>83.37913450888188</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.615x + -20573.544</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.615267230236416</v>
       </c>
       <c r="X2" t="n">
         <v>-20573.54412001033</v>
@@ -6312,7 +6124,7 @@
         <v>1.170304303577866e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>393.2799999999997</v>
+        <v>2723.277843501315</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000497e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>83.61803513372645</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 8.941x + -19997.393</t>
-        </is>
+      <c r="W3" t="n">
+        <v>8.940605284051504</v>
       </c>
       <c r="X3" t="n">
         <v>-19997.39323335383</v>
@@ -6364,7 +6174,7 @@
         <v>1.002591032092316e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>343.8899999999999</v>
+        <v>2587.165441155724</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>84.03481165514242</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.570x + -21071.539</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.570295222025628</v>
       </c>
       <c r="X4" t="n">
         <v>-21071.5388380355</v>
@@ -6416,7 +6224,7 @@
         <v>7.571592674941024e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>325.8600000000001</v>
+        <v>2538.874834447206</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000225e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>84.42708391190912</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.249x + -22371.364</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.24867052647247</v>
       </c>
       <c r="X5" t="n">
         <v>-22371.36367057697</v>
@@ -6468,7 +6274,7 @@
         <v>4.812708811615704e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>310.21</v>
+        <v>2504.426155924969</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>84.23096453301466</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.898x + -21292.767</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.898019063200836</v>
       </c>
       <c r="X6" t="n">
         <v>-21292.76737316284</v>
@@ -6520,7 +6324,7 @@
         <v>1.394252693007735e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>311.8700000000003</v>
+        <v>2476.020271105374</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000113e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>84.31447045918324</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.044x + -21420.927</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.04437579204434</v>
       </c>
       <c r="X7" t="n">
         <v>-21420.92662160226</v>
@@ -6572,7 +6374,7 @@
         <v>1.546173903231464e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>307.25</v>
+        <v>2453.672192265043</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003121e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>84.38940004641381</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.179x + -21544.927</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.17939728111461</v>
       </c>
       <c r="X8" t="n">
         <v>-21544.92691483485</v>
@@ -6624,7 +6424,7 @@
         <v>1.426944024014158e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>299.0799999999999</v>
+        <v>2433.13047114036</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000092e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>84.44831367860151</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.288x + -21613.733</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.28810946404589</v>
       </c>
       <c r="X9" t="n">
         <v>-21613.73295523469</v>
@@ -6676,7 +6474,7 @@
         <v>1.16263633443452e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>293.9299999999998</v>
+        <v>2413.248949911742</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>84.46216642747328</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.314x + -21505.441</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.31400649386177</v>
       </c>
       <c r="X10" t="n">
         <v>-21505.44090915568</v>
@@ -6728,7 +6524,7 @@
         <v>2.345472417549289e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>291.79</v>
+        <v>2393.858602499464</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000104e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>84.28096502357302</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.985x + -20594.971</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.98514076686746</v>
       </c>
       <c r="X11" t="n">
         <v>-20594.97147993325</v>
@@ -6780,7 +6574,7 @@
         <v>4.825886906986223e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>291.6300000000001</v>
+        <v>2374.418761341155</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000557e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>84.56837519777463</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.517x + -21599.756</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.51693366235457</v>
       </c>
       <c r="X12" t="n">
         <v>-21599.7562513388</v>
@@ -6832,7 +6624,7 @@
         <v>1.372774734725803e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>278.5899999999999</v>
+        <v>2355.567641591116</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000031e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>84.37076751565644</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 10.145x + -20608.624</t>
-        </is>
+      <c r="W13" t="n">
+        <v>10.14548717122323</v>
       </c>
       <c r="X13" t="n">
         <v>-20608.62393983498</v>
@@ -6884,7 +6674,7 @@
         <v>1.190584146090764e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>281.52</v>
+        <v>2336.211412167455</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000008e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>84.43795714968284</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 10.269x + -20706.392</t>
-        </is>
+      <c r="W14" t="n">
+        <v>10.26883245204201</v>
       </c>
       <c r="X14" t="n">
         <v>-20706.39173097324</v>
@@ -6936,7 +6724,7 @@
         <v>1.357878013934101e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>275.8000000000002</v>
+        <v>2316.517725308374</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000188e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>84.72405089865927</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 10.829x + -21745.415</t>
-        </is>
+      <c r="W15" t="n">
+        <v>10.82909361263419</v>
       </c>
       <c r="X15" t="n">
         <v>-21745.41487247886</v>
@@ -6988,7 +6774,7 @@
         <v>2.443108879293533e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>265.1400000000001</v>
+        <v>2297.117218662236</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000011993e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>84.27659453564172</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 9.977x + -19745.063</t>
-        </is>
+      <c r="W16" t="n">
+        <v>9.977465045537503</v>
       </c>
       <c r="X16" t="n">
         <v>-19745.06294729883</v>
@@ -7040,7 +6824,7 @@
         <v>1.511004981708023e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>275.5100000000002</v>
+        <v>2277.833135732118</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000151e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>84.286649382455</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 9.995x + -19617.170</t>
-        </is>
+      <c r="W17" t="n">
+        <v>9.995141500560601</v>
       </c>
       <c r="X17" t="n">
         <v>-19617.17045832672</v>
@@ -7092,7 +6874,7 @@
         <v>9.522623202295483e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>268.5599999999999</v>
+        <v>2258.148620359526</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000002555e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>84.82944702206727</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 11.051x + -21663.669</t>
-        </is>
+      <c r="W18" t="n">
+        <v>11.05107317230602</v>
       </c>
       <c r="X18" t="n">
         <v>-21663.66872149138</v>
@@ -7144,7 +6924,7 @@
         <v>2.960059470758436e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>253.3800000000001</v>
+        <v>2238.379325004129</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000034e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>84.40794136611431</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.213x + -19724.611</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.21336499026455</v>
       </c>
       <c r="X19" t="n">
         <v>-19724.6107521858</v>
@@ -7196,7 +6974,7 @@
         <v>6.969591339762135e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>261.4500000000003</v>
+        <v>2218.255854321172</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000024667e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>84.19932005317142</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 9.844x + -18794.789</t>
-        </is>
+      <c r="W20" t="n">
+        <v>9.84365465197263</v>
       </c>
       <c r="X20" t="n">
         <v>-18794.78887703615</v>
@@ -7248,7 +7024,7 @@
         <v>7.390666689570101e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>266.0900000000001</v>
+        <v>2198.118659851394</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000002782e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>84.66776912249384</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 10.714x + -20401.189</t>
-        </is>
+      <c r="W21" t="n">
+        <v>10.71414021119617</v>
       </c>
       <c r="X21" t="n">
         <v>-20401.18930379382</v>
@@ -7300,7 +7074,7 @@
         <v>3.62735696975217e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>248.9100000000001</v>
+        <v>2177.562979443003</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>84.95685930851931</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.332x + -21468.212</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.3317755292129</v>
       </c>
       <c r="X22" t="n">
         <v>-21468.21191511771</v>
@@ -7352,7 +7124,7 @@
         <v>5.714803429648379e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>233.4300000000001</v>
+        <v>2157.333272256946</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000121306e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>80.51210212876322</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 5.984x + -15874.346</t>
-        </is>
+      <c r="W2" t="n">
+        <v>5.983528072630889</v>
       </c>
       <c r="X2" t="n">
         <v>-15874.34624754627</v>
@@ -7550,7 +7320,7 @@
         <v>1.72998546983139e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>634.5</v>
+        <v>2993.862111401536</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000031e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>82.8008771632378</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 7.917x + -18389.017</t>
-        </is>
+      <c r="W3" t="n">
+        <v>7.916789803945005</v>
       </c>
       <c r="X3" t="n">
         <v>-18389.01727795352</v>
@@ -7602,7 +7370,7 @@
         <v>6.672037935581266e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>437.3099999999999</v>
+        <v>2676.007602567666</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000011993e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>83.800322581817</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.206x + -20764.144</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.205639155701688</v>
       </c>
       <c r="X4" t="n">
         <v>-20764.14428771099</v>
@@ -7654,7 +7420,7 @@
         <v>1.209362632440205e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>366.48</v>
+        <v>2592.350911856874</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000015e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>83.56031029996976</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 8.860x + -19510.069</t>
-        </is>
+      <c r="W5" t="n">
+        <v>8.859792687787619</v>
       </c>
       <c r="X5" t="n">
         <v>-19510.06915356576</v>
@@ -7706,7 +7470,7 @@
         <v>2.827790617756636e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>355.9099999999999</v>
+        <v>2547.892585559964</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>84.23501132711984</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.905x + -21674.404</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.905014248056899</v>
       </c>
       <c r="X6" t="n">
         <v>-21674.40370160397</v>
@@ -7758,7 +7520,7 @@
         <v>6.462583577566745e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>324.8700000000003</v>
+        <v>2510.960577695527</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000026449e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>84.10817881209063</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.690x + -20864.734</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.690328319741196</v>
       </c>
       <c r="X7" t="n">
         <v>-20864.73366181109</v>
@@ -7810,7 +7570,7 @@
         <v>2.024751398629683e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>327.5</v>
+        <v>2476.289429560517</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000002e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>84.23032734038878</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.897x + -21043.623</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.896918519469001</v>
       </c>
       <c r="X8" t="n">
         <v>-21043.62329328149</v>
@@ -7862,7 +7620,7 @@
         <v>1.065073969227068e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>315.5099999999998</v>
+        <v>2443.014271513823</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000303e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>84.28896888205668</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.999x + -20996.501</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.999227994732648</v>
       </c>
       <c r="X9" t="n">
         <v>-20996.50124691442</v>
@@ -7914,7 +7670,7 @@
         <v>7.25785676806503e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>302.6999999999998</v>
+        <v>2410.64347555354</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001071e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>84.36956451087175</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.143x + -21047.239</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.14330546159123</v>
       </c>
       <c r="X10" t="n">
         <v>-21047.23939884337</v>
@@ -7966,7 +7720,7 @@
         <v>9.595270494357625e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>296.3499999999999</v>
+        <v>2379.623915660651</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000808e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>84.47507958186047</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.338x + -21213.489</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.33826358341666</v>
       </c>
       <c r="X11" t="n">
         <v>-21213.48890531447</v>
@@ -8018,7 +7770,7 @@
         <v>2.211286328280494e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>284.1400000000001</v>
+        <v>2350.232133890175</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000597e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>83.5543991192702</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.852x + -19952.424</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.851598617414627</v>
       </c>
       <c r="X2" t="n">
         <v>-19952.42369852823</v>
@@ -8216,7 +7966,7 @@
         <v>2.001749904773327e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>359.3999999999996</v>
+        <v>2576.472967375066</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000005e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>84.08925682497375</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.659x + -20793.571</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.659086668367813</v>
       </c>
       <c r="X3" t="n">
         <v>-20793.57053931227</v>
@@ -8268,7 +8016,7 @@
         <v>2.250707467516904e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>316.77</v>
+        <v>2473.10513730076</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000003e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>84.21018159591914</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.862x + -20881.196</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.862247753027239</v>
       </c>
       <c r="X4" t="n">
         <v>-20881.19554562695</v>
@@ -8320,7 +8066,7 @@
         <v>1.719296877167754e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>305.9499999999998</v>
+        <v>2432.704602150638</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>84.0573327975454</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.607x + -20031.476</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.60682703902185</v>
       </c>
       <c r="X5" t="n">
         <v>-20031.4761887961</v>
@@ -8372,7 +8116,7 @@
         <v>3.869679054820073e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>310.9699999999998</v>
+        <v>2401.39949751879</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000015e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>84.34704382289181</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.103x + -20899.763</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.10263391301911</v>
       </c>
       <c r="X6" t="n">
         <v>-20899.76336249191</v>
@@ -8424,7 +8166,7 @@
         <v>1.458778026601151e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>298.3000000000002</v>
+        <v>2372.219847912399</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000017e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>84.43734079830348</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.268x + -21030.504</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.26768746907202</v>
       </c>
       <c r="X7" t="n">
         <v>-21030.50437148828</v>
@@ -8476,7 +8216,7 @@
         <v>1.099135095323489e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>291.53</v>
+        <v>2346.14593972893</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000009e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>83.99080242413268</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.500x + -19138.339</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.499694835795008</v>
       </c>
       <c r="X8" t="n">
         <v>-19138.33906001406</v>
@@ -8528,7 +8266,7 @@
         <v>6.029933164846459e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>295.6199999999999</v>
+        <v>2322.046114774923</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000007e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>84.51384114708173</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.412x + -20923.408</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.41176006984398</v>
       </c>
       <c r="X9" t="n">
         <v>-20923.40766616633</v>
@@ -8580,7 +8316,7 @@
         <v>7.119070493671383e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>277.3899999999999</v>
+        <v>2299.791109757578</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>84.32091260584585</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.056x + -19972.246</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.05584485917781</v>
       </c>
       <c r="X10" t="n">
         <v>-19972.2463116406</v>
@@ -8632,7 +8366,7 @@
         <v>4.002957545166091e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>280.5899999999999</v>
+        <v>2279.53393126862</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>84.14704381011862</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.755x + -19163.824</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.755128718863007</v>
       </c>
       <c r="X11" t="n">
         <v>-19163.82370747895</v>
@@ -8684,7 +8416,7 @@
         <v>4.876029599413158e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>278.5300000000002</v>
+        <v>2259.616609348771</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000033e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>84.40980167338525</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.217x + -19974.308</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.21678547260878</v>
       </c>
       <c r="X12" t="n">
         <v>-19974.30768321452</v>
@@ -8736,7 +8466,7 @@
         <v>5.652424625790092e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>272.1799999999998</v>
+        <v>2240.029239039912</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000876e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>84.21281745699126</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 9.867x + -19071.302</t>
-        </is>
+      <c r="W13" t="n">
+        <v>9.866770383495455</v>
       </c>
       <c r="X13" t="n">
         <v>-19071.30151111697</v>
@@ -8788,7 +8516,7 @@
         <v>4.405646836199243e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>268.0200000000002</v>
+        <v>2220.45164926095</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000038715e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>84.26872441677907</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 9.964x + -19107.991</t>
-        </is>
+      <c r="W14" t="n">
+        <v>9.963672478044014</v>
       </c>
       <c r="X14" t="n">
         <v>-19107.99141286724</v>
@@ -8840,7 +8566,7 @@
         <v>6.68519159908061e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>263.23</v>
+        <v>2201.364861816771</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000046e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>84.27469124761832</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 9.974x + -18975.231</t>
-        </is>
+      <c r="W15" t="n">
+        <v>9.97412602405227</v>
       </c>
       <c r="X15" t="n">
         <v>-18975.23095006755</v>
@@ -8892,7 +8616,7 @@
         <v>2.309785625433233e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>256.96</v>
+        <v>2182.479627035726</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>84.28098358509754</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 9.985x + -18841.880</t>
-        </is>
+      <c r="W16" t="n">
+        <v>9.985173390700096</v>
       </c>
       <c r="X16" t="n">
         <v>-18841.88034951055</v>
@@ -8944,7 +8666,7 @@
         <v>3.073822070376296e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>252.7500000000002</v>
+        <v>2164.218695951675</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000098e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>84.58584851380431</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.551x + -19826.849</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.55107928218669</v>
       </c>
       <c r="X17" t="n">
         <v>-19826.84922533125</v>
@@ -8996,7 +8716,7 @@
         <v>3.613226763162385e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>242.3899999999999</v>
+        <v>2145.953973210237</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000002e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>84.33590775682683</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 10.083x + -18725.292</t>
-        </is>
+      <c r="W18" t="n">
+        <v>10.08264169778994</v>
       </c>
       <c r="X18" t="n">
         <v>-18725.29177948506</v>
@@ -9048,7 +8766,7 @@
         <v>6.620729427644264e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>241.3600000000001</v>
+        <v>2127.456486914492</v>
       </c>
       <c r="AA18" t="n">
         <v>1.00000000000006e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>84.8472275073682</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 11.089x + -20569.156</t>
-        </is>
+      <c r="W19" t="n">
+        <v>11.08941417681177</v>
       </c>
       <c r="X19" t="n">
         <v>-20569.15604088516</v>
@@ -9100,7 +8816,7 @@
         <v>5.46674741496479e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>228.4099999999999</v>
+        <v>2109.284482831431</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000001002e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>84.3718801124962</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 10.148x + -18543.725</t>
-        </is>
+      <c r="W20" t="n">
+        <v>10.14750574900208</v>
       </c>
       <c r="X20" t="n">
         <v>-18543.72508123181</v>
@@ -9152,7 +8866,7 @@
         <v>1.522106775312913e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>232.3</v>
+        <v>2091.518776425849</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>84.41751953333907</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 10.231x + -18551.967</t>
-        </is>
+      <c r="W21" t="n">
+        <v>10.23100030374475</v>
       </c>
       <c r="X21" t="n">
         <v>-18551.96748768415</v>
@@ -9204,7 +8916,7 @@
         <v>1.055729918591458e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>229.6000000000001</v>
+        <v>2073.324016333495</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000001e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>84.674206150773</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 10.727x + -19356.706</t>
-        </is>
+      <c r="W22" t="n">
+        <v>10.72716490197373</v>
       </c>
       <c r="X22" t="n">
         <v>-19356.70630630733</v>
@@ -9256,7 +8966,7 @@
         <v>5.08786599857168e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>218.1800000000001</v>
+        <v>2054.917622897904</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000043e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>81.94691809876741</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.068x + -15811.897</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.067851536595724</v>
       </c>
       <c r="X2" t="n">
         <v>-15811.89697297614</v>
@@ -9454,7 +9162,7 @@
         <v>1.790087011635379e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>537.3899999999999</v>
+        <v>2451.890993791166</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000365e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>83.70293679891785</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.062x + -17208.840</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.062145301212764</v>
       </c>
       <c r="X3" t="n">
         <v>-17208.84006990088</v>
@@ -9506,7 +9212,7 @@
         <v>9.976602508334061e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>354.3599999999999</v>
+        <v>2154.014554009581</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000007021e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>84.20803156131308</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.859x + -18040.811</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.858561745178738</v>
       </c>
       <c r="X4" t="n">
         <v>-18040.81103764051</v>
@@ -9558,7 +9262,7 @@
         <v>3.664386647689722e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>304.6500000000001</v>
+        <v>2082.038696500387</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>84.22866483204541</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 9.894x + -17730.187</t>
-        </is>
+      <c r="W5" t="n">
+        <v>9.894048215477767</v>
       </c>
       <c r="X5" t="n">
         <v>-17730.1866662091</v>
@@ -9610,7 +9312,7 @@
         <v>1.107602193868262e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>290.28</v>
+        <v>2044.046495209578</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001067e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>84.32231179456203</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.058x + -17767.150</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.05833928846686</v>
       </c>
       <c r="X6" t="n">
         <v>-17767.14966146949</v>
@@ -9662,7 +9362,7 @@
         <v>4.054403846345418e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>280.4200000000001</v>
+        <v>2012.678866720348</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000221e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>84.40353029469115</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.205x + -17781.512</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.2052635662021</v>
       </c>
       <c r="X7" t="n">
         <v>-17781.51214802358</v>
@@ -9714,7 +9412,7 @@
         <v>3.114979369353384e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>268.8299999999999</v>
+        <v>1982.892256509418</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000158e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>84.31086005262659</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.038x + -17207.218</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.03795944193657</v>
       </c>
       <c r="X8" t="n">
         <v>-17207.21778862729</v>
@@ -9766,7 +9462,7 @@
         <v>1.418852326674026e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>266.1499999999999</v>
+        <v>1953.937251649365</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000006949e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>84.39118073912169</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.183x + -17229.113</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.18264979393043</v>
       </c>
       <c r="X9" t="n">
         <v>-17229.11253867616</v>
@@ -9818,7 +9512,7 @@
         <v>4.077135247975173e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>259.55</v>
+        <v>1925.844962918161</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000086e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>84.81318980529782</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.016x + -18499.841</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.01624630188137</v>
       </c>
       <c r="X10" t="n">
         <v>-18499.84125285816</v>
@@ -9870,7 +9562,7 @@
         <v>2.151239635401392e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>245.98</v>
+        <v>1898.99815532462</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000042839e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>84.49627319990968</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.378x + -17120.933</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.37832129807491</v>
       </c>
       <c r="X11" t="n">
         <v>-17120.9332421032</v>
@@ -9922,7 +9612,7 @@
         <v>9.579921850165052e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>246.7399999999998</v>
+        <v>1873.937511008381</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000042385e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-473.96</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-401.3600000000001</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-372.9200000000001</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-359.3600000000001</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-355.1200000000003</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-342.6699999999996</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-334.4399999999996</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-314.5099999999998</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-321.2599999999998</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-314.0999999999999</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-642.1500000000001</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-473.1900000000001</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-404.27</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-359.5299999999997</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-366.6800000000003</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-336.4000000000001</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-335.4899999999998</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-321.52</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-307.1000000000004</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-305.1800000000003</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-590.0200000000004</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-411.4200000000001</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-362.29</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-335.2199999999998</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-328.71</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-311.1500000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-312.0499999999997</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-303.1699999999996</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-294.6900000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-285.3699999999999</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-634.5</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-437.3099999999999</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-366.48</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-355.9099999999999</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-324.8700000000003</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-327.5</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-315.5099999999998</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-302.6999999999998</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-296.3499999999999</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-284.1400000000001</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-537.3899999999999</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-354.3599999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-304.6500000000001</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-290.28</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-280.4200000000001</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-268.8299999999999</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-266.1499999999999</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-259.55</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-245.98</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-246.7399999999998</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-473.96</v>
+        <v>2087.234</v>
       </c>
       <c r="D2" t="n">
         <v>2.47316e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-401.3600000000001</v>
+        <v>1965.1</v>
       </c>
       <c r="D3" t="n">
         <v>2.53993e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-372.9200000000001</v>
+        <v>1910.832</v>
       </c>
       <c r="D4" t="n">
         <v>2.56606e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-359.3600000000001</v>
+        <v>1871.58</v>
       </c>
       <c r="D5" t="n">
         <v>2.58279e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-355.1200000000003</v>
+        <v>1830.397</v>
       </c>
       <c r="D6" t="n">
         <v>2.59908e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-342.6699999999996</v>
+        <v>1804.514</v>
       </c>
       <c r="D7" t="n">
         <v>2.61229e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-334.4399999999996</v>
+        <v>1774.828</v>
       </c>
       <c r="D8" t="n">
         <v>2.6261e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-314.5099999999998</v>
+        <v>1757.883</v>
       </c>
       <c r="D9" t="n">
         <v>2.63999e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-321.2599999999998</v>
+        <v>1724.039</v>
       </c>
       <c r="D10" t="n">
         <v>2.64978e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-314.0999999999999</v>
+        <v>1702.963</v>
       </c>
       <c r="D11" t="n">
         <v>2.65937e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-350.0300000000002</v>
+        <v>1843.244</v>
       </c>
       <c r="D2" t="n">
         <v>2.56788e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-311.8800000000001</v>
+        <v>1726.966</v>
       </c>
       <c r="D3" t="n">
         <v>2.63289e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-302.9500000000003</v>
+        <v>1688.105</v>
       </c>
       <c r="D4" t="n">
         <v>2.65145e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-301.46</v>
+        <v>1658.146</v>
       </c>
       <c r="D5" t="n">
         <v>2.66116e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-302.26</v>
+        <v>1627.795</v>
       </c>
       <c r="D6" t="n">
         <v>2.6729e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-285.9899999999998</v>
+        <v>1613.135</v>
       </c>
       <c r="D7" t="n">
         <v>2.68413e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-281.4999999999998</v>
+        <v>1593.699</v>
       </c>
       <c r="D8" t="n">
         <v>2.69319e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-284.3100000000002</v>
+        <v>1569.828</v>
       </c>
       <c r="D9" t="n">
         <v>2.70232e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-274.7</v>
+        <v>1554.666</v>
       </c>
       <c r="D10" t="n">
         <v>2.71116e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-274.5699999999999</v>
+        <v>1537.197</v>
       </c>
       <c r="D11" t="n">
         <v>2.71722e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-270.4099999999999</v>
+        <v>1521.409</v>
       </c>
       <c r="D12" t="n">
         <v>2.72603e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-262.7</v>
+        <v>1509.958</v>
       </c>
       <c r="D13" t="n">
         <v>2.73371e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-262.8500000000001</v>
+        <v>1490.308</v>
       </c>
       <c r="D14" t="n">
         <v>2.74088e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-250.9400000000001</v>
+        <v>1482.278</v>
       </c>
       <c r="D15" t="n">
         <v>2.74915e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-246.79</v>
+        <v>1469.337</v>
       </c>
       <c r="D16" t="n">
         <v>2.75645e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-243.71</v>
+        <v>1454.173</v>
       </c>
       <c r="D17" t="n">
         <v>2.76371e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-236.8999999999999</v>
+        <v>1440.784</v>
       </c>
       <c r="D18" t="n">
         <v>2.77145e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-231.95</v>
+        <v>1427.898</v>
       </c>
       <c r="D19" t="n">
         <v>2.77966e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-229.98</v>
+        <v>1412.093</v>
       </c>
       <c r="D20" t="n">
         <v>2.78655e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-228.5699999999999</v>
+        <v>1393.428</v>
       </c>
       <c r="D21" t="n">
         <v>2.79416e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-221.3499999999999</v>
+        <v>1383.297</v>
       </c>
       <c r="D22" t="n">
         <v>2.80047e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-367.96</v>
+        <v>2011.455</v>
       </c>
       <c r="D2" t="n">
         <v>2.50243e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-334.3999999999996</v>
+        <v>1875.195</v>
       </c>
       <c r="D3" t="n">
         <v>2.5758e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-336.02</v>
+        <v>1821.97</v>
       </c>
       <c r="D4" t="n">
         <v>2.59576e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-326.52</v>
+        <v>1791.459</v>
       </c>
       <c r="D5" t="n">
         <v>2.61069e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-329.3499999999999</v>
+        <v>1758.682</v>
       </c>
       <c r="D6" t="n">
         <v>2.62175e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-308.3299999999999</v>
+        <v>1750.934</v>
       </c>
       <c r="D7" t="n">
         <v>2.63351e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-314.73</v>
+        <v>1715.923</v>
       </c>
       <c r="D8" t="n">
         <v>2.64473e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-300.3899999999999</v>
+        <v>1703.106</v>
       </c>
       <c r="D9" t="n">
         <v>2.65448e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-291.3599999999997</v>
+        <v>1691.294</v>
       </c>
       <c r="D10" t="n">
         <v>2.66297e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-297.77</v>
+        <v>1659.046</v>
       </c>
       <c r="D11" t="n">
         <v>2.67271e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-287.3099999999999</v>
+        <v>1647.535</v>
       </c>
       <c r="D12" t="n">
         <v>2.68187e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-288.71</v>
+        <v>1625.774</v>
       </c>
       <c r="D13" t="n">
         <v>2.68934e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-274.25</v>
+        <v>1617.955</v>
       </c>
       <c r="D14" t="n">
         <v>2.6978e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-270.3899999999999</v>
+        <v>1599.826</v>
       </c>
       <c r="D15" t="n">
         <v>2.70643e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-262.9400000000003</v>
+        <v>1584.736</v>
       </c>
       <c r="D16" t="n">
         <v>2.71554e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-258.71</v>
+        <v>1571.06</v>
       </c>
       <c r="D17" t="n">
         <v>2.72198e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-254.1900000000001</v>
+        <v>1553.62</v>
       </c>
       <c r="D18" t="n">
         <v>2.73004e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-257.6599999999999</v>
+        <v>1533.493</v>
       </c>
       <c r="D19" t="n">
         <v>2.73552e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-253.1300000000001</v>
+        <v>1518.719</v>
       </c>
       <c r="D20" t="n">
         <v>2.74227e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-247.51</v>
+        <v>1505.031</v>
       </c>
       <c r="D21" t="n">
         <v>2.7485e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-243.05</v>
+        <v>1490.541</v>
       </c>
       <c r="D22" t="n">
         <v>2.75752e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-642.1500000000001</v>
+        <v>2408.725</v>
       </c>
       <c r="D2" t="n">
         <v>2.24598e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-473.1900000000001</v>
+        <v>2041.874</v>
       </c>
       <c r="D3" t="n">
         <v>2.50617e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-404.27</v>
+        <v>1955.021</v>
       </c>
       <c r="D4" t="n">
         <v>2.56008e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-359.5299999999997</v>
+        <v>1922.261</v>
       </c>
       <c r="D5" t="n">
         <v>2.57981e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-366.6800000000003</v>
+        <v>1859.155</v>
       </c>
       <c r="D6" t="n">
         <v>2.59346e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-336.4000000000001</v>
+        <v>1842.76</v>
       </c>
       <c r="D7" t="n">
         <v>2.60676e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-335.4899999999998</v>
+        <v>1801.763</v>
       </c>
       <c r="D8" t="n">
         <v>2.61957e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-321.52</v>
+        <v>1771.611</v>
       </c>
       <c r="D9" t="n">
         <v>2.63361e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-307.1000000000004</v>
+        <v>1749.158</v>
       </c>
       <c r="D10" t="n">
         <v>2.64564e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-305.1800000000003</v>
+        <v>1712.861</v>
       </c>
       <c r="D11" t="n">
         <v>2.6591e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-414.4500000000003</v>
+        <v>1972.498</v>
       </c>
       <c r="D2" t="n">
         <v>2.55935e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-342.4899999999998</v>
+        <v>1832.88</v>
       </c>
       <c r="D3" t="n">
         <v>2.61466e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-326.6300000000001</v>
+        <v>1789.713</v>
       </c>
       <c r="D4" t="n">
         <v>2.62738e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-320.5900000000001</v>
+        <v>1762.941</v>
       </c>
       <c r="D5" t="n">
         <v>2.63498e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-322.96</v>
+        <v>1732.477</v>
       </c>
       <c r="D6" t="n">
         <v>2.64007e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-311.4599999999996</v>
+        <v>1710.21</v>
       </c>
       <c r="D7" t="n">
         <v>2.64831e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-302.3600000000001</v>
+        <v>1695.556</v>
       </c>
       <c r="D8" t="n">
         <v>2.65328e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-298.0699999999997</v>
+        <v>1675.858</v>
       </c>
       <c r="D9" t="n">
         <v>2.66028e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-301.3700000000003</v>
+        <v>1649.471</v>
       </c>
       <c r="D10" t="n">
         <v>2.66653e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-288.0599999999999</v>
+        <v>1637.425</v>
       </c>
       <c r="D11" t="n">
         <v>2.67369e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-281.74</v>
+        <v>1620.573</v>
       </c>
       <c r="D12" t="n">
         <v>2.68074e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-286.6199999999999</v>
+        <v>1597.221</v>
       </c>
       <c r="D13" t="n">
         <v>2.68452e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-284.7200000000003</v>
+        <v>1574.211</v>
       </c>
       <c r="D14" t="n">
         <v>2.69242e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-282.23</v>
+        <v>1558.589</v>
       </c>
       <c r="D15" t="n">
         <v>2.69735e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-265.97</v>
+        <v>1556.772</v>
       </c>
       <c r="D16" t="n">
         <v>2.70132e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-270.3299999999999</v>
+        <v>1534.684</v>
       </c>
       <c r="D17" t="n">
         <v>2.70694e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-269.1999999999998</v>
+        <v>1513.547</v>
       </c>
       <c r="D18" t="n">
         <v>2.71452e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-259.6100000000001</v>
+        <v>1503.857</v>
       </c>
       <c r="D19" t="n">
         <v>2.71953e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-262.8900000000001</v>
+        <v>1481.24</v>
       </c>
       <c r="D20" t="n">
         <v>2.72619e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-243.7900000000002</v>
+        <v>1479.339</v>
       </c>
       <c r="D21" t="n">
         <v>2.734e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-246.6500000000001</v>
+        <v>1456.159</v>
       </c>
       <c r="D22" t="n">
         <v>2.73957e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-590.0200000000004</v>
+        <v>2343.822</v>
       </c>
       <c r="D2" t="n">
         <v>2.28544e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-411.4200000000001</v>
+        <v>1983.834</v>
       </c>
       <c r="D3" t="n">
         <v>2.52144e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-362.29</v>
+        <v>1889.344</v>
       </c>
       <c r="D4" t="n">
         <v>2.57072e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-335.2199999999998</v>
+        <v>1852.22</v>
       </c>
       <c r="D5" t="n">
         <v>2.58989e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-328.71</v>
+        <v>1810.7</v>
       </c>
       <c r="D6" t="n">
         <v>2.60634e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-311.1500000000001</v>
+        <v>1786.002</v>
       </c>
       <c r="D7" t="n">
         <v>2.62199e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-312.0499999999997</v>
+        <v>1746.768</v>
       </c>
       <c r="D8" t="n">
         <v>2.63582e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-303.1699999999996</v>
+        <v>1716.744</v>
       </c>
       <c r="D9" t="n">
         <v>2.65159e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-294.6900000000001</v>
+        <v>1690.529</v>
       </c>
       <c r="D10" t="n">
         <v>2.66405e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-285.3699999999999</v>
+        <v>1665.543</v>
       </c>
       <c r="D11" t="n">
         <v>2.67788e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-393.2799999999997</v>
+        <v>1981.482</v>
       </c>
       <c r="D2" t="n">
         <v>2.5166e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-343.8899999999999</v>
+        <v>1824.727</v>
       </c>
       <c r="D3" t="n">
         <v>2.5857e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-325.8600000000001</v>
+        <v>1785.352</v>
       </c>
       <c r="D4" t="n">
         <v>2.60358e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-310.21</v>
+        <v>1767.733</v>
       </c>
       <c r="D5" t="n">
         <v>2.61499e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-311.8700000000003</v>
+        <v>1732.844</v>
       </c>
       <c r="D6" t="n">
         <v>2.62565e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-307.25</v>
+        <v>1713.982</v>
       </c>
       <c r="D7" t="n">
         <v>2.63224e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-299.0799999999999</v>
+        <v>1699</v>
       </c>
       <c r="D8" t="n">
         <v>2.6399e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-293.9299999999998</v>
+        <v>1681.85</v>
       </c>
       <c r="D9" t="n">
         <v>2.64761e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-291.79</v>
+        <v>1665.735</v>
       </c>
       <c r="D10" t="n">
         <v>2.65302e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-291.6300000000001</v>
+        <v>1642.453</v>
       </c>
       <c r="D11" t="n">
         <v>2.66007e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-278.5899999999999</v>
+        <v>1636.496</v>
       </c>
       <c r="D12" t="n">
         <v>2.66771e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-281.52</v>
+        <v>1614.385</v>
       </c>
       <c r="D13" t="n">
         <v>2.67451e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-275.8000000000002</v>
+        <v>1600.749</v>
       </c>
       <c r="D14" t="n">
         <v>2.68093e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-265.1400000000001</v>
+        <v>1589.961</v>
       </c>
       <c r="D15" t="n">
         <v>2.68826e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-275.5100000000002</v>
+        <v>1563.783</v>
       </c>
       <c r="D16" t="n">
         <v>2.69432e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-268.5599999999999</v>
+        <v>1548.647</v>
       </c>
       <c r="D17" t="n">
         <v>2.7027e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-253.3800000000001</v>
+        <v>1545.171</v>
       </c>
       <c r="D18" t="n">
         <v>2.70891e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-261.4500000000003</v>
+        <v>1517.703</v>
       </c>
       <c r="D19" t="n">
         <v>2.71565e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-266.0900000000001</v>
+        <v>1495.006</v>
       </c>
       <c r="D20" t="n">
         <v>2.72242e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-248.9100000000001</v>
+        <v>1489.912</v>
       </c>
       <c r="D21" t="n">
         <v>2.73186e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-233.4300000000001</v>
+        <v>1483.075</v>
       </c>
       <c r="D22" t="n">
         <v>2.73981e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-634.5</v>
+        <v>2256.101</v>
       </c>
       <c r="D2" t="n">
         <v>2.31914e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-437.3099999999999</v>
+        <v>1906.253</v>
       </c>
       <c r="D3" t="n">
         <v>2.56388e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-366.48</v>
+        <v>1832.576</v>
       </c>
       <c r="D4" t="n">
         <v>2.60971e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-355.9099999999999</v>
+        <v>1778.58</v>
       </c>
       <c r="D5" t="n">
         <v>2.6273e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-324.8700000000003</v>
+        <v>1762.227</v>
       </c>
       <c r="D6" t="n">
         <v>2.64217e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-327.5</v>
+        <v>1724.641</v>
       </c>
       <c r="D7" t="n">
         <v>2.65402e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-315.5099999999998</v>
+        <v>1695.8</v>
       </c>
       <c r="D8" t="n">
         <v>2.66921e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-302.6999999999998</v>
+        <v>1670.12</v>
       </c>
       <c r="D9" t="n">
         <v>2.68514e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-296.3499999999999</v>
+        <v>1642.478</v>
       </c>
       <c r="D10" t="n">
         <v>2.69867e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-284.1400000000001</v>
+        <v>1621.088</v>
       </c>
       <c r="D11" t="n">
         <v>2.71307e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-359.3999999999996</v>
+        <v>1834.501</v>
       </c>
       <c r="D2" t="n">
         <v>2.59609e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-316.77</v>
+        <v>1730.541</v>
       </c>
       <c r="D3" t="n">
         <v>2.65467e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-305.9499999999998</v>
+        <v>1692.576</v>
       </c>
       <c r="D4" t="n">
         <v>2.67275e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-310.9699999999998</v>
+        <v>1657.131</v>
       </c>
       <c r="D5" t="n">
         <v>2.68375e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-298.3000000000002</v>
+        <v>1638.692</v>
       </c>
       <c r="D6" t="n">
         <v>2.69563e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-291.53</v>
+        <v>1615.773</v>
       </c>
       <c r="D7" t="n">
         <v>2.70626e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-295.6199999999999</v>
+        <v>1583.603</v>
       </c>
       <c r="D8" t="n">
         <v>2.71799e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-277.3899999999999</v>
+        <v>1578.355</v>
       </c>
       <c r="D9" t="n">
         <v>2.7292e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-280.5899999999999</v>
+        <v>1553.738</v>
       </c>
       <c r="D10" t="n">
         <v>2.73763e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-278.5300000000002</v>
+        <v>1533.59</v>
       </c>
       <c r="D11" t="n">
         <v>2.74687e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-272.1799999999998</v>
+        <v>1520.407</v>
       </c>
       <c r="D12" t="n">
         <v>2.75528e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-268.0200000000002</v>
+        <v>1502.207</v>
       </c>
       <c r="D13" t="n">
         <v>2.76469e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-263.23</v>
+        <v>1487.358</v>
       </c>
       <c r="D14" t="n">
         <v>2.77318e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-256.96</v>
+        <v>1474.18</v>
       </c>
       <c r="D15" t="n">
         <v>2.78166e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-252.7500000000002</v>
+        <v>1458.19</v>
       </c>
       <c r="D16" t="n">
         <v>2.79004e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-242.3899999999999</v>
+        <v>1452.395</v>
       </c>
       <c r="D17" t="n">
         <v>2.79878e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-241.3600000000001</v>
+        <v>1431.534</v>
       </c>
       <c r="D18" t="n">
         <v>2.80715e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-228.4099999999999</v>
+        <v>1426.919</v>
       </c>
       <c r="D19" t="n">
         <v>2.8148e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-232.3</v>
+        <v>1402.282</v>
       </c>
       <c r="D20" t="n">
         <v>2.82385e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-229.6000000000001</v>
+        <v>1388.654</v>
       </c>
       <c r="D21" t="n">
         <v>2.8306e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-218.1800000000001</v>
+        <v>1381.295</v>
       </c>
       <c r="D22" t="n">
         <v>2.83893e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-537.3899999999999</v>
+        <v>1793.609</v>
       </c>
       <c r="D2" t="n">
         <v>2.56611e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-354.3599999999999</v>
+        <v>1447.856</v>
       </c>
       <c r="D3" t="n">
         <v>2.79414e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-304.6500000000001</v>
+        <v>1374.545</v>
       </c>
       <c r="D4" t="n">
         <v>2.82684e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-290.28</v>
+        <v>1334.922</v>
       </c>
       <c r="D5" t="n">
         <v>2.83732e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-280.4200000000001</v>
+        <v>1308.322</v>
       </c>
       <c r="D6" t="n">
         <v>2.84756e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-268.8299999999999</v>
+        <v>1282.416</v>
       </c>
       <c r="D7" t="n">
         <v>2.85869e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-266.1499999999999</v>
+        <v>1255.304</v>
       </c>
       <c r="D8" t="n">
         <v>2.86851e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-259.55</v>
+        <v>1232.165</v>
       </c>
       <c r="D9" t="n">
         <v>2.88131e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-245.98</v>
+        <v>1218.456</v>
       </c>
       <c r="D10" t="n">
         <v>2.89084e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-246.7399999999998</v>
+        <v>1188.819</v>
       </c>
       <c r="D11" t="n">
         <v>2.90098e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>2087.234</v>
       </c>
+      <c r="C2" t="n">
+        <v>2534.148354975808</v>
+      </c>
       <c r="D2" t="n">
         <v>2.47316e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1965.1</v>
       </c>
+      <c r="C3" t="n">
+        <v>2402.661038330325</v>
+      </c>
       <c r="D3" t="n">
         <v>2.53993e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1910.832</v>
       </c>
+      <c r="C4" t="n">
+        <v>2352.762856303859</v>
+      </c>
       <c r="D4" t="n">
         <v>2.56606e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1871.58</v>
       </c>
+      <c r="C5" t="n">
+        <v>2311.662060100506</v>
+      </c>
       <c r="D5" t="n">
         <v>2.58279e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1830.397</v>
       </c>
+      <c r="C6" t="n">
+        <v>2275.940382116427</v>
+      </c>
       <c r="D6" t="n">
         <v>2.59908e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1804.514</v>
       </c>
+      <c r="C7" t="n">
+        <v>2248.158537176274</v>
+      </c>
       <c r="D7" t="n">
         <v>2.61229e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1774.828</v>
       </c>
+      <c r="C8" t="n">
+        <v>2223.486004257281</v>
+      </c>
       <c r="D8" t="n">
         <v>2.6261e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1757.883</v>
       </c>
+      <c r="C9" t="n">
+        <v>2203.049810154411</v>
+      </c>
       <c r="D9" t="n">
         <v>2.63999e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1724.039</v>
       </c>
+      <c r="C10" t="n">
+        <v>2174.492412632753</v>
+      </c>
       <c r="D10" t="n">
         <v>2.64978e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1702.963</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2154.015390007403</v>
       </c>
       <c r="D11" t="n">
         <v>2.65937e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>1843.244</v>
       </c>
+      <c r="C2" t="n">
+        <v>2334.677364859909</v>
+      </c>
       <c r="D2" t="n">
         <v>2.56788e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1726.966</v>
       </c>
+      <c r="C3" t="n">
+        <v>2186.837256830815</v>
+      </c>
       <c r="D3" t="n">
         <v>2.63289e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1688.105</v>
       </c>
+      <c r="C4" t="n">
+        <v>2147.66082093477</v>
+      </c>
       <c r="D4" t="n">
         <v>2.65145e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1658.146</v>
       </c>
+      <c r="C5" t="n">
+        <v>2119.586294400986</v>
+      </c>
       <c r="D5" t="n">
         <v>2.66116e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1627.795</v>
       </c>
+      <c r="C6" t="n">
+        <v>2092.628087995692</v>
+      </c>
       <c r="D6" t="n">
         <v>2.6729e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1613.135</v>
       </c>
+      <c r="C7" t="n">
+        <v>2076.804889353468</v>
+      </c>
       <c r="D7" t="n">
         <v>2.68413e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1593.699</v>
       </c>
+      <c r="C8" t="n">
+        <v>2055.07039667952</v>
+      </c>
       <c r="D8" t="n">
         <v>2.69319e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1569.828</v>
       </c>
+      <c r="C9" t="n">
+        <v>2033.356972168813</v>
+      </c>
       <c r="D9" t="n">
         <v>2.70232e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1554.666</v>
       </c>
+      <c r="C10" t="n">
+        <v>2019.035590468495</v>
+      </c>
       <c r="D10" t="n">
         <v>2.71116e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1537.197</v>
       </c>
+      <c r="C11" t="n">
+        <v>2002.520152707067</v>
+      </c>
       <c r="D11" t="n">
         <v>2.71722e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1521.409</v>
       </c>
+      <c r="C12" t="n">
+        <v>1986.751471914043</v>
+      </c>
       <c r="D12" t="n">
         <v>2.72603e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1509.958</v>
       </c>
+      <c r="C13" t="n">
+        <v>1973.103985497663</v>
+      </c>
       <c r="D13" t="n">
         <v>2.73371e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1490.308</v>
       </c>
+      <c r="C14" t="n">
+        <v>1955.044679701886</v>
+      </c>
       <c r="D14" t="n">
         <v>2.74088e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1482.278</v>
       </c>
+      <c r="C15" t="n">
+        <v>1945.559437188276</v>
+      </c>
       <c r="D15" t="n">
         <v>2.74915e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1469.337</v>
       </c>
+      <c r="C16" t="n">
+        <v>1931.170152400852</v>
+      </c>
       <c r="D16" t="n">
         <v>2.75645e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1454.173</v>
       </c>
+      <c r="C17" t="n">
+        <v>1917.216831710167</v>
+      </c>
       <c r="D17" t="n">
         <v>2.76371e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1440.784</v>
       </c>
+      <c r="C18" t="n">
+        <v>1902.504279255319</v>
+      </c>
       <c r="D18" t="n">
         <v>2.77145e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1427.898</v>
       </c>
+      <c r="C19" t="n">
+        <v>1889.071253522337</v>
+      </c>
       <c r="D19" t="n">
         <v>2.77966e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1412.093</v>
       </c>
+      <c r="C20" t="n">
+        <v>1874.473569673127</v>
+      </c>
       <c r="D20" t="n">
         <v>2.78655e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1393.428</v>
       </c>
+      <c r="C21" t="n">
+        <v>1855.233746186314</v>
+      </c>
       <c r="D21" t="n">
         <v>2.79416e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1383.297</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1844.604965443586</v>
       </c>
       <c r="D22" t="n">
         <v>2.80047e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>2011.455</v>
       </c>
+      <c r="C2" t="n">
+        <v>2474.255249033753</v>
+      </c>
       <c r="D2" t="n">
         <v>2.50243e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1875.195</v>
       </c>
+      <c r="C3" t="n">
+        <v>2320.341544920394</v>
+      </c>
       <c r="D3" t="n">
         <v>2.5758e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1821.97</v>
       </c>
+      <c r="C4" t="n">
+        <v>2269.073986556991</v>
+      </c>
       <c r="D4" t="n">
         <v>2.59576e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1791.459</v>
       </c>
+      <c r="C5" t="n">
+        <v>2238.680826314071</v>
+      </c>
       <c r="D5" t="n">
         <v>2.61069e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1758.682</v>
       </c>
+      <c r="C6" t="n">
+        <v>2210.562658966077</v>
+      </c>
       <c r="D6" t="n">
         <v>2.62175e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1750.934</v>
       </c>
+      <c r="C7" t="n">
+        <v>2200.099462950644</v>
+      </c>
       <c r="D7" t="n">
         <v>2.63351e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1715.923</v>
       </c>
+      <c r="C8" t="n">
+        <v>2168.040071920074</v>
+      </c>
       <c r="D8" t="n">
         <v>2.64473e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1703.106</v>
       </c>
+      <c r="C9" t="n">
+        <v>2154.907056216087</v>
+      </c>
       <c r="D9" t="n">
         <v>2.65448e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1691.294</v>
       </c>
+      <c r="C10" t="n">
+        <v>2139.927328546217</v>
+      </c>
       <c r="D10" t="n">
         <v>2.66297e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1659.046</v>
       </c>
+      <c r="C11" t="n">
+        <v>2112.565105953716</v>
+      </c>
       <c r="D11" t="n">
         <v>2.67271e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1647.535</v>
       </c>
+      <c r="C12" t="n">
+        <v>2100.758085294226</v>
+      </c>
       <c r="D12" t="n">
         <v>2.68187e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1625.774</v>
       </c>
+      <c r="C13" t="n">
+        <v>2080.598377382642</v>
+      </c>
       <c r="D13" t="n">
         <v>2.68934e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1617.955</v>
       </c>
+      <c r="C14" t="n">
+        <v>2067.815170753907</v>
+      </c>
       <c r="D14" t="n">
         <v>2.6978e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1599.826</v>
       </c>
+      <c r="C15" t="n">
+        <v>2051.022302071356</v>
+      </c>
       <c r="D15" t="n">
         <v>2.70643e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1584.736</v>
       </c>
+      <c r="C16" t="n">
+        <v>2037.195801659356</v>
+      </c>
       <c r="D16" t="n">
         <v>2.71554e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1571.06</v>
       </c>
+      <c r="C17" t="n">
+        <v>2021.458832097063</v>
+      </c>
       <c r="D17" t="n">
         <v>2.72198e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1553.62</v>
       </c>
+      <c r="C18" t="n">
+        <v>2005.466990591064</v>
+      </c>
       <c r="D18" t="n">
         <v>2.73004e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1533.493</v>
       </c>
+      <c r="C19" t="n">
+        <v>1986.389996504737</v>
+      </c>
       <c r="D19" t="n">
         <v>2.73552e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1518.719</v>
       </c>
+      <c r="C20" t="n">
+        <v>1969.857934249273</v>
+      </c>
       <c r="D20" t="n">
         <v>2.74227e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1505.031</v>
       </c>
+      <c r="C21" t="n">
+        <v>1955.1749433572</v>
+      </c>
       <c r="D21" t="n">
         <v>2.7485e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1490.541</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1940.845218339031</v>
       </c>
       <c r="D22" t="n">
         <v>2.75752e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2408.725</v>
       </c>
+      <c r="C2" t="n">
+        <v>2921.433160577775</v>
+      </c>
       <c r="D2" t="n">
         <v>2.24598e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>2041.874</v>
       </c>
+      <c r="C3" t="n">
+        <v>2482.794084647284</v>
+      </c>
       <c r="D3" t="n">
         <v>2.50617e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1955.021</v>
       </c>
+      <c r="C4" t="n">
+        <v>2388.203036179813</v>
+      </c>
       <c r="D4" t="n">
         <v>2.56008e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1922.261</v>
       </c>
+      <c r="C5" t="n">
+        <v>2350.878940357654</v>
+      </c>
       <c r="D5" t="n">
         <v>2.57981e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1859.155</v>
       </c>
+      <c r="C6" t="n">
+        <v>2302.855700055726</v>
+      </c>
       <c r="D6" t="n">
         <v>2.59346e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1842.76</v>
       </c>
+      <c r="C7" t="n">
+        <v>2280.808500268657</v>
+      </c>
       <c r="D7" t="n">
         <v>2.60676e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1801.763</v>
       </c>
+      <c r="C8" t="n">
+        <v>2244.960954437265</v>
+      </c>
       <c r="D8" t="n">
         <v>2.61957e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1771.611</v>
       </c>
+      <c r="C9" t="n">
+        <v>2216.061629847627</v>
+      </c>
       <c r="D9" t="n">
         <v>2.63361e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1749.158</v>
       </c>
+      <c r="C10" t="n">
+        <v>2190.979982563955</v>
+      </c>
       <c r="D10" t="n">
         <v>2.64564e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1712.861</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2158.996789880885</v>
       </c>
       <c r="D11" t="n">
         <v>2.6591e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1972.498</v>
       </c>
+      <c r="C2" t="n">
+        <v>2428.970601936302</v>
+      </c>
       <c r="D2" t="n">
         <v>2.55935e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1832.88</v>
       </c>
+      <c r="C3" t="n">
+        <v>2277.72335825332</v>
+      </c>
       <c r="D3" t="n">
         <v>2.61466e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1789.713</v>
       </c>
+      <c r="C4" t="n">
+        <v>2231.582494689134</v>
+      </c>
       <c r="D4" t="n">
         <v>2.62738e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1762.941</v>
       </c>
+      <c r="C5" t="n">
+        <v>2206.203782906408</v>
+      </c>
       <c r="D5" t="n">
         <v>2.63498e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1732.477</v>
       </c>
+      <c r="C6" t="n">
+        <v>2179.848041482439</v>
+      </c>
       <c r="D6" t="n">
         <v>2.64007e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1710.21</v>
       </c>
+      <c r="C7" t="n">
+        <v>2160.124999805259</v>
+      </c>
       <c r="D7" t="n">
         <v>2.64831e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1695.556</v>
       </c>
+      <c r="C8" t="n">
+        <v>2143.96736136812</v>
+      </c>
       <c r="D8" t="n">
         <v>2.65328e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1675.858</v>
       </c>
+      <c r="C9" t="n">
+        <v>2122.704802615652</v>
+      </c>
       <c r="D9" t="n">
         <v>2.66028e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1649.471</v>
       </c>
+      <c r="C10" t="n">
+        <v>2099.62980335701</v>
+      </c>
       <c r="D10" t="n">
         <v>2.66653e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1637.425</v>
       </c>
+      <c r="C11" t="n">
+        <v>2086.699380408253</v>
+      </c>
       <c r="D11" t="n">
         <v>2.67369e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1620.573</v>
       </c>
+      <c r="C12" t="n">
+        <v>2068.992483857875</v>
+      </c>
       <c r="D12" t="n">
         <v>2.68074e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1597.221</v>
       </c>
+      <c r="C13" t="n">
+        <v>2049.350394846454</v>
+      </c>
       <c r="D13" t="n">
         <v>2.68452e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1574.211</v>
       </c>
+      <c r="C14" t="n">
+        <v>2028.293985029993</v>
+      </c>
       <c r="D14" t="n">
         <v>2.69242e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1558.589</v>
       </c>
+      <c r="C15" t="n">
+        <v>2013.294836278182</v>
+      </c>
       <c r="D15" t="n">
         <v>2.69735e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1556.772</v>
       </c>
+      <c r="C16" t="n">
+        <v>2007.408154294445</v>
+      </c>
       <c r="D16" t="n">
         <v>2.70132e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1534.684</v>
       </c>
+      <c r="C17" t="n">
+        <v>1987.15348425602</v>
+      </c>
       <c r="D17" t="n">
         <v>2.70694e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1513.547</v>
       </c>
+      <c r="C18" t="n">
+        <v>1967.466077201076</v>
+      </c>
       <c r="D18" t="n">
         <v>2.71452e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1503.857</v>
       </c>
+      <c r="C19" t="n">
+        <v>1955.879329291216</v>
+      </c>
       <c r="D19" t="n">
         <v>2.71953e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1481.24</v>
       </c>
+      <c r="C20" t="n">
+        <v>1936.338380936035</v>
+      </c>
       <c r="D20" t="n">
         <v>2.72619e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1479.339</v>
       </c>
+      <c r="C21" t="n">
+        <v>1929.550984018319</v>
+      </c>
       <c r="D21" t="n">
         <v>2.734e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1456.159</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1909.135729054293</v>
       </c>
       <c r="D22" t="n">
         <v>2.73957e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2343.822</v>
       </c>
+      <c r="C2" t="n">
+        <v>2849.109606841207</v>
+      </c>
       <c r="D2" t="n">
         <v>2.28544e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1983.834</v>
       </c>
+      <c r="C3" t="n">
+        <v>2430.054203346974</v>
+      </c>
       <c r="D3" t="n">
         <v>2.52144e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1889.344</v>
       </c>
+      <c r="C4" t="n">
+        <v>2329.309120105403</v>
+      </c>
       <c r="D4" t="n">
         <v>2.57072e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1852.22</v>
       </c>
+      <c r="C5" t="n">
+        <v>2290.175910921893</v>
+      </c>
       <c r="D5" t="n">
         <v>2.58989e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1810.7</v>
       </c>
+      <c r="C6" t="n">
+        <v>2251.45026374047</v>
+      </c>
       <c r="D6" t="n">
         <v>2.60634e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1786.002</v>
       </c>
+      <c r="C7" t="n">
+        <v>2227.752890635576</v>
+      </c>
       <c r="D7" t="n">
         <v>2.62199e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1746.768</v>
       </c>
+      <c r="C8" t="n">
+        <v>2193.693137401565</v>
+      </c>
       <c r="D8" t="n">
         <v>2.63582e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1716.744</v>
       </c>
+      <c r="C9" t="n">
+        <v>2167.135185618064</v>
+      </c>
       <c r="D9" t="n">
         <v>2.65159e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1690.529</v>
       </c>
+      <c r="C10" t="n">
+        <v>2140.707230409683</v>
+      </c>
       <c r="D10" t="n">
         <v>2.66405e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1665.543</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2114.911594572889</v>
       </c>
       <c r="D11" t="n">
         <v>2.67788e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1981.482</v>
       </c>
+      <c r="C2" t="n">
+        <v>2453.049910058739</v>
+      </c>
       <c r="D2" t="n">
         <v>2.5166e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1824.727</v>
       </c>
+      <c r="C3" t="n">
+        <v>2273.869828804703</v>
+      </c>
       <c r="D3" t="n">
         <v>2.5857e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1785.352</v>
       </c>
+      <c r="C4" t="n">
+        <v>2232.472765863288</v>
+      </c>
       <c r="D4" t="n">
         <v>2.60358e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1767.733</v>
       </c>
+      <c r="C5" t="n">
+        <v>2208.419784224196</v>
+      </c>
       <c r="D5" t="n">
         <v>2.61499e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1732.844</v>
       </c>
+      <c r="C6" t="n">
+        <v>2179.148588768236</v>
+      </c>
       <c r="D6" t="n">
         <v>2.62565e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1713.982</v>
       </c>
+      <c r="C7" t="n">
+        <v>2159.527184732122</v>
+      </c>
       <c r="D7" t="n">
         <v>2.63224e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1699</v>
       </c>
+      <c r="C8" t="n">
+        <v>2144.127257671733</v>
+      </c>
       <c r="D8" t="n">
         <v>2.6399e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1681.85</v>
       </c>
+      <c r="C9" t="n">
+        <v>2129.188967580939</v>
+      </c>
       <c r="D9" t="n">
         <v>2.64761e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1665.735</v>
       </c>
+      <c r="C10" t="n">
+        <v>2111.399154531131</v>
+      </c>
       <c r="D10" t="n">
         <v>2.65302e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1642.453</v>
       </c>
+      <c r="C11" t="n">
+        <v>2092.247867514787</v>
+      </c>
       <c r="D11" t="n">
         <v>2.66007e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1636.496</v>
       </c>
+      <c r="C12" t="n">
+        <v>2081.788064830518</v>
+      </c>
       <c r="D12" t="n">
         <v>2.66771e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1614.385</v>
       </c>
+      <c r="C13" t="n">
+        <v>2062.726926706182</v>
+      </c>
       <c r="D13" t="n">
         <v>2.67451e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1600.749</v>
       </c>
+      <c r="C14" t="n">
+        <v>2047.540372907699</v>
+      </c>
       <c r="D14" t="n">
         <v>2.68093e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1589.961</v>
       </c>
+      <c r="C15" t="n">
+        <v>2036.222950577755</v>
+      </c>
       <c r="D15" t="n">
         <v>2.68826e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1563.783</v>
       </c>
+      <c r="C16" t="n">
+        <v>2013.041521911694</v>
+      </c>
       <c r="D16" t="n">
         <v>2.69432e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1548.647</v>
       </c>
+      <c r="C17" t="n">
+        <v>1997.733505553642</v>
+      </c>
       <c r="D17" t="n">
         <v>2.7027e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1545.171</v>
       </c>
+      <c r="C18" t="n">
+        <v>1989.964371053056</v>
+      </c>
       <c r="D18" t="n">
         <v>2.70891e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1517.703</v>
       </c>
+      <c r="C19" t="n">
+        <v>1965.978165375447</v>
+      </c>
       <c r="D19" t="n">
         <v>2.71565e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1495.006</v>
       </c>
+      <c r="C20" t="n">
+        <v>1946.837721534329</v>
+      </c>
       <c r="D20" t="n">
         <v>2.72242e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1489.912</v>
       </c>
+      <c r="C21" t="n">
+        <v>1936.981156903518</v>
+      </c>
       <c r="D21" t="n">
         <v>2.73186e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1483.075</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1926.561544843088</v>
       </c>
       <c r="D22" t="n">
         <v>2.73981e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>2256.101</v>
       </c>
+      <c r="C2" t="n">
+        <v>2795.152781276797</v>
+      </c>
       <c r="D2" t="n">
         <v>2.31914e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1906.253</v>
       </c>
+      <c r="C3" t="n">
+        <v>2368.387132520875</v>
+      </c>
       <c r="D3" t="n">
         <v>2.56388e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1832.576</v>
       </c>
+      <c r="C4" t="n">
+        <v>2283.04589683425</v>
+      </c>
       <c r="D4" t="n">
         <v>2.60971e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1778.58</v>
       </c>
+      <c r="C5" t="n">
+        <v>2234.386842357108</v>
+      </c>
       <c r="D5" t="n">
         <v>2.6273e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1762.227</v>
       </c>
+      <c r="C6" t="n">
+        <v>2213.411973457326</v>
+      </c>
       <c r="D6" t="n">
         <v>2.64217e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1724.641</v>
       </c>
+      <c r="C7" t="n">
+        <v>2180.851164567806</v>
+      </c>
       <c r="D7" t="n">
         <v>2.65402e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1695.8</v>
       </c>
+      <c r="C8" t="n">
+        <v>2154.009967347798</v>
+      </c>
       <c r="D8" t="n">
         <v>2.66921e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1670.12</v>
       </c>
+      <c r="C9" t="n">
+        <v>2128.699843244138</v>
+      </c>
       <c r="D9" t="n">
         <v>2.68514e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1642.478</v>
       </c>
+      <c r="C10" t="n">
+        <v>2105.171844344286</v>
+      </c>
       <c r="D10" t="n">
         <v>2.69867e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1621.088</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2080.571736777088</v>
       </c>
       <c r="D11" t="n">
         <v>2.71307e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>1834.501</v>
       </c>
+      <c r="C2" t="n">
+        <v>2313.832839887632</v>
+      </c>
       <c r="D2" t="n">
         <v>2.59609e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1730.541</v>
       </c>
+      <c r="C3" t="n">
+        <v>2186.000976816722</v>
+      </c>
       <c r="D3" t="n">
         <v>2.65467e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1692.576</v>
       </c>
+      <c r="C4" t="n">
+        <v>2147.710375428213</v>
+      </c>
       <c r="D4" t="n">
         <v>2.67275e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1657.131</v>
       </c>
+      <c r="C5" t="n">
+        <v>2118.277941507281</v>
+      </c>
       <c r="D5" t="n">
         <v>2.68375e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1638.692</v>
       </c>
+      <c r="C6" t="n">
+        <v>2097.669870637065</v>
+      </c>
       <c r="D6" t="n">
         <v>2.69563e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1615.773</v>
       </c>
+      <c r="C7" t="n">
+        <v>2078.043321610151</v>
+      </c>
       <c r="D7" t="n">
         <v>2.70626e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1583.603</v>
       </c>
+      <c r="C8" t="n">
+        <v>2048.499390947482</v>
+      </c>
       <c r="D8" t="n">
         <v>2.71799e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1578.355</v>
       </c>
+      <c r="C9" t="n">
+        <v>2040.355551598688</v>
+      </c>
       <c r="D9" t="n">
         <v>2.7292e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1553.738</v>
       </c>
+      <c r="C10" t="n">
+        <v>2019.57003763554</v>
+      </c>
       <c r="D10" t="n">
         <v>2.73763e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1533.59</v>
       </c>
+      <c r="C11" t="n">
+        <v>1999.220764670188</v>
+      </c>
       <c r="D11" t="n">
         <v>2.74687e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1520.407</v>
       </c>
+      <c r="C12" t="n">
+        <v>1987.173997103841</v>
+      </c>
       <c r="D12" t="n">
         <v>2.75528e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1502.207</v>
       </c>
+      <c r="C13" t="n">
+        <v>1968.045472777215</v>
+      </c>
       <c r="D13" t="n">
         <v>2.76469e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1487.358</v>
       </c>
+      <c r="C14" t="n">
+        <v>1952.28341286356</v>
+      </c>
       <c r="D14" t="n">
         <v>2.77318e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1474.18</v>
       </c>
+      <c r="C15" t="n">
+        <v>1937.661299441232</v>
+      </c>
       <c r="D15" t="n">
         <v>2.78166e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1458.19</v>
       </c>
+      <c r="C16" t="n">
+        <v>1923.121761604705</v>
+      </c>
       <c r="D16" t="n">
         <v>2.79004e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1452.395</v>
       </c>
+      <c r="C17" t="n">
+        <v>1914.027844689531</v>
+      </c>
       <c r="D17" t="n">
         <v>2.79878e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1431.534</v>
       </c>
+      <c r="C18" t="n">
+        <v>1893.885812411079</v>
+      </c>
       <c r="D18" t="n">
         <v>2.80715e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1426.919</v>
       </c>
+      <c r="C19" t="n">
+        <v>1887.017700620966</v>
+      </c>
       <c r="D19" t="n">
         <v>2.8148e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1402.282</v>
       </c>
+      <c r="C20" t="n">
+        <v>1865.140334656425</v>
+      </c>
       <c r="D20" t="n">
         <v>2.82385e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1388.654</v>
       </c>
+      <c r="C21" t="n">
+        <v>1850.580375437595</v>
+      </c>
       <c r="D21" t="n">
         <v>2.8306e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1381.295</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1841.053560744098</v>
       </c>
       <c r="D22" t="n">
         <v>2.83893e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1793.609</v>
       </c>
+      <c r="C2" t="n">
+        <v>2427.753738354898</v>
+      </c>
       <c r="D2" t="n">
         <v>2.56611e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1447.856</v>
       </c>
+      <c r="C3" t="n">
+        <v>1957.347899869617</v>
+      </c>
       <c r="D3" t="n">
         <v>2.79414e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1374.545</v>
       </c>
+      <c r="C4" t="n">
+        <v>1872.712238790338</v>
+      </c>
       <c r="D4" t="n">
         <v>2.82684e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1334.922</v>
       </c>
+      <c r="C5" t="n">
+        <v>1834.635211109964</v>
+      </c>
       <c r="D5" t="n">
         <v>2.83732e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1308.322</v>
       </c>
+      <c r="C6" t="n">
+        <v>1806.656960013337</v>
+      </c>
       <c r="D6" t="n">
         <v>2.84756e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1282.416</v>
       </c>
+      <c r="C7" t="n">
+        <v>1785.070966453727</v>
+      </c>
       <c r="D7" t="n">
         <v>2.85869e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1255.304</v>
       </c>
+      <c r="C8" t="n">
+        <v>1759.056295456409</v>
+      </c>
       <c r="D8" t="n">
         <v>2.86851e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1232.165</v>
       </c>
+      <c r="C9" t="n">
+        <v>1736.132259088317</v>
+      </c>
       <c r="D9" t="n">
         <v>2.88131e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1218.456</v>
       </c>
+      <c r="C10" t="n">
+        <v>1723.782430278108</v>
+      </c>
       <c r="D10" t="n">
         <v>2.89084e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1188.819</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1694.917802196109</v>
       </c>
       <c r="D11" t="n">
         <v>2.90098e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -565,7 +565,7 @@
         <v>2087.234</v>
       </c>
       <c r="C2" t="n">
-        <v>2534.148354975808</v>
+        <v>10737.62557449148</v>
       </c>
       <c r="D2" t="n">
         <v>2.47316e-07</v>
@@ -598,10 +598,7 @@
         <v>-18797.5310808025</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.53059518513909e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2849.137192048378</v>
+        <v>-7564.629672672376</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000036296e-08</v>
@@ -618,7 +615,7 @@
         <v>1965.1</v>
       </c>
       <c r="C3" t="n">
-        <v>2402.661038330325</v>
+        <v>11473.41275963081</v>
       </c>
       <c r="D3" t="n">
         <v>2.53993e-07</v>
@@ -651,10 +648,7 @@
         <v>-19879.69519812554</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.268148809046955e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2733.239153431004</v>
+        <v>-8464.433062945536</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000004e-08</v>
@@ -671,7 +665,7 @@
         <v>1910.832</v>
       </c>
       <c r="C4" t="n">
-        <v>2352.762856303859</v>
+        <v>11435.25554247945</v>
       </c>
       <c r="D4" t="n">
         <v>2.56606e-07</v>
@@ -704,10 +698,7 @@
         <v>-20482.23161651968</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.069725929926401e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2672.031911764515</v>
+        <v>-8486.035594114595</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000046e-08</v>
@@ -724,7 +715,7 @@
         <v>1871.58</v>
       </c>
       <c r="C5" t="n">
-        <v>2311.662060100506</v>
+        <v>11355.46690270384</v>
       </c>
       <c r="D5" t="n">
         <v>2.58279e-07</v>
@@ -757,10 +748,7 @@
         <v>-20816.7812114036</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.033644803438425e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2628.085206854489</v>
+        <v>-8444.489740021905</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002743e-08</v>
@@ -777,7 +765,7 @@
         <v>1830.397</v>
       </c>
       <c r="C6" t="n">
-        <v>2275.940382116427</v>
+        <v>11840.03445042299</v>
       </c>
       <c r="D6" t="n">
         <v>2.59908e-07</v>
@@ -810,10 +798,7 @@
         <v>-19846.41411952285</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.25560870921364e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2590.7180302887</v>
+        <v>-8980.148380980039</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -830,7 +815,7 @@
         <v>1804.514</v>
       </c>
       <c r="C7" t="n">
-        <v>2248.158537176274</v>
+        <v>11610.98840517946</v>
       </c>
       <c r="D7" t="n">
         <v>2.61229e-07</v>
@@ -863,10 +848,7 @@
         <v>-20002.59579901699</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.987011567362903e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2556.556331153966</v>
+        <v>-8775.022521662702</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000002028e-08</v>
@@ -883,7 +865,7 @@
         <v>1774.828</v>
       </c>
       <c r="C8" t="n">
-        <v>2223.486004257281</v>
+        <v>11812.75205288622</v>
       </c>
       <c r="D8" t="n">
         <v>2.6261e-07</v>
@@ -916,10 +898,7 @@
         <v>-20126.9531701673</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.758849038161764e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2524.069810098983</v>
+        <v>-9013.676594744602</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000238e-08</v>
@@ -936,7 +915,7 @@
         <v>1757.883</v>
       </c>
       <c r="C9" t="n">
-        <v>2203.049810154411</v>
+        <v>11855.23202172622</v>
       </c>
       <c r="D9" t="n">
         <v>2.63999e-07</v>
@@ -969,10 +948,7 @@
         <v>-21226.34727106131</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.828193003699344e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2493.646315708108</v>
+        <v>-9087.43189262373</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000062e-08</v>
@@ -989,7 +965,7 @@
         <v>1724.039</v>
       </c>
       <c r="C10" t="n">
-        <v>2174.492412632753</v>
+        <v>12051.95261239851</v>
       </c>
       <c r="D10" t="n">
         <v>2.64978e-07</v>
@@ -1022,10 +998,7 @@
         <v>-20264.89165288859</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.146666063726302e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2465.268795843359</v>
+        <v>-9314.633119254437</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000018e-08</v>
@@ -1042,7 +1015,7 @@
         <v>1702.963</v>
       </c>
       <c r="C11" t="n">
-        <v>2154.015390007403</v>
+        <v>11843.92415139435</v>
       </c>
       <c r="D11" t="n">
         <v>2.65937e-07</v>
@@ -1075,10 +1048,7 @@
         <v>-20317.45519032307</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.047578772244435e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2438.58882605475</v>
+        <v>-9123.435566813492</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000001203e-08</v>
@@ -1241,7 +1211,7 @@
         <v>1843.244</v>
       </c>
       <c r="C2" t="n">
-        <v>2334.677364859909</v>
+        <v>11915.61487386078</v>
       </c>
       <c r="D2" t="n">
         <v>2.56788e-07</v>
@@ -1274,10 +1244,7 @@
         <v>-20428.7082248694</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.323747969975969e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2586.84725592886</v>
+        <v>-9026.597996064493</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000845e-08</v>
@@ -1294,7 +1261,7 @@
         <v>1726.966</v>
       </c>
       <c r="C3" t="n">
-        <v>2186.837256830815</v>
+        <v>12636.60359749908</v>
       </c>
       <c r="D3" t="n">
         <v>2.63289e-07</v>
@@ -1327,10 +1294,7 @@
         <v>-20994.09988761647</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.243424914054024e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2472.02471984687</v>
+        <v>-9906.027912612801</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001272e-08</v>
@@ -1347,7 +1311,7 @@
         <v>1688.105</v>
       </c>
       <c r="C4" t="n">
-        <v>2147.66082093477</v>
+        <v>12522.71409217288</v>
       </c>
       <c r="D4" t="n">
         <v>2.65145e-07</v>
@@ -1380,10 +1344,7 @@
         <v>-21042.93744743958</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.487304966651269e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2429.667557780532</v>
+        <v>-9830.409767850519</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000008256e-08</v>
@@ -1400,7 +1361,7 @@
         <v>1658.146</v>
       </c>
       <c r="C5" t="n">
-        <v>2119.586294400986</v>
+        <v>13070.40270211299</v>
       </c>
       <c r="D5" t="n">
         <v>2.66116e-07</v>
@@ -1433,10 +1394,7 @@
         <v>-21143.3318205291</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.412624397153866e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2398.365200523783</v>
+        <v>-10419.86092269257</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000002506e-08</v>
@@ -1453,7 +1411,7 @@
         <v>1627.795</v>
       </c>
       <c r="C6" t="n">
-        <v>2092.628087995692</v>
+        <v>12856.96736659893</v>
       </c>
       <c r="D6" t="n">
         <v>2.6729e-07</v>
@@ -1486,10 +1444,7 @@
         <v>-20152.54411207497</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.487790344343117e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2369.019706315526</v>
+        <v>-10227.0130371515</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000115e-08</v>
@@ -1506,7 +1461,7 @@
         <v>1613.135</v>
       </c>
       <c r="C7" t="n">
-        <v>2076.804889353468</v>
+        <v>13264.07987658852</v>
       </c>
       <c r="D7" t="n">
         <v>2.68413e-07</v>
@@ -1539,10 +1494,7 @@
         <v>-21099.59584119752</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.122977023555733e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2342.644976134678</v>
+        <v>-10670.61658535674</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000048e-08</v>
@@ -1559,7 +1511,7 @@
         <v>1593.699</v>
       </c>
       <c r="C8" t="n">
-        <v>2055.07039667952</v>
+        <v>13038.81881392879</v>
       </c>
       <c r="D8" t="n">
         <v>2.69319e-07</v>
@@ -1592,10 +1544,7 @@
         <v>-21088.49644340535</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.234150516350621e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2318.814309752132</v>
+        <v>-10461.02200392949</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000076e-08</v>
@@ -1612,7 +1561,7 @@
         <v>1569.828</v>
       </c>
       <c r="C9" t="n">
-        <v>2033.356972168813</v>
+        <v>13180.99773010443</v>
       </c>
       <c r="D9" t="n">
         <v>2.70232e-07</v>
@@ -1645,10 +1594,7 @@
         <v>-20220.06887163307</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.632902926560166e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2297.196617573889</v>
+        <v>-10626.81806324829</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000877e-08</v>
@@ -1665,7 +1611,7 @@
         <v>1554.666</v>
       </c>
       <c r="C10" t="n">
-        <v>2019.035590468495</v>
+        <v>12892.47398048587</v>
       </c>
       <c r="D10" t="n">
         <v>2.71116e-07</v>
@@ -1698,10 +1644,7 @@
         <v>-20248.02688448182</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.828493312931939e-12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2277.325681088746</v>
+        <v>-10350.07779426758</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1718,7 +1661,7 @@
         <v>1537.197</v>
       </c>
       <c r="C11" t="n">
-        <v>2002.520152707067</v>
+        <v>12906.55618368748</v>
       </c>
       <c r="D11" t="n">
         <v>2.71722e-07</v>
@@ -1751,10 +1694,7 @@
         <v>-20050.91065421495</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.122233241569001e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2258.278862675067</v>
+        <v>-10380.29475581633</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004632e-08</v>
@@ -1771,7 +1711,7 @@
         <v>1521.409</v>
       </c>
       <c r="C12" t="n">
-        <v>1986.751471914043</v>
+        <v>13356.9999748011</v>
       </c>
       <c r="D12" t="n">
         <v>2.72603e-07</v>
@@ -1804,10 +1744,7 @@
         <v>-20123.38766908173</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.206565981022582e-14</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2240.091406700813</v>
+        <v>-10861.44799757738</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -1824,7 +1761,7 @@
         <v>1509.958</v>
       </c>
       <c r="C13" t="n">
-        <v>1973.103985497663</v>
+        <v>13401.17085512893</v>
       </c>
       <c r="D13" t="n">
         <v>2.73371e-07</v>
@@ -1857,10 +1794,7 @@
         <v>-20061.183436252</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.002991068050196e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2222.104134904337</v>
+        <v>-10923.69490521943</v>
       </c>
       <c r="AA13" t="n">
         <v>1.00000000000118e-08</v>
@@ -1877,7 +1811,7 @@
         <v>1490.308</v>
       </c>
       <c r="C14" t="n">
-        <v>1955.044679701886</v>
+        <v>717.4695063062272</v>
       </c>
       <c r="D14" t="n">
         <v>2.74088e-07</v>
@@ -1910,16 +1844,13 @@
         <v>-19212.8954625368</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.037389633769716e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2204.560726432944</v>
+        <v>543.6224379836989</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.00000000000048e-08</v>
+        <v>2.636500751827648e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8195006339956028</v>
+        <v>0.9449774452240691</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1482.278</v>
       </c>
       <c r="C15" t="n">
-        <v>1945.559437188276</v>
+        <v>13530.88085646506</v>
       </c>
       <c r="D15" t="n">
         <v>2.74915e-07</v>
@@ -1963,10 +1894,7 @@
         <v>-20039.83720390238</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.89597990234963e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2186.438826776923</v>
+        <v>-11091.5081658135</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -1983,7 +1911,7 @@
         <v>1469.337</v>
       </c>
       <c r="C16" t="n">
-        <v>1931.170152400852</v>
+        <v>13617.64151278529</v>
       </c>
       <c r="D16" t="n">
         <v>2.75645e-07</v>
@@ -2016,10 +1944,7 @@
         <v>-19962.32828533247</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.88081800803275e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2168.44960213808</v>
+        <v>-11196.90061015472</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000814e-08</v>
@@ -2036,7 +1961,7 @@
         <v>1454.173</v>
       </c>
       <c r="C17" t="n">
-        <v>1917.216831710167</v>
+        <v>13644.12972706181</v>
       </c>
       <c r="D17" t="n">
         <v>2.76371e-07</v>
@@ -2069,10 +1994,7 @@
         <v>-19870.82377851203</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.394618212055567e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2150.697390267059</v>
+        <v>-11240.74669466448</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000105e-08</v>
@@ -2089,7 +2011,7 @@
         <v>1440.784</v>
       </c>
       <c r="C18" t="n">
-        <v>1902.504279255319</v>
+        <v>13713.58566542842</v>
       </c>
       <c r="D18" t="n">
         <v>2.77145e-07</v>
@@ -2122,10 +2044,7 @@
         <v>-19817.71831674836</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.780509939592464e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2132.505116102536</v>
+        <v>-11329.07119918537</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000376e-08</v>
@@ -2142,7 +2061,7 @@
         <v>1427.898</v>
       </c>
       <c r="C19" t="n">
-        <v>1889.071253522337</v>
+        <v>689.5293975903463</v>
       </c>
       <c r="D19" t="n">
         <v>2.77966e-07</v>
@@ -2175,16 +2094,13 @@
         <v>-19731.54103314185</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.256970417595998e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2114.301664692274</v>
+        <v>498.8965089889762</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000429e-08</v>
+        <v>1.214754758943311e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8208555340040277</v>
+        <v>0.9982811123344245</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1412.093</v>
       </c>
       <c r="C20" t="n">
-        <v>1874.473569673127</v>
+        <v>684.3929183225538</v>
       </c>
       <c r="D20" t="n">
         <v>2.78655e-07</v>
@@ -2228,16 +2144,13 @@
         <v>-19632.73673105193</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.1907409611764e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2096.065770975982</v>
+        <v>502.467876008696</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000033e-08</v>
+        <v>1.159170915567881e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8211350358494037</v>
+        <v>0.995995869684226</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1393.428</v>
       </c>
       <c r="C21" t="n">
-        <v>1855.233746186314</v>
+        <v>678.8716564687975</v>
       </c>
       <c r="D21" t="n">
         <v>2.79416e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-18671.83959492642</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.196065742501888e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2077.467099719895</v>
+        <v>510.3104896597935</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.00000000000388e-08</v>
+        <v>1.758346103146859e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8214261988556832</v>
+        <v>0.9708099036988457</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1383.297</v>
       </c>
       <c r="C22" t="n">
-        <v>1844.604965443586</v>
+        <v>673.1788991469942</v>
       </c>
       <c r="D22" t="n">
         <v>2.80047e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-19571.3656559198</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.672082578549202e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2057.764452642697</v>
+        <v>492.3509018683569</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.00000000000319e-08</v>
+        <v>1.478773665365487e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8217278797467344</v>
+        <v>0.9828628459378257</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>2011.455</v>
       </c>
       <c r="C2" t="n">
-        <v>2474.255249033753</v>
+        <v>11107.03582136518</v>
       </c>
       <c r="D2" t="n">
         <v>2.50243e-07</v>
@@ -2533,10 +2440,7 @@
         <v>-21891.96037960164</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.138344611660326e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2752.842315600089</v>
+        <v>-8040.131839779975</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000902e-08</v>
@@ -2553,7 +2457,7 @@
         <v>1875.195</v>
       </c>
       <c r="C3" t="n">
-        <v>2320.341544920394</v>
+        <v>11814.69300599354</v>
       </c>
       <c r="D3" t="n">
         <v>2.5758e-07</v>
@@ -2586,10 +2490,7 @@
         <v>-21436.88077054089</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.754115348614548e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2628.283211287756</v>
+        <v>-8919.077229027771</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000166e-08</v>
@@ -2606,7 +2507,7 @@
         <v>1821.97</v>
       </c>
       <c r="C4" t="n">
-        <v>2269.073986556991</v>
+        <v>11664.99105060892</v>
       </c>
       <c r="D4" t="n">
         <v>2.59576e-07</v>
@@ -2639,10 +2540,7 @@
         <v>-20318.60135010019</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.478673788885344e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2579.531278787112</v>
+        <v>-8810.22170969748</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000042e-08</v>
@@ -2659,7 +2557,7 @@
         <v>1791.459</v>
       </c>
       <c r="C5" t="n">
-        <v>2238.680826314071</v>
+        <v>11823.69133707342</v>
       </c>
       <c r="D5" t="n">
         <v>2.61069e-07</v>
@@ -2692,10 +2590,7 @@
         <v>-20376.43661082203</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.20139928796489e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2544.806429736098</v>
+        <v>-9006.749604119737</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000003e-08</v>
@@ -2712,7 +2607,7 @@
         <v>1758.682</v>
       </c>
       <c r="C6" t="n">
-        <v>2210.562658966077</v>
+        <v>11621.87312987859</v>
       </c>
       <c r="D6" t="n">
         <v>2.62175e-07</v>
@@ -2745,10 +2640,7 @@
         <v>-19387.00131202219</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.883837761576438e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2514.833913368448</v>
+        <v>-8824.085981522985</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000031e-08</v>
@@ -2765,7 +2657,7 @@
         <v>1750.934</v>
       </c>
       <c r="C7" t="n">
-        <v>2200.099462950644</v>
+        <v>12053.08351562189</v>
       </c>
       <c r="D7" t="n">
         <v>2.63351e-07</v>
@@ -2798,10 +2690,7 @@
         <v>-21490.53898041881</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.319542082488493e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2488.611740322311</v>
+        <v>-9294.339331328072</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000043e-08</v>
@@ -2818,7 +2707,7 @@
         <v>1715.923</v>
       </c>
       <c r="C8" t="n">
-        <v>2168.040071920074</v>
+        <v>12153.77477451181</v>
       </c>
       <c r="D8" t="n">
         <v>2.64473e-07</v>
@@ -2851,10 +2740,7 @@
         <v>-19499.41387650481</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56028147395294e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2463.0707411901</v>
+        <v>-9422.467020411465</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -2871,7 +2757,7 @@
         <v>1703.106</v>
       </c>
       <c r="C9" t="n">
-        <v>2154.907056216087</v>
+        <v>11913.63511212351</v>
       </c>
       <c r="D9" t="n">
         <v>2.65448e-07</v>
@@ -2904,10 +2790,7 @@
         <v>-20565.56710754223</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.345642398065806e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2439.317835678697</v>
+        <v>-9196.818631672282</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -2924,7 +2807,7 @@
         <v>1691.294</v>
       </c>
       <c r="C10" t="n">
-        <v>2139.927328546217</v>
+        <v>12337.45405940329</v>
       </c>
       <c r="D10" t="n">
         <v>2.66297e-07</v>
@@ -2957,10 +2840,7 @@
         <v>-21605.80827750863</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.392507189518107e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2416.275690543898</v>
+        <v>-9653.553378150793</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000314e-08</v>
@@ -2977,7 +2857,7 @@
         <v>1659.046</v>
       </c>
       <c r="C11" t="n">
-        <v>2112.565105953716</v>
+        <v>12085.69635308302</v>
       </c>
       <c r="D11" t="n">
         <v>2.67271e-07</v>
@@ -3010,10 +2890,7 @@
         <v>-19503.03704594555</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.263849689963189e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2394.38591193977</v>
+        <v>-9414.927889646558</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000078e-08</v>
@@ -3030,7 +2907,7 @@
         <v>1647.535</v>
       </c>
       <c r="C12" t="n">
-        <v>2100.758085294226</v>
+        <v>12502.83597609048</v>
       </c>
       <c r="D12" t="n">
         <v>2.68187e-07</v>
@@ -3063,10 +2940,7 @@
         <v>-20471.94954415383</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.502207539141519e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2372.78961248076</v>
+        <v>-9864.76098606191</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000131e-08</v>
@@ -3083,7 +2957,7 @@
         <v>1625.774</v>
       </c>
       <c r="C13" t="n">
-        <v>2080.598377382642</v>
+        <v>12260.65260390468</v>
       </c>
       <c r="D13" t="n">
         <v>2.68934e-07</v>
@@ -3116,10 +2990,7 @@
         <v>-19494.71640114519</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.665955034596872e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2351.856645666194</v>
+        <v>-9633.909719826392</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000002573e-08</v>
@@ -3136,7 +3007,7 @@
         <v>1617.955</v>
       </c>
       <c r="C14" t="n">
-        <v>2067.815170753907</v>
+        <v>12317.45655730029</v>
       </c>
       <c r="D14" t="n">
         <v>2.6978e-07</v>
@@ -3169,10 +3040,7 @@
         <v>-20545.21390106838</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.856140758154704e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2331.681342579034</v>
+        <v>-9711.684072561242</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000002e-08</v>
@@ -3189,7 +3057,7 @@
         <v>1599.826</v>
       </c>
       <c r="C15" t="n">
-        <v>2051.022302071356</v>
+        <v>755.4116990318543</v>
       </c>
       <c r="D15" t="n">
         <v>2.70643e-07</v>
@@ -3222,16 +3090,13 @@
         <v>-20368.10164579641</v>
       </c>
       <c r="Y15" t="n">
-        <v>123.1584967167218</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2420.312072086623</v>
+        <v>492.0247796733312</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.499795632128715e-08</v>
+        <v>1.292832633979948e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.7988401975565512</v>
+        <v>0.9859076688994823</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3107,7 @@
         <v>1584.736</v>
       </c>
       <c r="C16" t="n">
-        <v>2037.195801659356</v>
+        <v>747.9814460002273</v>
       </c>
       <c r="D16" t="n">
         <v>2.71554e-07</v>
@@ -3275,16 +3140,13 @@
         <v>-20435.36029162877</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.137276585033875e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2291.385284074499</v>
+        <v>491.3979370362943</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.302962007373681e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8199641689625303</v>
+        <v>0.9844545800939234</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3157,7 @@
         <v>1571.06</v>
       </c>
       <c r="C17" t="n">
-        <v>2021.458832097063</v>
+        <v>742.0282805362476</v>
       </c>
       <c r="D17" t="n">
         <v>2.72198e-07</v>
@@ -3328,16 +3190,13 @@
         <v>-20396.65667646144</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.91240828538836e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2272.177152141455</v>
+        <v>497.6768945866442</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000009001e-08</v>
+        <v>1.156567892787715e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8202555761943258</v>
+        <v>0.9900935151309244</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3207,7 @@
         <v>1553.62</v>
       </c>
       <c r="C18" t="n">
-        <v>2005.466990591064</v>
+        <v>734.8111627398306</v>
       </c>
       <c r="D18" t="n">
         <v>2.73004e-07</v>
@@ -3381,16 +3240,13 @@
         <v>-20335.01623703157</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.248311337201449e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2253.051247256828</v>
+        <v>501.7096615123477</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000003353e-08</v>
+        <v>1.361334381540027e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.820535013514108</v>
+        <v>0.9855518799989403</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3257,7 @@
         <v>1533.493</v>
       </c>
       <c r="C19" t="n">
-        <v>1986.389996504737</v>
+        <v>728.5512718551507</v>
       </c>
       <c r="D19" t="n">
         <v>2.73552e-07</v>
@@ -3434,16 +3290,13 @@
         <v>-19346.80571314451</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.615370707962783e-12</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2234.039382056779</v>
+        <v>493.2201059606239</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>1.052865667348267e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8208304562524634</v>
+        <v>0.9999195083747934</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3307,7 @@
         <v>1518.719</v>
       </c>
       <c r="C20" t="n">
-        <v>1969.857934249273</v>
+        <v>12792.01872143323</v>
       </c>
       <c r="D20" t="n">
         <v>2.74227e-07</v>
@@ -3487,10 +3340,7 @@
         <v>-19225.54669226714</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.920315953475424e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2215.098580596615</v>
+        <v>-10307.02062632307</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000001e-08</v>
@@ -3507,7 +3357,7 @@
         <v>1505.031</v>
       </c>
       <c r="C21" t="n">
-        <v>1955.1749433572</v>
+        <v>715.9436414680393</v>
       </c>
       <c r="D21" t="n">
         <v>2.7485e-07</v>
@@ -3540,16 +3390,13 @@
         <v>-19240.60136413622</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.015057859175186e-10</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2196.289567146322</v>
+        <v>484.187287890364</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000031e-08</v>
+        <v>1.028840192234787e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8214079875070345</v>
+        <v>0.9997801974180512</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3407,7 @@
         <v>1490.541</v>
       </c>
       <c r="C22" t="n">
-        <v>1940.845218339031</v>
+        <v>12964.22222718345</v>
       </c>
       <c r="D22" t="n">
         <v>2.75752e-07</v>
@@ -3593,10 +3440,7 @@
         <v>-19177.58072070149</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.770150961833606e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2177.645820512686</v>
+        <v>-10519.24646478044</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000002e-08</v>
@@ -3759,7 +3603,7 @@
         <v>2408.725</v>
       </c>
       <c r="C2" t="n">
-        <v>2921.433160577775</v>
+        <v>10446.64442179768</v>
       </c>
       <c r="D2" t="n">
         <v>2.24598e-07</v>
@@ -3792,10 +3636,7 @@
         <v>-16596.43705457958</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.086883614155678e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3150.041474697055</v>
+        <v>-6856.154779771625</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002127e-08</v>
@@ -3812,7 +3653,7 @@
         <v>2041.874</v>
       </c>
       <c r="C3" t="n">
-        <v>2482.794084647284</v>
+        <v>10879.54309341403</v>
       </c>
       <c r="D3" t="n">
         <v>2.50617e-07</v>
@@ -3845,10 +3686,7 @@
         <v>-18039.68739839427</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.953758495807705e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2813.683736807206</v>
+        <v>-7761.771920686305</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000092e-08</v>
@@ -3865,7 +3703,7 @@
         <v>1955.021</v>
       </c>
       <c r="C4" t="n">
-        <v>2388.203036179813</v>
+        <v>10964.3214404406</v>
       </c>
       <c r="D4" t="n">
         <v>2.56008e-07</v>
@@ -3898,10 +3736,7 @@
         <v>-19576.86477097476</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.587305870153576e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2723.73192417196</v>
+        <v>-7958.713972410918</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000007256e-08</v>
@@ -3918,7 +3753,7 @@
         <v>1922.261</v>
       </c>
       <c r="C5" t="n">
-        <v>2350.878940357654</v>
+        <v>11269.72195270348</v>
       </c>
       <c r="D5" t="n">
         <v>2.57981e-07</v>
@@ -3951,10 +3786,7 @@
         <v>-21528.52451899476</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.017523991552934e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2674.843221352956</v>
+        <v>-8324.370535869417</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000008e-08</v>
@@ -3971,7 +3803,7 @@
         <v>1859.155</v>
       </c>
       <c r="C6" t="n">
-        <v>2302.855700055726</v>
+        <v>11276.20536308243</v>
       </c>
       <c r="D6" t="n">
         <v>2.59346e-07</v>
@@ -4004,10 +3836,7 @@
         <v>-18971.86041012717</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.564685976818668e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2633.010412677293</v>
+        <v>-8369.497533647456</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000135e-08</v>
@@ -4024,7 +3853,7 @@
         <v>1842.76</v>
       </c>
       <c r="C7" t="n">
-        <v>2280.808500268657</v>
+        <v>11796.22520780285</v>
       </c>
       <c r="D7" t="n">
         <v>2.60676e-07</v>
@@ -4057,10 +3886,7 @@
         <v>-21101.02260573204</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.699355603460853e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2592.781821596367</v>
+        <v>-8941.996142383376</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -4077,7 +3903,7 @@
         <v>1801.763</v>
       </c>
       <c r="C8" t="n">
-        <v>2244.960954437265</v>
+        <v>11642.22980999481</v>
       </c>
       <c r="D8" t="n">
         <v>2.61957e-07</v>
@@ -4110,10 +3936,7 @@
         <v>-20113.85998948934</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.600960766084204e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2554.027386601243</v>
+        <v>-8815.934510120665</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000001678e-08</v>
@@ -4130,7 +3953,7 @@
         <v>1771.611</v>
       </c>
       <c r="C9" t="n">
-        <v>2216.061629847627</v>
+        <v>11816.75956160238</v>
       </c>
       <c r="D9" t="n">
         <v>2.63361e-07</v>
@@ -4163,10 +3986,7 @@
         <v>-20281.37775214522</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.421581870159603e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2516.5753119736</v>
+        <v>-9030.539049489147</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000057e-08</v>
@@ -4183,7 +4003,7 @@
         <v>1749.158</v>
       </c>
       <c r="C10" t="n">
-        <v>2190.979982563955</v>
+        <v>11950.78223800101</v>
       </c>
       <c r="D10" t="n">
         <v>2.64564e-07</v>
@@ -4216,10 +4036,7 @@
         <v>-21379.63591990633</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.339855109240715e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2480.550825597673</v>
+        <v>-9199.570469306227</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4236,7 +4053,7 @@
         <v>1712.861</v>
       </c>
       <c r="C11" t="n">
-        <v>2158.996789880885</v>
+        <v>12143.35054801704</v>
       </c>
       <c r="D11" t="n">
         <v>2.6591e-07</v>
@@ -4269,10 +4086,7 @@
         <v>-20420.19956460702</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.036382452996853e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2446.944159903048</v>
+        <v>-9428.909366242098</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -4435,7 +4249,7 @@
         <v>1972.498</v>
       </c>
       <c r="C2" t="n">
-        <v>2428.970601936302</v>
+        <v>10691.00634750893</v>
       </c>
       <c r="D2" t="n">
         <v>2.55935e-07</v>
@@ -4468,10 +4282,7 @@
         <v>-19828.45798244592</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.542881904764241e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2701.831590606215</v>
+        <v>-7664.648467145056</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000112e-08</v>
@@ -4488,7 +4299,7 @@
         <v>1832.88</v>
       </c>
       <c r="C3" t="n">
-        <v>2277.72335825332</v>
+        <v>11400.81219446142</v>
       </c>
       <c r="D3" t="n">
         <v>2.61466e-07</v>
@@ -4521,10 +4332,7 @@
         <v>-20067.30724886391</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.142657200067725e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2583.229542437809</v>
+        <v>-8541.520745752319</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000002826e-08</v>
@@ -4541,7 +4349,7 @@
         <v>1789.713</v>
       </c>
       <c r="C4" t="n">
-        <v>2231.582494689134</v>
+        <v>11757.80550230137</v>
       </c>
       <c r="D4" t="n">
         <v>2.62738e-07</v>
@@ -4574,10 +4382,7 @@
         <v>-20370.42307694079</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.025575325807361e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2538.714699164927</v>
+        <v>-8952.738667065394</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001918e-08</v>
@@ -4594,7 +4399,7 @@
         <v>1762.941</v>
       </c>
       <c r="C5" t="n">
-        <v>2206.203782906408</v>
+        <v>12050.78689526449</v>
       </c>
       <c r="D5" t="n">
         <v>2.63498e-07</v>
@@ -4627,10 +4432,7 @@
         <v>-20597.93088147454</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.135952387318772e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2507.926963519586</v>
+        <v>-9280.57746434442</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000226e-08</v>
@@ -4647,7 +4449,7 @@
         <v>1732.477</v>
       </c>
       <c r="C6" t="n">
-        <v>2179.848041482439</v>
+        <v>12251.32916451385</v>
       </c>
       <c r="D6" t="n">
         <v>2.64007e-07</v>
@@ -4680,10 +4482,7 @@
         <v>-19693.17686534335</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.115334331640313e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2480.208714911109</v>
+        <v>-9508.398694354069</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000002e-08</v>
@@ -4700,7 +4499,7 @@
         <v>1710.21</v>
       </c>
       <c r="C7" t="n">
-        <v>2160.124999805259</v>
+        <v>12061.49165529833</v>
       </c>
       <c r="D7" t="n">
         <v>2.64831e-07</v>
@@ -4733,10 +4532,7 @@
         <v>-19793.92875758646</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.497925975947455e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2452.968327995208</v>
+        <v>-9337.438101298552</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -4753,7 +4549,7 @@
         <v>1695.556</v>
       </c>
       <c r="C8" t="n">
-        <v>2143.96736136812</v>
+        <v>12269.47689510114</v>
       </c>
       <c r="D8" t="n">
         <v>2.65328e-07</v>
@@ -4786,10 +4582,7 @@
         <v>-20864.34924827407</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.759762479546224e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2427.61287404634</v>
+        <v>-9571.221182160389</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000017e-08</v>
@@ -4806,7 +4599,7 @@
         <v>1675.858</v>
       </c>
       <c r="C9" t="n">
-        <v>2122.704802615652</v>
+        <v>12851.34173467262</v>
       </c>
       <c r="D9" t="n">
         <v>2.66028e-07</v>
@@ -4839,10 +4632,7 @@
         <v>-21066.67986262115</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.784359300133081e-13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2403.38300821044</v>
+        <v>-10190.82204342547</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4859,7 +4649,7 @@
         <v>1649.471</v>
       </c>
       <c r="C10" t="n">
-        <v>2099.62980335701</v>
+        <v>12960.67984670794</v>
       </c>
       <c r="D10" t="n">
         <v>2.66653e-07</v>
@@ -4892,10 +4682,7 @@
         <v>-20034.87837944888</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.268957503321733e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2380.142599188782</v>
+        <v>-10322.56555669291</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000081e-08</v>
@@ -4912,7 +4699,7 @@
         <v>1637.425</v>
       </c>
       <c r="C11" t="n">
-        <v>2086.699380408253</v>
+        <v>12604.33019347531</v>
       </c>
       <c r="D11" t="n">
         <v>2.67369e-07</v>
@@ -4945,10 +4732,7 @@
         <v>-20962.99332618411</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.243229995285135e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2357.842904353146</v>
+        <v>-9976.32543990587</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000188e-08</v>
@@ -4965,7 +4749,7 @@
         <v>1620.573</v>
       </c>
       <c r="C12" t="n">
-        <v>2068.992483857875</v>
+        <v>13202.01980495287</v>
       </c>
       <c r="D12" t="n">
         <v>2.68074e-07</v>
@@ -4998,10 +4782,7 @@
         <v>-21147.04181470851</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.786353359074191e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2336.549176340451</v>
+        <v>-10610.32345049852</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -5018,7 +4799,7 @@
         <v>1597.221</v>
       </c>
       <c r="C13" t="n">
-        <v>2049.350394846454</v>
+        <v>12946.04093927824</v>
       </c>
       <c r="D13" t="n">
         <v>2.68452e-07</v>
@@ -5051,10 +4832,7 @@
         <v>-20121.95237616786</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.320292495968892e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2315.660692212417</v>
+        <v>-10363.30026197902</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000522e-08</v>
@@ -5071,7 +4849,7 @@
         <v>1574.211</v>
       </c>
       <c r="C14" t="n">
-        <v>2028.293985029993</v>
+        <v>12697.62649783227</v>
       </c>
       <c r="D14" t="n">
         <v>2.69242e-07</v>
@@ -5104,10 +4882,7 @@
         <v>-19184.5073901818</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.650732854260847e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2295.033058050712</v>
+        <v>-10127.38491067139</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000036e-08</v>
@@ -5124,7 +4899,7 @@
         <v>1558.589</v>
       </c>
       <c r="C15" t="n">
-        <v>2013.294836278182</v>
+        <v>13155.8097027464</v>
       </c>
       <c r="D15" t="n">
         <v>2.69735e-07</v>
@@ -5157,10 +4932,7 @@
         <v>-19215.07432547842</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.267501041664768e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2275.765793905397</v>
+        <v>-10614.80392997476</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000099e-08</v>
@@ -5177,7 +4949,7 @@
         <v>1556.772</v>
       </c>
       <c r="C16" t="n">
-        <v>2007.408154294445</v>
+        <v>13234.77174021526</v>
       </c>
       <c r="D16" t="n">
         <v>2.70132e-07</v>
@@ -5210,10 +4982,7 @@
         <v>-21160.37137131668</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.791518274147209e-12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2257.770160290217</v>
+        <v>-10710.48183318437</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5230,7 +4999,7 @@
         <v>1534.684</v>
       </c>
       <c r="C17" t="n">
-        <v>1987.15348425602</v>
+        <v>13425.9929386385</v>
       </c>
       <c r="D17" t="n">
         <v>2.70694e-07</v>
@@ -5263,10 +5032,7 @@
         <v>-20173.41678449231</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.177594460518473e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2238.235005567555</v>
+        <v>-10923.50123078786</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -5283,7 +5049,7 @@
         <v>1513.547</v>
       </c>
       <c r="C18" t="n">
-        <v>1967.466077201076</v>
+        <v>13127.52159789158</v>
       </c>
       <c r="D18" t="n">
         <v>2.71452e-07</v>
@@ -5316,10 +5082,7 @@
         <v>-19172.14252275833</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.620803406553089e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2218.787863907711</v>
+        <v>-10635.91693105074</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000045e-08</v>
@@ -5336,7 +5099,7 @@
         <v>1503.857</v>
       </c>
       <c r="C19" t="n">
-        <v>1955.879329291216</v>
+        <v>13323.94965464882</v>
       </c>
       <c r="D19" t="n">
         <v>2.71953e-07</v>
@@ -5369,10 +5132,7 @@
         <v>-20148.07418397862</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.872725503930049e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2199.060141569402</v>
+        <v>-10854.54419037352</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000183e-08</v>
@@ -5389,7 +5149,7 @@
         <v>1481.24</v>
       </c>
       <c r="C20" t="n">
-        <v>1936.338380936035</v>
+        <v>711.3853955685614</v>
       </c>
       <c r="D20" t="n">
         <v>2.72619e-07</v>
@@ -5422,16 +5182,13 @@
         <v>-19204.15331752017</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.781154353761066e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2179.398350205155</v>
+        <v>486.3617872144704</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.00000000000542e-08</v>
+        <v>1.15294239892515e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8212928590414705</v>
+        <v>0.9993230432772329</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5199,7 @@
         <v>1479.339</v>
       </c>
       <c r="C21" t="n">
-        <v>1929.550984018319</v>
+        <v>14205.31072574342</v>
       </c>
       <c r="D21" t="n">
         <v>2.734e-07</v>
@@ -5475,10 +5232,7 @@
         <v>-21202.28289242541</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.550094168873597e-14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2159.728236925961</v>
+        <v>-11794.41150779199</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5495,7 +5249,7 @@
         <v>1456.159</v>
       </c>
       <c r="C22" t="n">
-        <v>1909.135729054293</v>
+        <v>13586.98202770927</v>
       </c>
       <c r="D22" t="n">
         <v>2.73957e-07</v>
@@ -5528,10 +5282,7 @@
         <v>-20063.87136094583</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.459649451401785e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2139.959100126716</v>
+        <v>-11178.18779805068</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000251e-08</v>
@@ -5694,7 +5445,7 @@
         <v>2343.822</v>
       </c>
       <c r="C2" t="n">
-        <v>2849.109606841207</v>
+        <v>10652.34609762021</v>
       </c>
       <c r="D2" t="n">
         <v>2.28544e-07</v>
@@ -5727,10 +5478,7 @@
         <v>-17992.93817047779</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.425309557383945e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3081.059801711274</v>
+        <v>-7147.855199220194</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003688e-08</v>
@@ -5747,7 +5495,7 @@
         <v>1983.834</v>
       </c>
       <c r="C3" t="n">
-        <v>2430.054203346974</v>
+        <v>11402.24331715412</v>
       </c>
       <c r="D3" t="n">
         <v>2.52144e-07</v>
@@ -5780,10 +5528,7 @@
         <v>-20013.35023767647</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.450349800561396e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2745.301739067062</v>
+        <v>-8364.899151383652</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000679e-08</v>
@@ -5800,7 +5545,7 @@
         <v>1889.344</v>
       </c>
       <c r="C4" t="n">
-        <v>2329.309120105403</v>
+        <v>11890.00072706596</v>
       </c>
       <c r="D4" t="n">
         <v>2.57072e-07</v>
@@ -5833,10 +5578,7 @@
         <v>-20223.32743608797</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.69938379951708e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2654.604223475348</v>
+        <v>-8975.517932150955</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000151e-08</v>
@@ -5853,7 +5595,7 @@
         <v>1852.22</v>
       </c>
       <c r="C5" t="n">
-        <v>2290.175910921893</v>
+        <v>12155.95172109224</v>
       </c>
       <c r="D5" t="n">
         <v>2.58989e-07</v>
@@ -5886,10 +5628,7 @@
         <v>-21617.461420332</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.323591914397955e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2605.064474555924</v>
+        <v>-9298.272393598343</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -5906,7 +5645,7 @@
         <v>1810.7</v>
       </c>
       <c r="C6" t="n">
-        <v>2251.45026374047</v>
+        <v>12061.96237898394</v>
       </c>
       <c r="D6" t="n">
         <v>2.60634e-07</v>
@@ -5939,10 +5678,7 @@
         <v>-20812.28805137096</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.962429432940161e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2564.296362406016</v>
+        <v>-9239.354331067932</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000014483e-08</v>
@@ -5959,7 +5695,7 @@
         <v>1786.002</v>
       </c>
       <c r="C7" t="n">
-        <v>2227.752890635576</v>
+        <v>12226.51849191891</v>
       </c>
       <c r="D7" t="n">
         <v>2.62199e-07</v>
@@ -5992,10 +5728,7 @@
         <v>-21994.79614495493</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.776885641637098e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2526.265882645215</v>
+        <v>-9444.028727231827</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -6012,7 +5745,7 @@
         <v>1746.768</v>
       </c>
       <c r="C8" t="n">
-        <v>2193.693137401565</v>
+        <v>12403.23954898216</v>
       </c>
       <c r="D8" t="n">
         <v>2.63582e-07</v>
@@ -6045,10 +5778,7 @@
         <v>-21017.87469777355</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.476418874005884e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2490.742438648057</v>
+        <v>-9657.774707961</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000003e-08</v>
@@ -6065,7 +5795,7 @@
         <v>1716.744</v>
       </c>
       <c r="C9" t="n">
-        <v>2167.135185618064</v>
+        <v>12527.25568455356</v>
       </c>
       <c r="D9" t="n">
         <v>2.65159e-07</v>
@@ -6098,10 +5828,7 @@
         <v>-21064.62675204686</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.723600175702745e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2456.832642935767</v>
+        <v>-9818.533947162125</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000026e-08</v>
@@ -6118,7 +5845,7 @@
         <v>1690.529</v>
       </c>
       <c r="C10" t="n">
-        <v>2140.707230409683</v>
+        <v>795.8939240327082</v>
       </c>
       <c r="D10" t="n">
         <v>2.66405e-07</v>
@@ -6151,16 +5878,13 @@
         <v>-20997.09228365609</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.065434141302727e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2424.319554397909</v>
+        <v>493.581618383975</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000002584e-08</v>
+        <v>1.008216767820758e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.818431322878423</v>
+        <v>0.9972427223683068</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1665.543</v>
       </c>
       <c r="C11" t="n">
-        <v>2114.911594572889</v>
+        <v>12424.49019017062</v>
       </c>
       <c r="D11" t="n">
         <v>2.67788e-07</v>
@@ -6204,10 +5928,7 @@
         <v>-21129.25677728041</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.320895351229182e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2394.173291675013</v>
+        <v>-9770.628457098597</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000006275e-08</v>
@@ -6370,7 +6091,7 @@
         <v>1981.482</v>
       </c>
       <c r="C2" t="n">
-        <v>2453.049910058739</v>
+        <v>11527.87734004635</v>
       </c>
       <c r="D2" t="n">
         <v>2.5166e-07</v>
@@ -6403,10 +6124,7 @@
         <v>-20573.54412001033</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.170304303577866e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2723.277843501315</v>
+        <v>-8496.77216538551</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000497e-08</v>
@@ -6423,7 +6141,7 @@
         <v>1824.727</v>
       </c>
       <c r="C3" t="n">
-        <v>2273.869828804703</v>
+        <v>12162.85077901959</v>
       </c>
       <c r="D3" t="n">
         <v>2.5857e-07</v>
@@ -6456,10 +6174,7 @@
         <v>-19997.39323335383</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.002591032092316e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2587.165441155724</v>
+        <v>-9314.070356053693</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -6476,7 +6191,7 @@
         <v>1785.352</v>
       </c>
       <c r="C4" t="n">
-        <v>2232.472765863288</v>
+        <v>12423.00617342341</v>
       </c>
       <c r="D4" t="n">
         <v>2.60358e-07</v>
@@ -6509,10 +6224,7 @@
         <v>-21071.5388380355</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.571592674941024e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2538.874834447206</v>
+        <v>-9628.430165829928</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000225e-08</v>
@@ -6529,7 +6241,7 @@
         <v>1767.733</v>
       </c>
       <c r="C5" t="n">
-        <v>2208.419784224196</v>
+        <v>12702.43154061258</v>
       </c>
       <c r="D5" t="n">
         <v>2.61499e-07</v>
@@ -6562,10 +6274,7 @@
         <v>-22371.36367057697</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.812708811615704e-13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2504.426155924969</v>
+        <v>-9945.579442406472</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000007e-08</v>
@@ -6582,7 +6291,7 @@
         <v>1732.844</v>
       </c>
       <c r="C6" t="n">
-        <v>2179.148588768236</v>
+        <v>12842.19953859519</v>
       </c>
       <c r="D6" t="n">
         <v>2.62565e-07</v>
@@ -6615,10 +6324,7 @@
         <v>-21292.76737316284</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.394252693007735e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2476.020271105374</v>
+        <v>-10115.71021616251</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000113e-08</v>
@@ -6635,7 +6341,7 @@
         <v>1713.982</v>
       </c>
       <c r="C7" t="n">
-        <v>2159.527184732122</v>
+        <v>13006.30370198483</v>
       </c>
       <c r="D7" t="n">
         <v>2.63224e-07</v>
@@ -6668,10 +6374,7 @@
         <v>-21420.92662160226</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.546173903231464e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2453.672192265043</v>
+        <v>-10304.49081423469</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003121e-08</v>
@@ -6688,7 +6391,7 @@
         <v>1699</v>
       </c>
       <c r="C8" t="n">
-        <v>2144.127257671733</v>
+        <v>13135.78787785043</v>
       </c>
       <c r="D8" t="n">
         <v>2.6399e-07</v>
@@ -6721,10 +6424,7 @@
         <v>-21544.92691483485</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.426944024014158e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2433.13047114036</v>
+        <v>-10456.62102744036</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000092e-08</v>
@@ -6741,7 +6441,7 @@
         <v>1681.85</v>
       </c>
       <c r="C9" t="n">
-        <v>2129.188967580939</v>
+        <v>13241.37484710622</v>
       </c>
       <c r="D9" t="n">
         <v>2.64761e-07</v>
@@ -6774,10 +6474,7 @@
         <v>-21613.73295523469</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16263633443452e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2413.248949911742</v>
+        <v>-10583.43887999307</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6794,7 +6491,7 @@
         <v>1665.735</v>
       </c>
       <c r="C10" t="n">
-        <v>2111.399154531131</v>
+        <v>13290.91542161422</v>
       </c>
       <c r="D10" t="n">
         <v>2.65302e-07</v>
@@ -6827,10 +6524,7 @@
         <v>-21505.44090915568</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.345472417549289e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2393.858602499464</v>
+        <v>-10650.15595711177</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000104e-08</v>
@@ -6847,7 +6541,7 @@
         <v>1642.453</v>
       </c>
       <c r="C11" t="n">
-        <v>2092.247867514787</v>
+        <v>13436.49482866604</v>
       </c>
       <c r="D11" t="n">
         <v>2.66007e-07</v>
@@ -6880,10 +6574,7 @@
         <v>-20594.97147993325</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.825886906986223e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2374.418761341155</v>
+        <v>-10818.1982285282</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000557e-08</v>
@@ -6900,7 +6591,7 @@
         <v>1636.496</v>
       </c>
       <c r="C12" t="n">
-        <v>2081.788064830518</v>
+        <v>13079.03808224255</v>
       </c>
       <c r="D12" t="n">
         <v>2.66771e-07</v>
@@ -6933,10 +6624,7 @@
         <v>-21599.7562513388</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.372774734725803e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2355.567641591116</v>
+        <v>-10468.86647473002</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000031e-08</v>
@@ -6953,7 +6641,7 @@
         <v>1614.385</v>
       </c>
       <c r="C13" t="n">
-        <v>2062.726926706182</v>
+        <v>13550.2693876243</v>
       </c>
       <c r="D13" t="n">
         <v>2.67451e-07</v>
@@ -6986,10 +6674,7 @@
         <v>-20608.62393983498</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.190584146090764e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2336.211412167455</v>
+        <v>-10969.99532741757</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000008e-08</v>
@@ -7006,7 +6691,7 @@
         <v>1600.749</v>
       </c>
       <c r="C14" t="n">
-        <v>2047.540372907699</v>
+        <v>757.9081083215475</v>
       </c>
       <c r="D14" t="n">
         <v>2.68093e-07</v>
@@ -7039,16 +6724,13 @@
         <v>-20706.39173097324</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.357878013934101e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2316.517725308374</v>
+        <v>495.4875004919372</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000188e-08</v>
+        <v>1.199747730433509e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8197500442627443</v>
+        <v>0.9932245560383968</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6741,7 @@
         <v>1589.961</v>
       </c>
       <c r="C15" t="n">
-        <v>2036.222950577755</v>
+        <v>13445.41185267139</v>
       </c>
       <c r="D15" t="n">
         <v>2.68826e-07</v>
@@ -7092,10 +6774,7 @@
         <v>-21745.41487247886</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.443108879293533e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2297.117218662236</v>
+        <v>-10897.63981883722</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000011993e-08</v>
@@ -7112,7 +6791,7 @@
         <v>1563.783</v>
       </c>
       <c r="C16" t="n">
-        <v>2013.041521911694</v>
+        <v>13499.24738648391</v>
       </c>
       <c r="D16" t="n">
         <v>2.69432e-07</v>
@@ -7145,10 +6824,7 @@
         <v>-19745.06294729883</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.511004981708023e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2277.833135732118</v>
+        <v>-10968.82658176239</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000151e-08</v>
@@ -7165,7 +6841,7 @@
         <v>1548.647</v>
       </c>
       <c r="C17" t="n">
-        <v>1997.733505553642</v>
+        <v>13503.51343657907</v>
       </c>
       <c r="D17" t="n">
         <v>2.7027e-07</v>
@@ -7198,10 +6874,7 @@
         <v>-19617.17045832672</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.522623202295483e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2258.148620359526</v>
+        <v>-10992.31936086652</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000002555e-08</v>
@@ -7218,7 +6891,7 @@
         <v>1545.171</v>
       </c>
       <c r="C18" t="n">
-        <v>1989.964371053056</v>
+        <v>730.8246932734335</v>
       </c>
       <c r="D18" t="n">
         <v>2.70891e-07</v>
@@ -7251,16 +6924,13 @@
         <v>-21663.66872149138</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.960059470758436e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2238.379325004129</v>
+        <v>486.5533983531421</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000034e-08</v>
+        <v>1.389422012334979e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8208897780338125</v>
+        <v>0.9830150165655813</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6941,7 @@
         <v>1517.703</v>
       </c>
       <c r="C19" t="n">
-        <v>1965.978165375447</v>
+        <v>13458.55019755089</v>
       </c>
       <c r="D19" t="n">
         <v>2.71565e-07</v>
@@ -7304,10 +6974,7 @@
         <v>-19724.6107521858</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.969591339762135e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2218.255854321172</v>
+        <v>-10981.12755775497</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000024667e-08</v>
@@ -7324,7 +6991,7 @@
         <v>1495.006</v>
       </c>
       <c r="C20" t="n">
-        <v>1946.837721534329</v>
+        <v>717.8248425987946</v>
       </c>
       <c r="D20" t="n">
         <v>2.72242e-07</v>
@@ -7357,16 +7024,13 @@
         <v>-18794.78887703615</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.390666689570101e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2198.118659851394</v>
+        <v>498.6252880943536</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000002782e-08</v>
+        <v>1.440823530430889e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8214780621471813</v>
+        <v>0.9831356274113308</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7041,7 @@
         <v>1489.912</v>
       </c>
       <c r="C21" t="n">
-        <v>1936.981156903518</v>
+        <v>1489.912</v>
       </c>
       <c r="D21" t="n">
         <v>2.73186e-07</v>
@@ -7409,11 +7073,10 @@
       <c r="X21" t="n">
         <v>-20401.18930379382</v>
       </c>
-      <c r="Y21" t="n">
-        <v>3.62735696975217e-10</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2177.562979443003</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7430,7 +7093,7 @@
         <v>1483.075</v>
       </c>
       <c r="C22" t="n">
-        <v>1926.561544843088</v>
+        <v>704.0327527303724</v>
       </c>
       <c r="D22" t="n">
         <v>2.73981e-07</v>
@@ -7463,16 +7126,13 @@
         <v>-21468.21191511771</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.714803429648379e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2157.333272256946</v>
+        <v>511.305807566907</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000121306e-08</v>
+        <v>2.137347803520496e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8220778198675921</v>
+        <v>0.9562288585530122</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7289,7 @@
         <v>2256.101</v>
       </c>
       <c r="C2" t="n">
-        <v>2795.152781276797</v>
+        <v>10765.74741042347</v>
       </c>
       <c r="D2" t="n">
         <v>2.31914e-07</v>
@@ -7662,10 +7322,7 @@
         <v>-15874.34624754627</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.72998546983139e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2993.862111401536</v>
+        <v>-7325.90241798604</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000031e-08</v>
@@ -7682,7 +7339,7 @@
         <v>1906.253</v>
       </c>
       <c r="C3" t="n">
-        <v>2368.387132520875</v>
+        <v>11642.02511181832</v>
       </c>
       <c r="D3" t="n">
         <v>2.56388e-07</v>
@@ -7715,10 +7372,7 @@
         <v>-18389.01727795352</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.672037935581266e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2676.007602567666</v>
+        <v>-8674.003321047221</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000011993e-08</v>
@@ -7735,7 +7389,7 @@
         <v>1832.576</v>
       </c>
       <c r="C4" t="n">
-        <v>2283.04589683425</v>
+        <v>12158.35932532115</v>
       </c>
       <c r="D4" t="n">
         <v>2.60971e-07</v>
@@ -7768,10 +7422,7 @@
         <v>-20764.14428771099</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.209362632440205e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2592.350911856874</v>
+        <v>-9308.602716325862</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000015e-08</v>
@@ -7788,7 +7439,7 @@
         <v>1778.58</v>
       </c>
       <c r="C5" t="n">
-        <v>2234.386842357108</v>
+        <v>11814.0807556599</v>
       </c>
       <c r="D5" t="n">
         <v>2.6273e-07</v>
@@ -7821,10 +7472,7 @@
         <v>-19510.06915356576</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.827790617756636e-13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2547.892585559964</v>
+        <v>-8999.970186188306</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -7841,7 +7489,7 @@
         <v>1762.227</v>
       </c>
       <c r="C6" t="n">
-        <v>2213.411973457326</v>
+        <v>12295.11216187535</v>
       </c>
       <c r="D6" t="n">
         <v>2.64217e-07</v>
@@ -7874,10 +7522,7 @@
         <v>-21674.40370160397</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.462583577566745e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2510.960577695527</v>
+        <v>-9531.171833038072</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000026449e-08</v>
@@ -7894,7 +7539,7 @@
         <v>1724.641</v>
       </c>
       <c r="C7" t="n">
-        <v>2180.851164567806</v>
+        <v>12577.66310013551</v>
       </c>
       <c r="D7" t="n">
         <v>2.65402e-07</v>
@@ -7927,10 +7572,7 @@
         <v>-20864.73366181109</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.024751398629683e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2476.289429560517</v>
+        <v>-9851.313913922597</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000002e-08</v>
@@ -7947,7 +7589,7 @@
         <v>1695.8</v>
       </c>
       <c r="C8" t="n">
-        <v>2154.009967347798</v>
+        <v>12757.9863016983</v>
       </c>
       <c r="D8" t="n">
         <v>2.66921e-07</v>
@@ -7980,10 +7622,7 @@
         <v>-21043.62329328149</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.065073969227068e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2443.014271513823</v>
+        <v>-10069.45002950717</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000303e-08</v>
@@ -8000,7 +7639,7 @@
         <v>1670.12</v>
       </c>
       <c r="C9" t="n">
-        <v>2128.699843244138</v>
+        <v>12767.5122654151</v>
       </c>
       <c r="D9" t="n">
         <v>2.68514e-07</v>
@@ -8033,10 +7672,7 @@
         <v>-20996.50124691442</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.25785676806503e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2410.64347555354</v>
+        <v>-10110.98534502476</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001071e-08</v>
@@ -8053,7 +7689,7 @@
         <v>1642.478</v>
       </c>
       <c r="C10" t="n">
-        <v>2105.171844344286</v>
+        <v>12562.8527949072</v>
       </c>
       <c r="D10" t="n">
         <v>2.69867e-07</v>
@@ -8086,10 +7722,7 @@
         <v>-21047.23939884337</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.595270494357625e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2379.623915660651</v>
+        <v>-9929.469568028806</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000808e-08</v>
@@ -8106,7 +7739,7 @@
         <v>1621.088</v>
       </c>
       <c r="C11" t="n">
-        <v>2080.571736777088</v>
+        <v>13019.96277001701</v>
       </c>
       <c r="D11" t="n">
         <v>2.71307e-07</v>
@@ -8139,10 +7772,7 @@
         <v>-21213.48890531447</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.211286328280494e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2350.232133890175</v>
+        <v>-10427.9808000454</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000597e-08</v>
@@ -8305,7 +7935,7 @@
         <v>1834.501</v>
       </c>
       <c r="C2" t="n">
-        <v>2313.832839887632</v>
+        <v>11993.45734731063</v>
       </c>
       <c r="D2" t="n">
         <v>2.59609e-07</v>
@@ -8338,10 +7968,7 @@
         <v>-19952.42369852823</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.001749904773327e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2576.472967375066</v>
+        <v>-9128.861140396391</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000005e-08</v>
@@ -8358,7 +7985,7 @@
         <v>1730.541</v>
       </c>
       <c r="C3" t="n">
-        <v>2186.000976816722</v>
+        <v>12389.04986964771</v>
       </c>
       <c r="D3" t="n">
         <v>2.65467e-07</v>
@@ -8391,10 +8018,7 @@
         <v>-20793.57053931227</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.250707467516904e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2473.10513730076</v>
+        <v>-9660.305029739036</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000003e-08</v>
@@ -8411,7 +8035,7 @@
         <v>1692.576</v>
       </c>
       <c r="C4" t="n">
-        <v>2147.710375428213</v>
+        <v>12597.5203851927</v>
       </c>
       <c r="D4" t="n">
         <v>2.67275e-07</v>
@@ -8444,10 +8068,7 @@
         <v>-20881.19554562695</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.719296877167754e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2432.704602150638</v>
+        <v>-9914.881656374566</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000001e-08</v>
@@ -8464,7 +8085,7 @@
         <v>1657.131</v>
       </c>
       <c r="C5" t="n">
-        <v>2118.277941507281</v>
+        <v>12839.19268769227</v>
       </c>
       <c r="D5" t="n">
         <v>2.68375e-07</v>
@@ -8497,10 +8118,7 @@
         <v>-20031.4761887961</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.869679054820073e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2401.39949751879</v>
+        <v>-10189.96328961975</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000015e-08</v>
@@ -8517,7 +8135,7 @@
         <v>1638.692</v>
       </c>
       <c r="C6" t="n">
-        <v>2097.669870637065</v>
+        <v>12562.08845714811</v>
       </c>
       <c r="D6" t="n">
         <v>2.69563e-07</v>
@@ -8550,10 +8168,7 @@
         <v>-20899.76336249191</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.458778026601151e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2372.219847912399</v>
+        <v>-9931.482449661684</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000017e-08</v>
@@ -8570,7 +8185,7 @@
         <v>1615.773</v>
       </c>
       <c r="C7" t="n">
-        <v>2078.043321610151</v>
+        <v>12709.07250225934</v>
       </c>
       <c r="D7" t="n">
         <v>2.70626e-07</v>
@@ -8603,10 +8218,7 @@
         <v>-21030.50437148828</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.099135095323489e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2346.14593972893</v>
+        <v>-10106.71382692084</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000009e-08</v>
@@ -8623,7 +8235,7 @@
         <v>1583.603</v>
       </c>
       <c r="C8" t="n">
-        <v>2048.499390947482</v>
+        <v>12757.59672299339</v>
       </c>
       <c r="D8" t="n">
         <v>2.71799e-07</v>
@@ -8656,10 +8268,7 @@
         <v>-19138.33906001406</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.029933164846459e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2322.046114774923</v>
+        <v>-10180.19404121907</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000007e-08</v>
@@ -8676,7 +8285,7 @@
         <v>1578.355</v>
       </c>
       <c r="C9" t="n">
-        <v>2040.355551598688</v>
+        <v>13134.34588809015</v>
       </c>
       <c r="D9" t="n">
         <v>2.7292e-07</v>
@@ -8709,10 +8318,7 @@
         <v>-20923.40766616633</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.119070493671383e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2299.791109757578</v>
+        <v>-10588.99050819617</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8729,7 +8335,7 @@
         <v>1553.738</v>
       </c>
       <c r="C10" t="n">
-        <v>2019.57003763554</v>
+        <v>12893.15842822759</v>
       </c>
       <c r="D10" t="n">
         <v>2.73763e-07</v>
@@ -8762,10 +8368,7 @@
         <v>-19972.2463116406</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.002957545166091e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2279.53393126862</v>
+        <v>-10359.96664113587</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8782,7 +8385,7 @@
         <v>1533.59</v>
       </c>
       <c r="C11" t="n">
-        <v>1999.220764670188</v>
+        <v>12984.61343032919</v>
       </c>
       <c r="D11" t="n">
         <v>2.74687e-07</v>
@@ -8815,10 +8418,7 @@
         <v>-19163.82370747895</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.876029599413158e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2259.616609348771</v>
+        <v>-10472.98038169555</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000033e-08</v>
@@ -8835,7 +8435,7 @@
         <v>1520.407</v>
       </c>
       <c r="C12" t="n">
-        <v>1987.173997103841</v>
+        <v>13040.99456548361</v>
       </c>
       <c r="D12" t="n">
         <v>2.75528e-07</v>
@@ -8868,10 +8468,7 @@
         <v>-19974.30768321452</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.652424625790092e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2240.029239039912</v>
+        <v>-10548.67167858738</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000876e-08</v>
@@ -8888,7 +8485,7 @@
         <v>1502.207</v>
       </c>
       <c r="C13" t="n">
-        <v>1968.045472777215</v>
+        <v>722.7515447719778</v>
       </c>
       <c r="D13" t="n">
         <v>2.76469e-07</v>
@@ -8921,16 +8518,13 @@
         <v>-19071.30151111697</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.405646836199243e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2220.45164926095</v>
+        <v>550.2796942038177</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000038715e-08</v>
+        <v>2.398328837104097e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8192951388287493</v>
+        <v>0.9440414465335256</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8535,7 @@
         <v>1487.358</v>
       </c>
       <c r="C14" t="n">
-        <v>1952.28341286356</v>
+        <v>716.9930865356729</v>
       </c>
       <c r="D14" t="n">
         <v>2.77318e-07</v>
@@ -8974,16 +8568,13 @@
         <v>-19107.99141286724</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.68519159908061e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2201.364861816771</v>
+        <v>541.124056056804</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000046e-08</v>
+        <v>2.613632639180733e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8195449557188662</v>
+        <v>0.9427154562880472</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8585,7 @@
         <v>1474.18</v>
       </c>
       <c r="C15" t="n">
-        <v>1937.661299441232</v>
+        <v>710.8259360437445</v>
       </c>
       <c r="D15" t="n">
         <v>2.78166e-07</v>
@@ -9027,16 +8618,13 @@
         <v>-18975.23095006755</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.309785625433233e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2182.479627035726</v>
+        <v>495.3101299940504</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>1.250960858710519e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8198153963052757</v>
+        <v>0.9915291786403853</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8635,7 @@
         <v>1458.19</v>
       </c>
       <c r="C16" t="n">
-        <v>1923.121761604705</v>
+        <v>705.0849789268351</v>
       </c>
       <c r="D16" t="n">
         <v>2.79004e-07</v>
@@ -9080,16 +8668,13 @@
         <v>-18841.88034951055</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.073822070376296e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2164.218695951675</v>
+        <v>517.8412285671026</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000098e-08</v>
+        <v>1.664565037532888e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8200853084615732</v>
+        <v>0.9730297881355796</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8685,7 @@
         <v>1452.395</v>
       </c>
       <c r="C17" t="n">
-        <v>1914.027844689531</v>
+        <v>13023.85481101618</v>
       </c>
       <c r="D17" t="n">
         <v>2.79878e-07</v>
@@ -9133,10 +8718,7 @@
         <v>-19826.84922533125</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.613226763162385e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2145.953973210237</v>
+        <v>-10620.79152700789</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000002e-08</v>
@@ -9153,7 +8735,7 @@
         <v>1431.534</v>
       </c>
       <c r="C18" t="n">
-        <v>1893.885812411079</v>
+        <v>693.7088584810346</v>
       </c>
       <c r="D18" t="n">
         <v>2.80715e-07</v>
@@ -9186,16 +8768,13 @@
         <v>-18725.29177948506</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.620729427644264e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2127.456486914492</v>
+        <v>508.0670412991982</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.00000000000006e-08</v>
+        <v>1.168395589225458e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8206301626029076</v>
+        <v>0.9990239582087141</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8785,7 @@
         <v>1426.919</v>
       </c>
       <c r="C19" t="n">
-        <v>1887.017700620966</v>
+        <v>688.5913440104868</v>
       </c>
       <c r="D19" t="n">
         <v>2.8148e-07</v>
@@ -9239,16 +8818,13 @@
         <v>-20569.15604088516</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.46674741496479e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2109.284482831431</v>
+        <v>499.1564348962405</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000001002e-08</v>
+        <v>1.178114039775246e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8209033797924614</v>
+        <v>0.9948360822758371</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8835,7 @@
         <v>1402.282</v>
       </c>
       <c r="C20" t="n">
-        <v>1865.140334656425</v>
+        <v>13090.81708194982</v>
       </c>
       <c r="D20" t="n">
         <v>2.82385e-07</v>
@@ -9292,10 +8868,7 @@
         <v>-18543.72508123181</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.522106775312913e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2091.518776425849</v>
+        <v>-10742.3360046345</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -9312,7 +8885,7 @@
         <v>1388.654</v>
       </c>
       <c r="C21" t="n">
-        <v>1850.580375437595</v>
+        <v>677.8305283270449</v>
       </c>
       <c r="D21" t="n">
         <v>2.8306e-07</v>
@@ -9345,16 +8918,13 @@
         <v>-18551.96748768415</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.055729918591458e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2073.324016333495</v>
+        <v>500.1367159838276</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.57990005803642e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8214385401595771</v>
+        <v>0.9784962130345223</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8935,7 @@
         <v>1381.295</v>
       </c>
       <c r="C22" t="n">
-        <v>1841.053560744098</v>
+        <v>672.7906364364638</v>
       </c>
       <c r="D22" t="n">
         <v>2.83893e-07</v>
@@ -9398,16 +8968,13 @@
         <v>-19356.70630630733</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.08786599857168e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2054.917622897904</v>
+        <v>490.6200816634109</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000043e-08</v>
+        <v>1.1605099286521e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8217239236305618</v>
+        <v>0.9956998163892772</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9131,7 @@
         <v>1793.609</v>
       </c>
       <c r="C2" t="n">
-        <v>2427.753738354898</v>
+        <v>11452.72136862572</v>
       </c>
       <c r="D2" t="n">
         <v>2.56611e-07</v>
@@ -9597,10 +9164,7 @@
         <v>-15811.89697297614</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.790087011635379e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2451.890993791166</v>
+        <v>-8507.752582454474</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000365e-08</v>
@@ -9617,7 +9181,7 @@
         <v>1447.856</v>
       </c>
       <c r="C3" t="n">
-        <v>1957.347899869617</v>
+        <v>12830.92684355034</v>
       </c>
       <c r="D3" t="n">
         <v>2.79414e-07</v>
@@ -9650,10 +9214,7 @@
         <v>-17208.84006990088</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.976602508334061e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2154.014554009581</v>
+        <v>-10359.85860650628</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000007021e-08</v>
@@ -9670,7 +9231,7 @@
         <v>1374.545</v>
       </c>
       <c r="C4" t="n">
-        <v>1872.712238790338</v>
+        <v>13111.76857478609</v>
       </c>
       <c r="D4" t="n">
         <v>2.82684e-07</v>
@@ -9703,10 +9264,7 @@
         <v>-18040.81103764051</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.664386647689722e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2082.038696500387</v>
+        <v>-10738.89642971113</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -9723,7 +9281,7 @@
         <v>1334.922</v>
       </c>
       <c r="C5" t="n">
-        <v>1834.635211109964</v>
+        <v>13517.02857692051</v>
       </c>
       <c r="D5" t="n">
         <v>2.83732e-07</v>
@@ -9756,10 +9314,7 @@
         <v>-17730.1866662091</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.107602193868262e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2044.046495209578</v>
+        <v>-11193.77132710648</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001067e-08</v>
@@ -9776,7 +9331,7 @@
         <v>1308.322</v>
       </c>
       <c r="C6" t="n">
-        <v>1806.656960013337</v>
+        <v>13415.80688117554</v>
       </c>
       <c r="D6" t="n">
         <v>2.84756e-07</v>
@@ -9809,10 +9364,7 @@
         <v>-17767.14966146949</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.054403846345418e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2012.678866720348</v>
+        <v>-11119.43220325452</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000221e-08</v>
@@ -9829,7 +9381,7 @@
         <v>1282.416</v>
       </c>
       <c r="C7" t="n">
-        <v>1785.070966453727</v>
+        <v>13861.14456725207</v>
       </c>
       <c r="D7" t="n">
         <v>2.85869e-07</v>
@@ -9862,10 +9414,7 @@
         <v>-17781.51214802358</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.114979369353384e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1982.892256509418</v>
+        <v>-11604.79025243319</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000158e-08</v>
@@ -9882,7 +9431,7 @@
         <v>1255.304</v>
       </c>
       <c r="C8" t="n">
-        <v>1759.056295456409</v>
+        <v>13754.19180235009</v>
       </c>
       <c r="D8" t="n">
         <v>2.86851e-07</v>
@@ -9915,10 +9464,7 @@
         <v>-17207.21778862729</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.418852326674026e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1953.937251649365</v>
+        <v>-11521.675269775</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000006949e-08</v>
@@ -9935,7 +9481,7 @@
         <v>1232.165</v>
       </c>
       <c r="C9" t="n">
-        <v>1736.132259088317</v>
+        <v>13955.56701586472</v>
       </c>
       <c r="D9" t="n">
         <v>2.88131e-07</v>
@@ -9968,10 +9514,7 @@
         <v>-17229.11253867616</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.077135247975173e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1925.844962918161</v>
+        <v>-11754.58490692105</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000086e-08</v>
@@ -9988,7 +9531,7 @@
         <v>1218.456</v>
       </c>
       <c r="C10" t="n">
-        <v>1723.782430278108</v>
+        <v>14329.24695148505</v>
       </c>
       <c r="D10" t="n">
         <v>2.89084e-07</v>
@@ -10021,10 +9564,7 @@
         <v>-18499.84125285816</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.151239635401392e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1898.99815532462</v>
+        <v>-12161.06439872946</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000042839e-08</v>
@@ -10041,7 +9581,7 @@
         <v>1188.819</v>
       </c>
       <c r="C11" t="n">
-        <v>1694.917802196109</v>
+        <v>598.5116903068348</v>
       </c>
       <c r="D11" t="n">
         <v>2.90098e-07</v>
@@ -10074,16 +9614,13 @@
         <v>-17120.9332421032</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.579921850165052e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1873.937511008381</v>
+        <v>524.6541001021958</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000042385e-08</v>
+        <v>1.392254114108892e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8201622407633004</v>
+        <v>0.9972360198482751</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 41.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.000000000001203e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8183555707089423</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2087.234</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2479.12899422041</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.47316e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-56.819</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.196392617449662</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7033579965851531</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.305686205686208</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.089555517998962</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18.71452402252282</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.46736018888438</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.562460989615774</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-18797.5310808025</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-2.565672660824021</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000036296e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8167711133695439</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1965.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9414852383585166</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2352.958758349375</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9491070306687651</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.53993e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-59.185</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.03747795414462193</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8657534246575769</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.250913705583778</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.705566012368892</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19.2455581810793</v>
+      </c>
+      <c r="M13" t="n">
+        <v>83.19808207998913</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.383864927548856</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-19879.69519812554</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.47977416593767</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8170985786547826</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1910.832</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9154852786031658</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2301.392052674481</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9283066988606535</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.56606e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-60.135</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5407838983050834</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7072122052704208</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.463977272727263</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.829421817146058</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.395010753338</v>
+      </c>
+      <c r="M14" t="n">
+        <v>83.53630557181546</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.826610120665062</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-20482.23161651968</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.831950723977343</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8172552841217894</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1871.58</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8966795289842923</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2258.463965620513</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9109909048241003</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.58279e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-60.746</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3248896734333596</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9201657458564007</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.066175115207367</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.781132075471695</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.86308698379345</v>
+      </c>
+      <c r="M15" t="n">
+        <v>83.73705993304102</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.11191844502801</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-20816.7812114036</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>8.43670229328859</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000002743e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8173227183843529</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1830.397</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8769486315381984</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2226.81473633473</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8982246351545644</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.59908e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-61.209</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2128230616302022</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7168784029037711</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9632145258910516</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.547996794871786</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18.34302339477952</v>
+      </c>
+      <c r="M16" t="n">
+        <v>83.54559931867567</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8.839428031437869</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-19846.41411952285</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8.406411028385719</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8174198236172382</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1804.514</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8645480094709075</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2198.269309396819</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8867103383977361</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.61229e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-61.639</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1495000000000117</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4722554890219663</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9614684466019159</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.60989106753813</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.7961360208567</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83.67340039265403</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.019494282363736</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-20002.59579901699</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.59775609536382</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000002028e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8175664051140747</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1774.828</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8503253588241665</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2171.830425684544</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8760457526606037</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.6261e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-62.004</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.09293193717277154</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2840198863636422</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.042970822281184</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.661189683860235</v>
+      </c>
+      <c r="L18" t="n">
+        <v>19.51033246693692</v>
+      </c>
+      <c r="M18" t="n">
+        <v>83.78452013252992</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.182050498841342</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-20126.9531701673</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.944158714581363</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000238e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8177346224402359</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1757.883</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.842206959066401</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2146.488219986379</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8658235311637613</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.63999e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-62.394</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7237366003063038</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.877333333333396</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.259237246161507</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.083392226148422</v>
+      </c>
+      <c r="L19" t="n">
+        <v>27.83201034958929</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.14860515850387</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.757749909217273</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-21226.34727106131</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.099556964705471</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000062e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8179248010997409</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1724.039</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8259921982873029</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2123.831540336339</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8566845635251833</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.64978e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-62.694</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.09751984126984883</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5292568203198169</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.183730158730159</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.644236371202658</v>
+      </c>
+      <c r="L20" t="n">
+        <v>20.59680704060719</v>
+      </c>
+      <c r="M20" t="n">
+        <v>83.95881316459732</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.449020328885336</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-20264.89165288859</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.477597628257627</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8181297373002657</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1702.963</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8158946241772604</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2100.46681904738</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8472599949192622</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.65937e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-62.993</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4125842696629033</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.259853121174958</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.269389373513136</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.919780743565296</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.93087611708754</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.03429603958867</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>9.569462053909261</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-20317.45519032307</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.827149369716153</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000001203e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8183555707089423</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.00000000000319e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8217278797467344</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1843.244</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2280.562584760337</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.56788e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-61.461</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.06911281489594526</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3936698717948769</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.930997304582252</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.87210501640884</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.21947061934407</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.66871024912238</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.012758108158772</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-20428.7082248694</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-10.83439920461046</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000845e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8171067159191447</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1726.966</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9369166534653035</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2137.604303578444</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.937314466992838</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.63289e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-62.927</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1910543130990644</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5267723102585367</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.134585400425155</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.87274017983911</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.45051959703535</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.14594536917514</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.753285492065807</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-20994.09988761647</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5.812721278532536</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000001272e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8173916224843785</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1688.105</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9158337149069793</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2095.476856224709</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9188420744195105</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.65145e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-63.383</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4255483870967612</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.026666666666608</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.132622739018061</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.71042713567837</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20.98872998598784</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.25946863714121</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.947499738827316</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-21042.93744743958</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>7.75143009729527</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000008256e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8174941142872491</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1658.146</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8995803051576461</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2067.622100215087</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9066280899422772</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.66116e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-63.699</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1458210422812247</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6887733887733997</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.293607954545458</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.80384437239456</v>
+      </c>
+      <c r="L26" t="n">
+        <v>21.31562869220404</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.35350925532681</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.11427715715188</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-21143.3318205291</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>8.698176816513751</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000002506e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8175918416580957</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1627.795</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8831142268739244</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2041.090394018901</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8949942473222668</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.6729e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-63.984</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.07519083969465755</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4031177829098941</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.945803357314173</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.699353169469554</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.94219095687694</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.16583802044572</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.786773295977596</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-20152.54411207497</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>9.211102169046057</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000115e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8177430005991729</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1613.135</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8751608577052198</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2021.983969800007</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8866163039382217</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.68413e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-64.301</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.07955665024630304</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7959420289855733</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.133697234352249</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.056112224448851</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.2524522619306</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.46460540010293</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.31857941040324</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21099.59584119752</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>7.656791704913189</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8179159658623437</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1593.699</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8646164045563149</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2002.585057614852</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8781101080044699</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.69319e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-64.556</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6324459234609291</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8241676942046238</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.297320061255772</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.769258266309223</v>
+      </c>
+      <c r="L29" t="n">
+        <v>22.9910377313169</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.51424850142372</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.41253795957086</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-21088.49644340535</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>7.489865467816912</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000076e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.818099682844138</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1569.828</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8516658673512568</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1980.835391622562</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8685731340412773</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.70232e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-64.753</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4562271062270772</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.5707382550335168</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.03739837398374</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.816702977487322</v>
+      </c>
+      <c r="L30" t="n">
+        <v>18.68501317782741</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.3479571801164</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.10427711767442</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-20220.06887163307</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>9.02805154595751</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000877e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8183064137903061</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1554.666</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8434401522533099</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1965.000487357418</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8616297138646246</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.71116e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-65.015</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2970454545454007</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6771047227926291</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.102588438308916</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.627663331371482</v>
+      </c>
+      <c r="L31" t="n">
+        <v>19.05980553726456</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.39902851910159</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.19700866891676</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-20248.02688448182</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>8.42683771314671</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8185311841796514</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1537.197</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8339628394287464</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1947.900076895281</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8541313840330259</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.71722e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-65.193</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.7976702508959942</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4587147887323725</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.124664879356535</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.497173544375334</v>
+      </c>
+      <c r="L32" t="n">
+        <v>19.27708984811738</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.39091253370604</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10.18215977337713</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-20050.91065421495</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>9.209160238357754</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000004632e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8187604292413309</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1521.409</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.825397505701904</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1933.104895673584</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.847643870241225</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.72603e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-65.396</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4420704845814839</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4747081712061997</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8945469798657776</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.559654350417166</v>
+      </c>
+      <c r="L33" t="n">
+        <v>19.59334227620773</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.45181317356524</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.29463942715375</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-20123.38766908173</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>9.266070095728537</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8189917624324934</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1509.958</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8191850888976175</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1920.507713985046</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8421201535176774</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.73371e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-65.59399999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3541899441340641</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5342642320086169</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.362996594778637</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.512400906002286</v>
+      </c>
+      <c r="L34" t="n">
+        <v>19.65905631038383</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.47601219736865</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.34001985952958</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-20061.183436252</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>8.244674960133693</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.00000000000118e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8192459476339421</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1490.308</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8085245360896333</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1905.804523519554</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8356729765957439</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.74088e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-65.809</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3841818181818274</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4550087873462115</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.7988326848248868</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.52915966386556</v>
+      </c>
+      <c r="L35" t="n">
+        <v>17.04792516646086</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.29369569325458</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.00756593942882</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-19212.8954625368</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>8.522123388253817</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.00000000000048e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8195006339956028</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1482.278</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8041680862653018</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1891.333131087494</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8293274403983319</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.74915e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-66.01600000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.632649572649592</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4783910196445003</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9291838417147177</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.663282674772063</v>
+      </c>
+      <c r="L36" t="n">
+        <v>19.9087522418928</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.55171167265325</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.48457392029028</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-20039.83720390238</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>8.061373394883503</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8197793088208508</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1469.337</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7971473120216315</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1875.285502220912</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8222907429738372</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.75645e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-66.197</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2434042553191375</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4688046647230798</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9983430799221245</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.814862138533979</v>
+      </c>
+      <c r="L37" t="n">
+        <v>20.17378351015897</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.57235353542768</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10.5246886907921</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-19962.32828533247</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>8.79594119303249</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000814e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8200499075385141</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1454.173</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7889205118801418</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1862.351176838422</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8166191926866746</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.76371e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-66.396</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1544207317073149</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6698315467074842</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.095953141640018</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.687617765814273</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20.48898892195001</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.58906510992153</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.55738898223555</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-19870.82377851203</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>8.03538975337392</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000105e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8203218995395141</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1440.784</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7816566878828848</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1845.064566173119</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8090392162454144</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.77145e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-66.596</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.425842696629147</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3551119766309576</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.502519893899108</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.525184275184312</v>
+      </c>
+      <c r="L39" t="n">
+        <v>20.52617800020768</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.61605159952668</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10.61062197453706</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-19817.71831674836</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>8.897076898214209</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000376e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8205959326397551</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1427.898</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7746657523366413</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1829.403158674579</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8021718723701809</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.77966e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-66.782</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6886649874056293</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4292249047014076</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.168306010928987</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.635066666666613</v>
+      </c>
+      <c r="L40" t="n">
+        <v>20.49012737551057</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.63667721716214</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.65166775410546</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-19731.54103314185</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>9.318381198098905</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000429e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8208555340040277</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1412.093</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.766091195739685</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1820.005799033833</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7980512401614694</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.78655e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-66.97799999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2462757527733778</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2266488413547116</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.536611374407521</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.670784982935182</v>
+      </c>
+      <c r="L41" t="n">
+        <v>20.63670133607735</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.65233205633582</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10.68303222944918</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-19632.73673105193</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>6.739327665956921</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8211350358494037</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1393.428</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7559650268765286</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1803.280017605023</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7907171807760448</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.79416e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-67.196</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3324478178368112</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5527397260273904</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.474022346368743</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.773021925643575</v>
+      </c>
+      <c r="L42" t="n">
+        <v>17.92286347236746</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.44383619669455</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10.27976656123243</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-18671.83959492642</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>7.510070105690716</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.00000000000388e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8214261988556832</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1383.297</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7504687388104885</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1789.544156484041</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7846941664493294</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.80047e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-67.372</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4352402745995777</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.911654135338464</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.090259740259713</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.595928753180744</v>
+      </c>
+      <c r="L43" t="n">
+        <v>20.90349361015664</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.72507677859303</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10.83121163249838</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-19571.3656559198</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>6.163878931063437</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.00000000000319e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8217278797467344</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.000000000000002e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8217336582581808</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2011.455</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2415.01358002031</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.50243e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-59.666</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6308123249299794</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8008349389851893</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.409814612868113</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.320956086714828</v>
+      </c>
+      <c r="L23" t="n">
+        <v>37.8542682315176</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.69378511491739</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.048887585791975</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-21891.96037960164</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-8.411692794967166</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000902e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8170672020976124</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1875.195</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9322579923488222</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2265.94812445922</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9382755207696032</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.5758e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-61.235</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07142857142857578</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6799620733249256</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.39320882852295</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.955216360403119</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.64267270908129</v>
+      </c>
+      <c r="M24" t="n">
+        <v>83.90657962404948</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.367416111232719</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-21436.88077054089</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.39804339458783</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000166e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8174320846404626</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1821.97</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9057970474109539</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2219.814804654694</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9191728042523164</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.59576e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-61.74</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1773462783171516</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1726147123088067</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.030661040787675</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.448363774733604</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.35448719668512</v>
+      </c>
+      <c r="M25" t="n">
+        <v>83.72045429682552</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.087629611191723</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-20318.60135010019</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>7.722540467589852</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8175336911349108</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1791.459</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8906284256918499</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2186.624205565021</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9054293622426056</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.61069e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-62.122</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0001312335958140222</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2058171745152704</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.020588235294137</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.592317380352629</v>
+      </c>
+      <c r="L26" t="n">
+        <v>19.95135763101045</v>
+      </c>
+      <c r="M26" t="n">
+        <v>83.81604540887508</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.229228137305199</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20376.43661082203</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>9.308809266427033</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8176155112344339</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1758.682</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8743332562746867</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2162.243856210246</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8953340362550101</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.62175e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-62.422</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2835185185185199</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5346425765907309</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.471122011036214</v>
+      </c>
+      <c r="L27" t="n">
+        <v>16.66740806818526</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.59765404793657</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8.911906799058885</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-19387.00131202219</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8.568815247160501</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8177240154395706</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1750.934</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8704813182497246</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2141.964052635065</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8869366492825483</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.63351e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-62.698</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6456140350876758</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7490399999999865</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.273733255678555</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.79906976744186</v>
+      </c>
+      <c r="L28" t="n">
+        <v>29.01772231390578</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.23216218771115</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.900088279319178</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21490.53898041881</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>7.820217044961282</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.817867089439878</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1715.923</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.853075510016381</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2119.290058301228</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8775478845478811</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.64473e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-62.988</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1241184767277723</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7013468013468027</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.102117863720142</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.311625460284108</v>
+      </c>
+      <c r="L29" t="n">
+        <v>17.18478488349748</v>
+      </c>
+      <c r="M29" t="n">
+        <v>83.75423241396796</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.137171693787529</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-19499.41387650481</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>8.545742064792876</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8180365574728585</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1703.106</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8467035056712678</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2102.03784130057</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8704041495629569</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.65448e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-63.265</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4072765072764948</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6350114416475688</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9334174022698225</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.783826164874576</v>
+      </c>
+      <c r="L30" t="n">
+        <v>21.84578478440752</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.10581044209108</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.686407016058292</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-20565.56710754223</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>7.116325029799782</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8182333383683441</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1691.294</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8408311396476681</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2079.760859001529</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.861179778121181</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.66297e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-63.482</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4011916583912551</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8661403508771675</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.464665911664746</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.149415692821335</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.29046946008798</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.41428634945154</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.22504062760255</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-21605.80827750863</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>8.668597301267937</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8184443633002594</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1659.046</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8247989639340678</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2062.470880522335</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8540204070011854</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.67271e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-63.731</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1878357030015745</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.2349502487562166</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.019274809160269</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.174963890226261</v>
+      </c>
+      <c r="L32" t="n">
+        <v>18.13966724688534</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.91441608444889</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.379569993771415</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-19503.03704594555</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>8.379725642053245</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000078e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.818677322426041</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1647.535</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8190762408306426</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2045.145027295863</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8468461809969052</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.68187e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-63.946</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4053805774278482</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7264907135875026</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8819857312722535</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.777513464991051</v>
+      </c>
+      <c r="L33" t="n">
+        <v>23.09239173394585</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.22814971961796</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.893159213431094</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-20471.94954415383</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>8.057126333753331</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000131e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8189065265328207</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1625.774</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.808257704000338</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2026.058825219102</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8389430361721042</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.68934e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-64.187</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2354399008673988</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.3663953488371757</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8065217391303824</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.23640948058495</v>
+      </c>
+      <c r="L34" t="n">
+        <v>18.63434081105737</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.01105019342835</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.532048261278273</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19494.71640114519</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>8.631281513697559</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000002573e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8191680807773446</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1617.955</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8043704681437069</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2014.281174874429</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8340661897468459</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.6978e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-64.42100000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4467966573816213</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8425659472421455</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.106403940886703</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.749525101763896</v>
+      </c>
+      <c r="L35" t="n">
+        <v>23.38835407550272</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.33994571805323</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.08988185607426</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-20545.21390106838</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>6.776955992407352</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8194266197450795</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1599.826</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7953575894066733</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1995.694709629969</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8263699741237833</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.70643e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-64.65300000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3699408284023595</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5475915221579801</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.117126269956377</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.736452328159637</v>
+      </c>
+      <c r="L36" t="n">
+        <v>23.89679150068261</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.33925983606377</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.08865132786261</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-20368.10164579641</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>7.369257421402494</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.499795632128715e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.7988401975565512</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1584.736</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7878555572955894</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1980.34405616817</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8200136316216969</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.71554e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-64.883</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5423475258918582</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4817153628652396</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.228179190751497</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.922355193872732</v>
+      </c>
+      <c r="L37" t="n">
+        <v>24.14951231951334</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.40001111425599</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10.19880932308978</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-20435.36029162877</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>6.805909942532253</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8199641689625303</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1571.06</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7810564989025357</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1962.696130929689</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8127060432153691</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.72198e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-65.09399999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3480561555075393</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.003853564547159</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.428178963893274</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.765049415992795</v>
+      </c>
+      <c r="L38" t="n">
+        <v>24.39138543555431</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.43303214988309</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.25969044250655</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-20396.65667646144</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>7.912584873884157</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000009001e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8202555761943258</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1553.62</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7723861582784601</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1948.2291410798</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8067156049132508</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.73004e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-65.322</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3170825335892302</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8773844641101496</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.395030581039688</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.791106993978688</v>
+      </c>
+      <c r="L39" t="n">
+        <v>24.88029530600378</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.46092811865101</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10.31168628116558</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-20335.01623703157</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>7.405211148328704</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000003353e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.820535013514108</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1533.493</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7623799687291041</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1932.825568764298</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8003373499655613</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.73552e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-65.51300000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.07020602218699427</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.7738624338625241</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9832000000000074</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.410034013605425</v>
+      </c>
+      <c r="L40" t="n">
+        <v>19.82829025316722</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.24472827825706</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>9.921850754493514</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-19346.80571314451</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>7.246338694891392</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8208304562524634</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1518.719</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7550350368265758</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1917.583565287036</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7940259968521212</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.74227e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-65.73999999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3252525252525371</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5628458498023391</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.9610226320201497</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.318688901667636</v>
+      </c>
+      <c r="L41" t="n">
+        <v>20.00447072950847</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.25427488926518</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9.938447384427251</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-19225.54669226714</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>7.183984028078612</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8211177620050742</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1505.031</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7482300126028174</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1900.016809768166</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7867520189067375</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.7485e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-65.953</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.341711229946507</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.3653618906942309</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.316479017400163</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.491004672897216</v>
+      </c>
+      <c r="L42" t="n">
+        <v>20.19462359542494</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.30323224331785</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10.02443008987026</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-19240.60136413622</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>8.232052839500625</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8214079875070345</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1490.541</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7410262720269656</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1887.817617805855</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.781700622068543</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.75752e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-66.152</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1740276035131765</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4865577889447271</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.266209081309417</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.667608545830489</v>
+      </c>
+      <c r="L43" t="n">
+        <v>20.11115858716999</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.32978047774316</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10.0716749755915</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-19177.58072070149</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>6.712452310598906</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8217336582581808</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,18 +6881,6 @@
       <c r="G2" t="n">
         <v>-52.22</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>7.326634273776826</v>
       </c>
@@ -4504,6 +7404,566 @@
         <v>1.000000000000001e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8185136253431561</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2408.725</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2866.726105833339</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.24598e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-52.22</v>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>7.326634273776826</v>
+      </c>
+      <c r="M12" t="n">
+        <v>80.46022753213575</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.95038716277577</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-16596.43705457958</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-46.07761346189568</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000002127e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.816019314392889</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2041.874</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8476990939189821</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2436.949038640515</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8500808757703449</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.50617e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-57.014</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.07316692667706126</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4952591656131515</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.029713493530446</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.653190348525476</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.2923991778671</v>
+      </c>
+      <c r="M13" t="n">
+        <v>82.29931049878363</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7.395489235621429</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-18039.68739839427</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.357115049829872</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000092e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8169922817106536</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1955.021</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8116414285566015</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2340.032950106405</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8162736388889067</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.56008e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-58.915</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3881556683587455</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6341922695738159</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.070540677109657</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.913585813044759</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18.58080452143282</v>
+      </c>
+      <c r="M14" t="n">
+        <v>83.12721420698479</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.296593855953182</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-19576.86477097476</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>9.491590135709203</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000007256e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8172046310811947</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1922.261</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7980408722456902</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2295.007124687508</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8005672812681781</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.57981e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-59.933</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6132111861138156</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9827722772277231</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.457560405300037</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.426779793251413</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.55784237975648</v>
+      </c>
+      <c r="M15" t="n">
+        <v>83.82196546708683</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.238141003488344</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-21528.52451899476</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11.09074754734979</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8173278837103433</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1859.155</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7718419495791341</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2263.369284802988</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7895310543261826</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.59346e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-60.657</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01195039458849224</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8844909609896571</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.167331932773075</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.84843063488352</v>
+      </c>
+      <c r="M16" t="n">
+        <v>83.17851291028614</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8.359585879488316</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-18971.86041012717</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.602768911585827</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000135e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.817480515916053</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1842.76</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7650354440627303</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2228.721576761448</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7774448951458417</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.60676e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-61.223</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2155255544840882</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9361702127659295</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.385803520726878</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.918413348946138</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.88479081851846</v>
+      </c>
+      <c r="M17" t="n">
+        <v>83.90111205292037</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.35895466280445</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-21101.02260573204</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.897556814901918</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8176567548882594</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1801.763</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7480152362764534</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2194.875460324456</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7656383551460418</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.61957e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-61.699</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.250248756218918</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5526490066225234</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.03590425531912</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.737578757875707</v>
+      </c>
+      <c r="L18" t="n">
+        <v>19.19478999449868</v>
+      </c>
+      <c r="M18" t="n">
+        <v>83.7154442810232</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.080326634656894</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-20113.85998948934</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>10.59574434329329</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.00000000001678e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8178570218045128</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1771.611</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.735497410455739</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2166.939868329197</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7558935832480866</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.63361e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-62.195</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5366504854368606</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3584967320261362</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.143029490616631</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.621946082561104</v>
+      </c>
+      <c r="L19" t="n">
+        <v>19.95061505542963</v>
+      </c>
+      <c r="M19" t="n">
+        <v>83.85014603447942</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.28080222960611</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-20281.37775214522</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.892020428236719</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8180700508087868</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1749.158</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7261758814310475</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2136.424012501288</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7452487379781413</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.64564e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-62.602</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.16601178781914</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.650267857142817</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.226390346274944</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.944460988683725</v>
+      </c>
+      <c r="L20" t="n">
+        <v>28.42415180959887</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.21828066961335</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.876157291461302</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-21379.63591990633</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>9.218351513352445</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8182931365863191</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1712.861</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.711106913408546</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2109.230095001752</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7357626843770665</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.6591e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-62.996</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1770025839793141</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5423480083857113</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.225000000000019</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.6764285714286</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21.1056576418306</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.04447768895014</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>9.585940889812488</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-20420.19956460702</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8.819182676935043</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8185136253431561</v>
       </c>
     </row>
@@ -4518,7 +7978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9296,1182 @@
         <v>1.000000000000251e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8218301952795388</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1972.498</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2369.067794355129</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.55935e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-58.352</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4268680445151118</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7776947705443157</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.249007862223878</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.227582397348579</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24.04814665321205</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.16577915132731</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.343861700297175</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-19828.45798244592</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-6.630063732283361</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000112e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8177933982786206</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1832.88</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9292176722105676</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2229.304409780478</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9410049028956997</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.61466e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-61.194</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.166273584905667</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1718749999999939</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.156821378340342</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.798462929475662</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18.6007973304738</v>
+      </c>
+      <c r="M24" t="n">
+        <v>83.62452825045602</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.949786582535486</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-20067.30724886391</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.945247587187168</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000002826e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8181484381521468</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1789.713</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9073332393746408</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2182.953899850915</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9214400301470161</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.62738e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-61.952</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1121212121212109</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.571169354838756</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9669083717863549</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.636326023996679</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.87226948236077</v>
+      </c>
+      <c r="M25" t="n">
+        <v>83.83055126744466</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.251097517588128</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-20370.42307694079</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>10.13167266766141</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000001918e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8182197875865584</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1762.941</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8937606020386334</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2156.757962242978</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9103825426110517</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.63498e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-62.36</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3478858350951508</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.020977353992901</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.096551724137973</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.54973305954825</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.29080252833919</v>
+      </c>
+      <c r="M26" t="n">
+        <v>83.9650348185034</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.458834187049936</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20597.93088147454</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>9.990975255010198</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000226e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.818279889635725</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1732.477</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8783162264296339</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2135.174267371211</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9012719148260656</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.64007e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-62.701</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.02926208651398968</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2988977955911664</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.951447245564891</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.336912362159</v>
+      </c>
+      <c r="L27" t="n">
+        <v>16.95622810917169</v>
+      </c>
+      <c r="M27" t="n">
+        <v>83.77616862547849</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.16963221561913</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-19693.17686534335</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>9.168592225950306</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8183684494997781</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1710.21</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8670274950849128</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2113.128122598961</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8919660837203536</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.64831e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-63.109</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1882943143812804</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1510204081632536</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.000280636108542</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.433182076006768</v>
+      </c>
+      <c r="L28" t="n">
+        <v>17.53433330166287</v>
+      </c>
+      <c r="M28" t="n">
+        <v>83.87018936677882</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.3113826683564</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-19793.92875758646</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>8.455207365855358</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8184932486559968</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1695.556</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8595983367283515</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2091.690222495439</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8829169969214861</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.65328e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-63.396</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6347368421052422</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5179982440737453</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9578145695364265</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.690482128013273</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.76744932080738</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.21531341296713</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.87105675004211</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-20864.34924827407</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>8.569087736313804</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8186466810846492</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1675.858</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8496120148157312</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2070.538513574207</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8739887134119844</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.66028e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-63.671</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1390697674418673</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6590796019900218</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.313046495489257</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.581365159128966</v>
+      </c>
+      <c r="L30" t="n">
+        <v>21.85640074615799</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.32075407376576</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.05556231047639</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-21066.67986262115</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>9.161701068936509</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8188129449133479</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1649.471</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8362345614545617</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2049.754371892934</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.865215582592007</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.66653e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-63.943</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.03146766169153264</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4468129571577376</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.7095477386934208</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.445284124194475</v>
+      </c>
+      <c r="L31" t="n">
+        <v>18.36313144980152</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.10431499623327</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.683932627429103</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-20034.87837944888</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>9.786493376261433</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000081e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8190007458013827</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1637.425</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8301275844132668</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2033.841595569403</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8584986889845523</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.67369e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-64.239</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2909407665505153</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7679039301310366</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.388283582089544</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.755659574468069</v>
+      </c>
+      <c r="L32" t="n">
+        <v>23.16256421981209</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.39459888704101</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10.18889896208118</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-20962.99332618411</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>8.535836122222349</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000188e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8191968952765044</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1620.573</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.821584103000358</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2014.978520986468</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8505364539535917</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.68074e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-64.488</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.241043723554316</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8281951219512091</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.409725685785603</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.750479511769812</v>
+      </c>
+      <c r="L33" t="n">
+        <v>23.31820649449569</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.48819197142076</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.36301087432603</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-21147.04181470851</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>9.224742809653776</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.819398544133023</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1597.221</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8097453077265478</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1998.756935928772</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8436892100307508</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.68452e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-64.72499999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.05493197278910691</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5605932203389947</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.162962962962901</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.495202952029508</v>
+      </c>
+      <c r="L34" t="n">
+        <v>19.02803514226293</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.27667473740605</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.977605795602566</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-20121.95237616786</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>8.39011490545272</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000522e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8196288879205859</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1574.211</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7980798966589574</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1981.983045809869</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8366088342986292</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.69242e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-64.98999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.191961414791003</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1630617977528206</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8758139534883993</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.359870782483834</v>
+      </c>
+      <c r="L35" t="n">
+        <v>16.54082510549502</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.06863647500586</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>9.625267057910696</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-19184.5073901818</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>8.257090251617115</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8198401343475772</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1558.589</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7901599900228036</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1965.095460832795</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8294804671757833</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.69735e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-65.199</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2969696969696615</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3851315789473341</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6818956336528617</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.319264069264076</v>
+      </c>
+      <c r="L36" t="n">
+        <v>16.71935717042281</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.12331800311765</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.715468648422329</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-19215.07432547842</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>8.695980208026185</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000099e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8200691839237128</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1556.772</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7892388230558409</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1948.785644122728</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8225959800585597</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.70132e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-65.411</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.472549019607821</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7118993135011537</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.347467876039276</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.864963855421668</v>
+      </c>
+      <c r="L37" t="n">
+        <v>24.94880172072926</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.66097067907468</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10.70041823531683</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-21160.37137131668</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>9.495089067166418</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8202696063643365</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1534.684</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7780408395851353</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1934.252228072879</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8164613240202321</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.70694e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-65.61799999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3783821478382325</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8398657718120702</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9453231939162883</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.576962457337811</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20.22864971093547</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.46436919022685</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.318136356421</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-20173.41678449231</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>8.805646587896604</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8205216769259432</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1513.547</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7673249858808476</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1917.24398774078</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8092820274325087</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.71452e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-65.85899999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1500000000000019</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4660280970625718</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.282992125984167</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.15361890694239</v>
+      </c>
+      <c r="L39" t="n">
+        <v>17.45927884714912</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.24640570436796</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>9.924762957797471</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-19172.14252275833</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>9.48851908544907</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000045e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8207782671205919</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1503.857</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7624124333712886</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1901.57599576875</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.802668459003035</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.71953e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-66.087</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6387520525450973</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5451793721972986</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9971404541631533</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.793554817275863</v>
+      </c>
+      <c r="L40" t="n">
+        <v>20.85165652855288</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.54828666484978</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.47794715915338</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-20148.07418397862</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>9.212940669009868</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000183e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8210302304657228</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1481.24</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7509462620494419</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1887.391402264548</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7966810433883359</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.72619e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-66.294</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.04354587869363801</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5247563352826666</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.7865070729054349</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.334049079754501</v>
+      </c>
+      <c r="L41" t="n">
+        <v>17.8084165862987</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.34739039629048</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10.1032573647088</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-19204.15331752017</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>8.190994789862884</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.00000000000542e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8212928590414705</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1479.339</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7499825094879691</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1869.429907703857</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7890993715579692</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.734e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-66.50700000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4278592375366325</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9012387387386892</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.432857142857106</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.961904761904775</v>
+      </c>
+      <c r="L42" t="n">
+        <v>26.38269113505972</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.88351923064154</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>11.16849675512312</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-21202.28289242541</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>8.986040273767685</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.821558097952326</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1456.159</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7382309132886321</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1854.358312116171</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7827375461920608</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.73957e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-66.75</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1030266343825631</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7848809523809244</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.013526119402955</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.438801791713309</v>
+      </c>
+      <c r="L43" t="n">
+        <v>21.59577158869739</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.6600940446538</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10.69865137251171</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-20063.87136094583</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>8.474280476334457</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000251e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8218301952795388</v>
       </c>
     </row>
@@ -5850,7 +10486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6017,18 +10653,6 @@
       <c r="G2" t="n">
         <v>-53.846</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>8.234688476041077</v>
       </c>
@@ -6552,6 +11176,566 @@
         <v>1.000000000006275e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8186182018649745</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2343.822</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2795.236398252212</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.28544e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-53.846</v>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>8.234688476041077</v>
+      </c>
+      <c r="M12" t="n">
+        <v>81.36431841194489</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.584455517970201</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-17992.93817047779</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-37.6313096100323</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000003688e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8161333206409143</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1983.834</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8464098382897678</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2381.028249025822</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8518164154254063</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.52144e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-59.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3834862385320884</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4263543191800724</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.195845190665972</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.889665127020793</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18.10672055246469</v>
+      </c>
+      <c r="M13" t="n">
+        <v>83.19487280191028</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.379873718206376</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-20013.35023767647</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.302780150581839</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.00000000000679e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8171872320926066</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1889.344</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8060953434177169</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2285.759232023129</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8177337821775486</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.57072e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-60.647</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.08645235361653589</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.395790458372292</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9033918128654946</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.694973070017998</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.5003643464166</v>
+      </c>
+      <c r="M14" t="n">
+        <v>83.52017807525401</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.804454013023333</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-20223.32743608797</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.395094773657092</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000151e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8174623314093123</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1852.22</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7902562566611289</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2240.742149901264</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8016288537536009</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.58989e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-61.393</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1851923076923117</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.742928039702247</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.338007380073789</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.979223536548399</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.21520044792798</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.02204049867409</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.549700837646792</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-21617.461420332</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9.574445163609425</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8176126109616081</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1810.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7725416008553553</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2205.370557930926</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7889746138501511</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.60634e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-61.881</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1470503597122284</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.56597671410087</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.236050860134603</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.822561531449396</v>
+      </c>
+      <c r="L16" t="n">
+        <v>19.46317990057672</v>
+      </c>
+      <c r="M16" t="n">
+        <v>83.90344003211119</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.36255552498617</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-20812.28805137096</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>10.08189709751196</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000014483e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8177529448784333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1786.002</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.762004111233703</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2173.620543692872</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7776159987942274</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.62199e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-62.315</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3252735229759296</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9488742964351774</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.370902817711314</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.006579357655121</v>
+      </c>
+      <c r="L17" t="n">
+        <v>27.72156214473095</v>
+      </c>
+      <c r="M17" t="n">
+        <v>84.28566690441858</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.993411567738487</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-21994.79614495493</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.711316823584184</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.817920919922607</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1746.768</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7452647854657907</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2143.615110655193</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7668815102706662</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.63582e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-62.69</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1038777908343106</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1373088685015246</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.025129725722789</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.796234939759024</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.75838870489735</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.11994026873391</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.709848360727335</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-21017.87469777355</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>9.724797211991927</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8180750580475632</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1716.744</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7324549389842746</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2117.933985248213</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7576940492662808</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.65159e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-63.069</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4305309734513381</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7608784473953437</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.342674616695105</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.87209831588531</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.46812717691878</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.20785551503312</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.858260053169104</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-21064.62675204686</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.515681488402606</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8182563140784691</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1690.529</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7212702159123006</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2091.269825063207</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7481549061005445</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.66405e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-63.424</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3675646551723929</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4226032735775437</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.121720430107549</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.844479495268125</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21.95898081541222</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.25992660385282</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.948298727391515</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-20997.09228365609</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8.090470300594461</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000002584e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.818431322878423</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1665.543</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7106098500654061</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2062.464242260321</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7378496657921048</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.67788e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-63.748</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3976486860304238</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3613333333333243</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.020038659793785</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.027326440177282</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.49958851339385</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.35980011485024</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.1256315615637</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-21129.25677728041</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>9.889819567436916</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000006275e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8186182018649745</v>
       </c>
     </row>
@@ -6566,7 +11750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13068,1182 @@
         <v>1.000000000121306e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8220778198675921</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1981.482</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2400.377869004647</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.5166e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-59.466</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1959183673469399</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6597989949748657</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.100452716297781</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.878398404103713</v>
+      </c>
+      <c r="L23" t="n">
+        <v>19.66364582666129</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.37913450888188</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.615267230236416</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-20573.54412001033</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-11.20961020686627</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000497e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8174266170452604</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1824.727</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9208900207016768</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2232.736109295715</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9301602627346142</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.5857e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-61.761</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.02034104750304589</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5954849498328042</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.345410103204742</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.03013299732778</v>
+      </c>
+      <c r="M24" t="n">
+        <v>83.61803513372645</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.940605284051504</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-19997.39323335383</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>7.276964024628342</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8178427318459133</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1785.352</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.90101853057459</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2186.085563171783</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9107255950823597</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.60358e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-62.368</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.260554371002118</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4878522837706806</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9188461538460965</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.66925425207144</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20.18992051636893</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.03481165514242</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.570295222025628</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-21071.5388380355</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>9.09263911629705</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000225e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8179661160573165</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1767.733</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8921267011257231</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2156.193514432908</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8982725354516815</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.61499e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-62.723</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4680147058823848</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.040714908456841</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.341228070175515</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.191389830508532</v>
+      </c>
+      <c r="L26" t="n">
+        <v>27.82732694138629</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.42708391190912</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.24867052647247</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-22371.36367057697</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>9.004179884348559</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8180717381706577</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1732.844</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8745191730230201</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2131.120562466618</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8878271167157195</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.62565e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-63.063</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1642760487144584</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6416071428571334</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.185607196401746</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.75555555555556</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20.81945140759208</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.23096453301466</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.898019063200836</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-21292.76737316284</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>9.091302643457993</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000113e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8181701141548615</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1713.982</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8650000353270936</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2110.611586795831</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8792830554095339</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.63224e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-63.342</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.322698744769866</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6099735216240337</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9641877256317694</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.750423539901952</v>
+      </c>
+      <c r="L28" t="n">
+        <v>21.34848952029452</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.31447045918324</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.04437579204434</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21420.92662160226</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>9.833912473574401</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000003121e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8182800585519358</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1699</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8574390279598807</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2094.200402554464</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8724461384168888</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.6399e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-63.591</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.05043327556324714</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.5197905759162222</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.186715867158696</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.765391304347803</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.79453431421497</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.38940004641381</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.17939728111461</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-21544.92691483485</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>9.505373595646688</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.00000000000092e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8184168526982933</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1681.85</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8487838900378605</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2078.395783133266</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8658619169802231</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.64761e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-63.819</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1254929577464822</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.782976324689993</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.156786171574951</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.79692168402001</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.32205963369945</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.44831367860151</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.28810946404589</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-21613.73295523469</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>8.864497015298411</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8185938627657556</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1665.735</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8406510884277526</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2062.016094492905</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8590381210888067</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.65302e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-64.02800000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.31796565389697</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.110242587601143</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.227420667209135</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.906088650754924</v>
+      </c>
+      <c r="L31" t="n">
+        <v>22.81025027808876</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.46216642747328</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.31400649386177</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-21505.44090915568</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>9.262050770609449</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000104e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8187742416076917</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1642.453</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.828901297109941</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2044.771086007234</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8518538320198434</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.66007e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-64.283</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.001488833746904069</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4059617547806575</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.356790123456814</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.420941828254865</v>
+      </c>
+      <c r="L32" t="n">
+        <v>18.87809987552327</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.28096502357302</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.98514076686746</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-20594.97147993325</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>9.68358223501923</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.00000000000557e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8189891355133533</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1636.496</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8258949614480475</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2031.359454303393</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8462665318380591</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.66771e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-64.48699999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3273489932885895</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6273316062175948</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.353562447611091</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.952159468438487</v>
+      </c>
+      <c r="L33" t="n">
+        <v>23.35922062666841</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.56837519777463</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.51693366235457</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-21599.7562513388</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>8.946263806449451</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.00000000000031e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8192327580215248</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1614.385</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8147361419382059</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2016.40511992451</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.840036540063854</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.67451e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-64.69199999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.713541666666625</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6293772032902399</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.7183282208588976</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.435401459854079</v>
+      </c>
+      <c r="L34" t="n">
+        <v>19.1503199371461</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.37076751565644</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.14548717122323</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-20608.62393983498</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>8.477206409249561</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8194843553541412</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1600.749</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8078544241128609</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1997.495773507742</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8321588860240716</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.68093e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-64.908</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1962174940898458</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2391719745222758</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.018621399176959</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.394614512471751</v>
+      </c>
+      <c r="L35" t="n">
+        <v>19.36322230843254</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.43795714968284</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.26883245204201</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-20706.39173097324</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>9.532672803656851</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000188e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8197500442627443</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1589.961</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8024100143226131</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1980.974479920332</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8252760973595268</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.68826e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-65.13500000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3358722358722225</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4533849129594112</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.329816513761455</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.822842639593877</v>
+      </c>
+      <c r="L36" t="n">
+        <v>24.51467701874523</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.72405089865927</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.82909361263419</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-21745.41487247886</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>9.792247611856737</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000011993e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.820021308622045</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1563.783</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7891986906769781</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1965.659773339347</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8188959741386208</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.69432e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-65.307</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1125000000000102</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2786707882534825</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.8694623655913647</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.441993720565193</v>
+      </c>
+      <c r="L37" t="n">
+        <v>17.13175230033426</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.27659453564172</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.977465045537503</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-19745.06294729883</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>9.554392886158439</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000151e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8203141624254933</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1548.647</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7815599637039347</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1949.333590815419</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8120944689528153</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.7027e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-65.545</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.07367149758453706</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.158631921824107</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6905544147843979</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.365894039735122</v>
+      </c>
+      <c r="L38" t="n">
+        <v>17.11659033325271</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.286649382455</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>9.995141500560601</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-19617.17045832672</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>9.798301894312544</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.00000000002555e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8206048508333549</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1545.171</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7798057211723347</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1935.739919838689</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8064313310143013</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.70891e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-65.75</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5509554140126989</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.094622093023203</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.362405446293567</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.049121044701122</v>
+      </c>
+      <c r="L39" t="n">
+        <v>25.50213388485793</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.82944702206727</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>11.05107317230602</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-21663.66872149138</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>8.72145154981763</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8208897780338125</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1517.703</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.765943369659679</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1917.281825803126</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7987416692015061</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.71565e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-65.958</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2010638297872467</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.820043811610139</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.29107901444348</v>
+      </c>
+      <c r="L40" t="n">
+        <v>17.53740833600056</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.40794136611431</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.21336499026455</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-19724.6107521858</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>9.650037811633865</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000024667e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8211831260788123</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1495.006</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7544888119094698</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1904.92627458767</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7935943332861909</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.72242e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-66.15600000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.02925262411359317</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.3329016411290147</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.345867295065355</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.317468293052444</v>
+      </c>
+      <c r="L41" t="n">
+        <v>38.79862059585109</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.19932005317142</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9.84365465197263</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-18794.78887703615</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>7.560124151563627</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000002782e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8214780621471813</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1489.912</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7519180088438856</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1886.237358333607</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7858085106890957</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.73186e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-66.38</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1522550544323391</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6109782608695393</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9685929648241338</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.82022160664816</v>
+      </c>
+      <c r="L42" t="n">
+        <v>21.18034895660722</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.66776912249384</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10.71414021119617</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-20401.18930379382</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>8.394813921640207</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8217749184601845</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1483.075</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7484675611486755</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1871.699050793504</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7797518361430456</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.73981e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-66.611</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7194871794871567</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5343832020997323</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.151388888888861</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.774398931433593</v>
+      </c>
+      <c r="L43" t="n">
+        <v>26.56287558678353</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.95685930851931</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.3317755292129</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-21468.21191511771</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>7.504666018168905</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000121306e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8220778198675921</v>
       </c>
     </row>
@@ -7898,7 +14258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14960,566 @@
         <v>1.000000000000597e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8177875118159668</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2256.101</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2732.462939544247</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.31914e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-53.358</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1389931740614312</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7245493107105099</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.288827636898208</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.062925683610159</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.61971839664786</v>
+      </c>
+      <c r="M12" t="n">
+        <v>80.51210212876322</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.983528072630889</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-15874.34624754627</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-47.19738009822481</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8155172555282038</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1906.253</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8449324742110393</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2324.427546521652</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8506712068743915</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.56388e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-58.882</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.08793103448276125</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5272817460317337</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9409596662030196</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.586843211433382</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13.56235382455064</v>
+      </c>
+      <c r="M13" t="n">
+        <v>82.8008771632378</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7.916789803945005</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-18389.01727795352</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.572019347119749</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000011993e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8165086764521647</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1832.576</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8122756915581349</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2230.092464380623</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8161473782889018</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.60971e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-60.653</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2468435498627512</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5976987447698477</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.274279123414075</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.032618296529959</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.89910652263104</v>
+      </c>
+      <c r="M14" t="n">
+        <v>83.800322581817</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.205639155701688</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-20764.14428771099</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.929667176283147</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8166992361082839</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1778.58</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7883423658781233</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2191.131046110046</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8018886603730147</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.6273e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-61.436</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1470588235294004</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.287663107947844</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.330056497175139</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15.30167275544352</v>
+      </c>
+      <c r="M15" t="n">
+        <v>83.56031029996976</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.859792687787619</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-19510.06915356576</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9.381536919267774</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.816749196087574</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1762.227</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7810940201701961</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2160.400628560996</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7906422434118477</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.64217e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-61.976</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3713188220231063</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.653948462177858</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.572194199243367</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.183277814790173</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25.08181189675972</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.23501132711984</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.905014248056899</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-21674.40370160397</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.141523082435697</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000026449e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8168381229918887</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1724.641</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7644343050244647</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2129.963058547788</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.779502999921034</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.65402e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-62.345</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2295757575757543</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.602048085485331</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.02297200287156</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.787950200088943</v>
+      </c>
+      <c r="L17" t="n">
+        <v>19.25451336890452</v>
+      </c>
+      <c r="M17" t="n">
+        <v>84.10817881209063</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.690328319741196</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-20864.73366181109</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.790546984848561</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8169639935614609</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1695.8</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7516507461323763</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2103.119435085283</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7696790337570201</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.66921e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-62.762</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2239130434782363</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5164948453607965</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.226533864541761</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.923291626564001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.16479779337769</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.23032734038878</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.896918519469001</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-21043.62329328149</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>9.562170844712227</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000303e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8171037842308665</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1670.12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7402682769964641</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2076.942133145929</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7600989214120306</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.68514e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-63.142</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.01626984126982352</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7189767441860725</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.23158301158298</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.744984669294811</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.95283912038498</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.28896888205668</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.999227994732648</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-20996.50124691442</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.851980231398784</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000001071e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8173117676151218</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1642.478</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7280161659429253</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2053.278987997978</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7514389155230221</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.69867e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-63.476</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.46795774647887</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5330365093499739</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.557218777679419</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.794229074889852</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21.54304900235988</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.36956451087175</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.14330546159123</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-21047.23939884337</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.760981088109702</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000808e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8175302622281605</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1621.088</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7185352074220082</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2027.945174061228</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7421674946484264</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.71307e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-63.814</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4576051779935844</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8505714285714113</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.168970814132045</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.807663896583642</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.07616813643018</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.47507958186047</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.33826358341666</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-21213.48890531447</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>8.344275295139369</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000597e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8177875118159668</v>
       </c>
     </row>
@@ -8614,7 +15534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16852,1182 @@
         <v>1.000000000000043e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8217239236305618</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1834.501</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2262.352426549757</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.59609e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-61.009</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0748120300751902</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5361007462686694</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.137841625788382</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.479186413902029</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.46062478302137</v>
+      </c>
+      <c r="M23" t="n">
+        <v>83.5543991192702</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8.851598617414627</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-19952.42369852823</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-7.088257246394051</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8173246663261311</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1730.541</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9433306386859422</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2136.443379340288</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9443459623125613</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.65467e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-62.502</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1963380281689936</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5152654867256768</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.431133540372693</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.839020843431862</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19.9011448805181</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.08925682497375</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.659086668367813</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-20793.57053931227</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.479499400562872</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8176015206148097</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1692.576</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9226356377020235</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2097.037108921224</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9269276900943986</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.67275e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-62.975</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0489112227805572</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6816784869975813</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.224822190611617</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.627798901563164</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20.61133451116726</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.21018159591914</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>9.862247753027239</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-20881.19554562695</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>8.394378785217668</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8176559638828779</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1657.131</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9033143072693882</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2068.208957815589</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.914185134705007</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.68375e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-63.281</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.154945054945038</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8013353115726938</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9853202846974791</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.462901376146825</v>
+      </c>
+      <c r="L26" t="n">
+        <v>17.25250939835447</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.0573327975454</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.60682703902185</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-20031.4761887961</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>9.368145053868375</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8177376544004198</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1638.692</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8932630726284695</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2046.173931237407</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9044452611470279</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.69563e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-63.596</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3045366795366647</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.807838983050774</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.258918918918867</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.09236076885161</v>
+      </c>
+      <c r="L27" t="n">
+        <v>21.48362324576938</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.34704382289181</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.10263391301911</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-20899.76336249191</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8.08813017735406</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.00000000000017e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8178344398151369</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1615.773</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8807697570074914</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2022.641390014108</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8940434594882174</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.70626e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-63.888</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4997633136094589</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4712918660287061</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.099537037037107</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.863270142180041</v>
+      </c>
+      <c r="L28" t="n">
+        <v>21.8429634525422</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.43734079830348</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.26768746907202</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-21030.50437148828</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>8.565804514970296</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8179709595681299</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1583.603</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8632336531841628</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2002.37674349418</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8850861253955654</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.71799e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-64.15900000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1372093023255872</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1632102272727234</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5744755244754897</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.480989180834662</v>
+      </c>
+      <c r="L29" t="n">
+        <v>15.95354433378363</v>
+      </c>
+      <c r="M29" t="n">
+        <v>83.99080242413268</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.499694835795008</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-19138.33906001406</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>8.78968730474719</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8181370194560634</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1578.355</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8603729297503789</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1984.363402220162</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8771239082526381</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.7292e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-64.395</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3059602649006583</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8247311827957384</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.302034428795044</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.969181141439258</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.79719582802324</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.51384114708173</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.41176006984398</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-20923.40766616633</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>8.101591715258792</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8183280814833082</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1553.738</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8469540218293692</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1969.556873323653</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8705791592017177</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.73763e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-64.60299999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2335897435897476</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8039503386004322</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.107149758454123</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.541460470730267</v>
+      </c>
+      <c r="L31" t="n">
+        <v>18.68171960298863</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.32091260584585</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.05584485917781</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-19972.2463116406</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>7.382714975310364</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8185505935177548</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1533.59</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8359711987074413</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1951.863754489502</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8627584860711682</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.74687e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-64.825</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1552875695732857</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1848314606741487</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.8980362537763764</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.501993355481739</v>
+      </c>
+      <c r="L32" t="n">
+        <v>16.63378257857468</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.14704381011862</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.755128718863007</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-19163.82370747895</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>7.999465362383944</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8187869365856546</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1520.407</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8287850483591994</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1935.586685018689</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8555637319383486</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.75528e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-65.027</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1801611278952677</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5463903743315345</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.398526315789415</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.467764298093565</v>
+      </c>
+      <c r="L33" t="n">
+        <v>19.41236923403016</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.40980167338525</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.21678547260878</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-19974.30768321452</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>7.926149217375951</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000876e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8190313616880684</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1502.207</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.818864094377708</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1919.94761806321</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8486509862617925</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.76469e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-65.264</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1640465793304201</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.03872832369942201</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8859234234234478</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.538610378188251</v>
+      </c>
+      <c r="L34" t="n">
+        <v>16.80655903712441</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.21281745699126</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.866770383495455</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19071.30151111697</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>7.668364982572143</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000038715e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8192951388287493</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1487.358</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8107697951650066</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1904.998048098118</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8420430105151085</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.77318e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-65.47199999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.02061349693251201</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1388489208633126</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8564722617353453</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.370229007633536</v>
+      </c>
+      <c r="L35" t="n">
+        <v>16.86446670764263</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.26872441677907</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>9.963672478044014</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-19107.99141286724</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>7.453956290336237</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8195449557188662</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1474.18</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8035863703535729</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1886.692053940182</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8339514355937536</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.78166e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-65.669</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3023904382470256</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3964664310954357</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.107221542227598</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.493669803250675</v>
+      </c>
+      <c r="L36" t="n">
+        <v>17.14309350332852</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.27469124761832</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.97412602405227</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-18975.23095006755</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>8.578137654669717</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8198153963052757</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1458.19</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7948701036412626</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1870.791930518222</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8269232983171012</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.79004e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-65.892</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.03828124999999826</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4239454094293033</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9264634146341579</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.408581138487672</v>
+      </c>
+      <c r="L37" t="n">
+        <v>17.38867140859042</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.28098358509754</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.985173390700096</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-18841.88034951055</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>9.08367648701369</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000098e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8200853084615732</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1452.395</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7917112064806723</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1859.597049504112</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8219749618498324</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.79878e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-66.048</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6505555555556124</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6110091743119126</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.258864541832704</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.65665829145731</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20.44918926322903</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.58584851380431</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.55107928218669</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-19826.84922533125</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>7.177916220073939</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8203575111761711</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1431.534</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7803397218099091</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1842.427358729804</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8143856532289412</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.80715e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-66.29000000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.03673110720562076</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3247524752475102</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.8567360350493016</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.592844677137885</v>
+      </c>
+      <c r="L39" t="n">
+        <v>17.52263532439852</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.33590775682683</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10.08264169778994</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-18725.29177948506</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>8.351591371899076</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.00000000000006e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8206301626029076</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1426.919</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7778240513360308</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1828.93125160525</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8084201339021683</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.8148e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-66.46299999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6942381562099648</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.345919778699847</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.652189781021872</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.003128103277153</v>
+      </c>
+      <c r="L40" t="n">
+        <v>25.5149896845222</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.8472275073682</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>11.08941417681177</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-20569.15604088516</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>7.649121094558495</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000001002e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8209033797924614</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1402.282</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7643942412677888</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1812.94602697409</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8013543803778429</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.82385e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-66.68000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3023853211009121</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4100502512563085</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.025245901639266</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.494798657718168</v>
+      </c>
+      <c r="L41" t="n">
+        <v>17.44413620813657</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.3718801124962</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>10.14750574900208</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-18543.72508123181</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>8.306132315121204</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8211643784372921</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1388.654</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7569655181436259</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1798.60661190368</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7950161039439282</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.8306e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-66.855</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1186046511628068</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7689463955637642</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.188563829787132</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.226170376055194</v>
+      </c>
+      <c r="L42" t="n">
+        <v>17.81629726446116</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.41751953333907</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10.23100030374475</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-18551.96748768415</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>8.026610231083055</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8214385401595771</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1381.295</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7529540730694614</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1786.30793547346</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7895798702758714</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.83893e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-67.05</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5647696476963108</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5908685968819308</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.217177242888365</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.905502567865054</v>
+      </c>
+      <c r="L43" t="n">
+        <v>20.84607862213791</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.674206150773</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10.72716490197373</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-19356.70630630733</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>6.535439744962105</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8217239236305618</v>
       </c>
     </row>
@@ -9946,7 +18042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18747,566 @@
         <v>0.8201622407633004</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1793.609</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2328.331339659278</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.56611e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-58.574</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3486046511627698</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5514157014157092</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.232695139911637</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.885199076745522</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.81704803791686</v>
+      </c>
+      <c r="M12" t="n">
+        <v>81.94691809876741</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.067851536595724</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-15811.89697297614</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-72.90398331008555</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.00000000000365e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8175070335430823</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1447.856</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8072305613988332</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1896.043490455103</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8143357683501201</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.79414e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-64.09399999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3588477366254406</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5127753303964417</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6373447946513836</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.477863910422069</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13.98046504472647</v>
+      </c>
+      <c r="M13" t="n">
+        <v>83.70293679891785</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.062145301212764</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-17208.84006990088</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-4.630950554463311</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000007021e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8184154589588939</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1374.545</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7663571045863397</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1813.807671953809</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7790161310199247</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.82684e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-65.599</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1738582677165369</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3570347957640028</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.357492795388785</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.372817764165362</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16.10290299005365</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.20803156131308</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.858561745178738</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-18040.81103764051</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.454712293143871</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8185937882319108</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1334.922</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7442658907264628</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1780.38760503424</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7646624750989167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.83732e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-66.264</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.08115696536102841</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6274840578390521</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.292061199343341</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.299978270548977</v>
+      </c>
+      <c r="L15" t="n">
+        <v>32.33805799693324</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.22866483204541</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.894048215477767</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-17730.1866662091</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.650123948556825</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000001067e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8187290695597692</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1308.322</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7294354566686497</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1754.051977482677</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7533515301732612</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.84756e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-66.679</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.04210455880302637</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7824916385878236</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.517462033495072</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.290929851793189</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.38576633600083</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.32231179456203</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.05833928846686</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-17767.14966146949</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.815582543673827</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000221e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8188776381573664</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1282.416</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7149919519806156</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1728.85546441163</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7425298259588026</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.85869e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-67.093</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1457748853064295</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7718386937785487</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.508840863099997</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.307237582321114</v>
+      </c>
+      <c r="L17" t="n">
+        <v>36.71233965526284</v>
+      </c>
+      <c r="M17" t="n">
+        <v>84.40353029469115</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10.2052635662021</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-17781.51214802358</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.773269457453694</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.00000000000158e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8190833049760865</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1255.304</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6998760599439455</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1787.870708857163</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7678764093424928</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.86851e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-67.431</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2994496512641588</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5417194830273654</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.222136092536269</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.996206807629712</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.3574052993444</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.31086005262659</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.03795944193657</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-17207.21778862729</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-41.43701217090336</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000006949e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8193265740749397</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1232.165</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6869752549189929</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1686.107590470732</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7241699502775545</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.88131e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-67.727</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7832055013424076</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.141664433747493</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.047436710604299</v>
+      </c>
+      <c r="L19" t="n">
+        <v>27.25101787174676</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.39118073912169</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>10.18264979393043</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-17229.11253867616</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.067123769127761</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000086e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8195900053713181</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1218.456</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6793320060280698</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1666.580451865371</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7157831978112076</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.89084e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-68.029</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1387692307692332</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5932170542635534</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8230834035383143</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.506753458096021</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18.71147425255148</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.81318980529782</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>11.01624630188137</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-18499.84125285816</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.6802594764826608</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000042839e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.819881167266154</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1188.819</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6628083378261372</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1644.293726374507</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7062112244793856</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.90098e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-68.342</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1797860043332367</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.4857745568484353</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.213098180450833</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.044100565635068</v>
+      </c>
+      <c r="L21" t="n">
+        <v>28.27694640384896</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.49627319990968</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.37832129807491</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-17120.9332421032</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.1366675286308237</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000042385e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8201622407633004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
